--- a/setbet/locales-excel/gu.xlsx
+++ b/setbet/locales-excel/gu.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C502"/>
+  <dimension ref="A1:C524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -994,46 +994,46 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>cms.defaultPageName</t>
+          <t>jackpot.pageName</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>પેજ</t>
+          <t>જેકપોટ</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>seo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>jackpotWinners.pageName</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>સબમિટ કરો</t>
+          <t>જેકપોટ વિજેતાઓ</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>seo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>submitting</t>
+          <t>cms.defaultPageName</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>સબમિટ થઈ રહ્યું છે…</t>
+          <t>પેજ</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>loading</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>લોડ થઈ રહ્યું છે</t>
+          <t>સબમિટ કરો</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>submitting</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>સંપાદિત કરો</t>
+          <t>સબમિટ થઈ રહ્યું છે…</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>loading</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>રદ કરો</t>
+          <t>લોડ થઈ રહ્યું છે</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>close</t>
+          <t>edit</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>બંધ કરો</t>
+          <t>સંપાદિત કરો</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>retry</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ફરી પ્રયાસ કરો</t>
+          <t>રદ કરો</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>tryAgain</t>
+          <t>close</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ફરી પ્રયાસ કરો</t>
+          <t>બંધ કરો</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>goBackHome</t>
+          <t>retry</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>હોમ પર પાછા જાઓ</t>
+          <t>ફરી પ્રયાસ કરો</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>readMore</t>
+          <t>tryAgain</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>વધુ વાંચો</t>
+          <t>ફરી પ્રયાસ કરો</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>seeAll</t>
+          <t>goBackHome</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>બધું જુઓ</t>
+          <t>હોમ પર પાછા જાઓ</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>pick</t>
+          <t>readMore</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>પસંદ કરો</t>
+          <t>વધુ વાંચો</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>seeAll</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ઠીક છે</t>
+          <t>બધું જુઓ</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>or</t>
+          <t>pick</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>અથવા</t>
+          <t>પસંદ કરો</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>of</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>નો</t>
+          <t>ઠીક છે</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>અપડેટ કરો</t>
+          <t>અથવા</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>updating</t>
+          <t>of</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>અપડેટ થઈ રહ્યું છે…</t>
+          <t>નો</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>update</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>હા</t>
+          <t>અપડેટ કરો</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>updating</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ના</t>
+          <t>અપડેટ થઈ રહ્યું છે…</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>copied</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>કૉપી થઈ ગયું</t>
+          <t>હા</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>copy</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>કૉપી કરો</t>
+          <t>ના</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>downloadImage</t>
+          <t>copied</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>છબી ડાઉનલોડ કરો</t>
+          <t>કૉપી થઈ ગયું</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>notAvailable</t>
+          <t>copy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ઉપલબ્ધ નથી</t>
+          <t>કૉપી કરો</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>gotIt</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>કુલ</t>
+          <t>સમજી ગયું!</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>goToSlide</t>
+          <t>downloadImage</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>સ્લાઇડ {{index}} પર જાઓ</t>
+          <t>છબી ડાઉનલોડ કરો</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>logoAlt</t>
+          <t>notAvailable</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>લોગો</t>
+          <t>ઉપલબ્ધ નથી</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>whatsappCta</t>
+          <t>total</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>WhatsApp પર તમારી ID મેળવો</t>
+          <t>કુલ</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>noDataAvailable</t>
+          <t>goToSlide</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>કોઈ ડેટા ઉપલબ્ધ નથી</t>
+          <t>સ્લાઇડ {{index}} પર જાઓ</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>imageUpload.preview</t>
+          <t>logoAlt</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>પૂર્વાવલોકન</t>
+          <t>લોગો</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>imageUpload.imagePreviewAlt</t>
+          <t>whatsappCta</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>અપલોડ કરેલી રસીદ પૂર્વાવલોકન</t>
+          <t>WhatsApp પર તમારી ID મેળવો</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>imageUpload.modalImageAlt</t>
+          <t>noDataAvailable</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>રસીદ પૂર્વાવલોકન</t>
+          <t>કોઈ ડેટા ઉપલબ્ધ નથી</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>imageUpload.removeImage</t>
+          <t>creditedToWallet</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>છબી દૂર કરો</t>
+          <t>તમારા વૉલેટમાં જમા કરવામાં આવ્યું</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>imageUpload.clickToUpload</t>
+          <t>imageUpload.preview</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>અપલોડ કરવા ક્લિક કરો</t>
+          <t>પૂર્વાવલોકન</t>
         </is>
       </c>
     </row>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>imageUpload.dragAndDrop</t>
+          <t>imageUpload.imagePreviewAlt</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>અથવા ખેંચો અને છોડો</t>
+          <t>અપલોડ કરેલી રસીદ પૂર્વાવલોકન</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>imageUpload.fileTypesHint</t>
+          <t>imageUpload.modalImageAlt</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>JPG, JPEG, PNG અથવા SVG (મહત્તમ 1MB)</t>
+          <t>રસીદ પૂર્વાવલોકન</t>
         </is>
       </c>
     </row>
@@ -1606,12 +1606,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>imageUpload.browseFiles</t>
+          <t>imageUpload.removeImage</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ફાઇલ બ્રાઉઝ કરો</t>
+          <t>છબી દૂર કરો</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>imageUpload.toastInvalidFileTypeErr</t>
+          <t>imageUpload.clickToUpload</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>માત્ર JPG, JPEG, PNG અને SVG ફાઇલો માન્ય છે.</t>
+          <t>અપલોડ કરવા ક્લિક કરો</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>imageUpload.toastFileSizeExceededErr</t>
+          <t>imageUpload.dragAndDrop</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ફાઇલ કદ 1MB ની મર્યાદા કરતાં વધી ગઈ છે.</t>
+          <t>અથવા ખેંચો અને છોડો</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>imageUpload.toastValidFileErr</t>
+          <t>imageUpload.fileTypesHint</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>કૃપા કરીને પ્રથમ માન્ય ફાઇલ પસંદ કરો.</t>
+          <t>JPG, JPEG, PNG અથવા SVG (મહત્તમ 1MB)</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>imageUpload.toastNoFileErr</t>
+          <t>imageUpload.browseFiles</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>કોઈ ફાઇલ પસંદ નથી</t>
+          <t>ફાઇલ બ્રાઉઝ કરો</t>
         </is>
       </c>
     </row>
@@ -1691,12 +1691,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>banner.defaultAlt</t>
+          <t>imageUpload.toastInvalidFileTypeErr</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>બૅનર {{index}}</t>
+          <t>માત્ર JPG, JPEG, PNG અને SVG ફાઇલો માન્ય છે.</t>
         </is>
       </c>
     </row>
@@ -1708,12 +1708,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>timeLeft.dayLeft</t>
+          <t>imageUpload.toastFileSizeExceededErr</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{{count}} દિવસ બાકી</t>
+          <t>ફાઇલ કદ 1MB ની મર્યાદા કરતાં વધી ગઈ છે.</t>
         </is>
       </c>
     </row>
@@ -1725,12 +1725,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>timeLeft.daysLeft</t>
+          <t>imageUpload.toastValidFileErr</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{{count}} દિવસ બાકી</t>
+          <t>કૃપા કરીને પ્રથમ માન્ય ફાઇલ પસંદ કરો.</t>
         </is>
       </c>
     </row>
@@ -1742,12 +1742,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>timeLeft.hoursLeft</t>
+          <t>imageUpload.toastNoFileErr</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{{count}} કલાક બાકી</t>
+          <t>કોઈ ફાઇલ પસંદ નથી</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>timeLeft.minsLeft</t>
+          <t>banner.defaultAlt</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{{count}} મિનિટ બાકી</t>
+          <t>બૅનર {{index}}</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>timeLeft.expired</t>
+          <t>timeLeft.dayLeft</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>સમય સમાપ્ત</t>
+          <t>{{count}} દિવસ બાકી</t>
         </is>
       </c>
     </row>
@@ -1793,12 +1793,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>days.mo</t>
+          <t>timeLeft.daysLeft</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>સો</t>
+          <t>{{count}} દિવસ બાકી</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>days.tu</t>
+          <t>timeLeft.hoursLeft</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>મં</t>
+          <t>{{count}} કલાક બાકી</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>days.we</t>
+          <t>timeLeft.minsLeft</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>બુ</t>
+          <t>{{count}} મિનિટ બાકી</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>days.th</t>
+          <t>timeLeft.expired</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ગુ</t>
+          <t>સમય સમાપ્ત</t>
         </is>
       </c>
     </row>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>days.fr</t>
+          <t>days.mo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>શુ</t>
+          <t>સો</t>
         </is>
       </c>
     </row>
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>days.sa</t>
+          <t>days.tu</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>શ</t>
+          <t>મં</t>
         </is>
       </c>
     </row>
@@ -1895,80 +1895,80 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>days.su</t>
+          <t>days.we</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ર</t>
+          <t>બુ</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>auth</t>
+          <t>common</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>login.title</t>
+          <t>days.th</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>લૉગ ઇન</t>
+          <t>ગુ</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>auth</t>
+          <t>common</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>login.usernamePlaceholder</t>
+          <t>days.fr</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>વપરાશકર્તા નામ</t>
+          <t>શુ</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>auth</t>
+          <t>common</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>login.passwordPlaceholder</t>
+          <t>days.sa</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>પાસવર્ડ</t>
+          <t>શ</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>auth</t>
+          <t>common</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>login.forgotPassword</t>
+          <t>days.su</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>પાસવર્ડ ભૂલ્યા?</t>
+          <t>ર</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>login.submitIdle</t>
+          <t>login.title</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>હવે લૉગ ઇન કરો</t>
+          <t>લૉગ ઇન</t>
         </is>
       </c>
     </row>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>login.submitLoading</t>
+          <t>login.usernamePlaceholder</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>લૉગ ઇન થઈ રહ્યું છે…</t>
+          <t>વપરાશકર્તા નામ</t>
         </is>
       </c>
     </row>
@@ -2014,12 +2014,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>login.noAccount</t>
+          <t>login.passwordPlaceholder</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ખાતું નથી?</t>
+          <t>પાસવર્ડ</t>
         </is>
       </c>
     </row>
@@ -2031,12 +2031,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>login.registerNow</t>
+          <t>login.forgotPassword</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>હવે નોંધણી કરો</t>
+          <t>પાસવર્ડ ભૂલ્યા?</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2048,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>login.whatsappCta</t>
+          <t>login.submitIdle</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>WhatsApp પર તમારી ID મેળવો</t>
+          <t>હવે લૉગ ઇન કરો</t>
         </is>
       </c>
     </row>
@@ -2065,12 +2065,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>login.bannerAltPrefix</t>
+          <t>login.submitLoading</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>લૉગ ઇન બૅનર</t>
+          <t>લૉગ ઇન થઈ રહ્યું છે…</t>
         </is>
       </c>
     </row>
@@ -2082,12 +2082,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>login.toastSuccess</t>
+          <t>login.noAccount</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>લૉગ ઇન સફળ</t>
+          <t>ખાતું નથી?</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>login.toastError</t>
+          <t>login.registerNow</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>લૉગ ઇન નિષ્ફળ</t>
+          <t>હવે નોંધણી કરો</t>
         </is>
       </c>
     </row>
@@ -2116,12 +2116,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>login.validation.usernameRequired</t>
+          <t>login.whatsappCta</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>વપરાશકર્તા નામ જરૂરી છે</t>
+          <t>WhatsApp પર તમારી ID મેળવો</t>
         </is>
       </c>
     </row>
@@ -2133,12 +2133,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>login.validation.usernameMinLength</t>
+          <t>login.bannerAltPrefix</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ઓછામાં ઓછા 3 અક્ષર</t>
+          <t>લૉગ ઇન બૅનર</t>
         </is>
       </c>
     </row>
@@ -2150,12 +2150,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>login.validation.usernameMaxLength</t>
+          <t>login.toastSuccess</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>16 અક્ષરથી વધુ ન હોઈ શકે</t>
+          <t>લૉગ ઇન સફળ</t>
         </is>
       </c>
     </row>
@@ -2167,12 +2167,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>login.validation.usernameNoSpaces</t>
+          <t>login.toastError</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>વપરાશકર્તા નામમાં ખાલી જગ્યા માન્ય નથી</t>
+          <t>લૉગ ઇન નિષ્ફળ</t>
         </is>
       </c>
     </row>
@@ -2184,12 +2184,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>login.validation.passwordRequired</t>
+          <t>login.validation.usernameRequired</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>પાસવર્ડ જરૂરી છે</t>
+          <t>વપરાશકર્તા નામ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -2201,12 +2201,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>login.validation.passwordPattern</t>
+          <t>login.validation.usernameMinLength</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>પાસવર્ડ 8–15 અક્ષરનો હોવો જોઈએ, જેમાં અપરકેઝ, લોઅરકેઝ, સંખ્યા અને વિશેષ અક્ષર હોવા જોઈએ</t>
+          <t>ઓછામાં ઓછા 3 અક્ષર</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>login.validation.showPassword</t>
+          <t>login.validation.usernameMaxLength</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>પાસવર્ડ બતાવો</t>
+          <t>16 અક્ષરથી વધુ ન હોઈ શકે</t>
         </is>
       </c>
     </row>
@@ -2235,12 +2235,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>login.validation.hidePassword</t>
+          <t>login.validation.usernameNoSpaces</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>પાસવર્ડ છુપાવો</t>
+          <t>વપરાશકર્તા નામમાં ખાલી જગ્યા માન્ય નથી</t>
         </is>
       </c>
     </row>
@@ -2252,12 +2252,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>register.title</t>
+          <t>login.validation.passwordRequired</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>નોંધણી</t>
+          <t>પાસવર્ડ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>register.usernamePlaceholder</t>
+          <t>login.validation.passwordPattern</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>વપરાશકર્તા નામ</t>
+          <t>પાસવર્ડ 8–15 અક્ષરનો હોવો જોઈએ, જેમાં અપરકેઝ, લોઅરકેઝ, સંખ્યા અને વિશેષ અક્ષર હોવા જોઈએ</t>
         </is>
       </c>
     </row>
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>register.passwordPlaceholder</t>
+          <t>login.validation.showPassword</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>પાસવર્ડ</t>
+          <t>પાસવર્ડ બતાવો</t>
         </is>
       </c>
     </row>
@@ -2303,12 +2303,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>register.confirmPasswordPlaceholder</t>
+          <t>login.validation.hidePassword</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>પાસવર્ડ ની પુષ્ટિ કરો</t>
+          <t>પાસવર્ડ છુપાવો</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>register.promoCodePlaceholder</t>
+          <t>register.title</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>પ્રોમો કોડ (વૈકલ્પિક)</t>
+          <t>નોંધણી</t>
         </is>
       </c>
     </row>
@@ -2337,12 +2337,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>register.countryPlaceholder</t>
+          <t>register.usernamePlaceholder</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>દેશ</t>
+          <t>વપરાશકર્તા નામ</t>
         </is>
       </c>
     </row>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>register.mobileNumberPlaceholder</t>
+          <t>register.passwordPlaceholder</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>મોબાઇલ નંબર</t>
+          <t>પાસવર્ડ</t>
         </is>
       </c>
     </row>
@@ -2371,12 +2371,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>register.checkboxAge</t>
+          <t>register.confirmPasswordPlaceholder</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>હું ઓછામાં ઓછો 18 વર્ષનો/ની છું</t>
+          <t>પાસવર્ડ ની પુષ્ટિ કરો</t>
         </is>
       </c>
     </row>
@@ -2388,12 +2388,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>register.checkboxTerms</t>
+          <t>register.promoCodePlaceholder</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>હું શરતો અને ગોપનીયતા સ્વીકારું છું</t>
+          <t>પ્રોમો કોડ (વૈકલ્પિક)</t>
         </is>
       </c>
     </row>
@@ -2405,12 +2405,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>register.submitIdle</t>
+          <t>register.countryPlaceholder</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>હવે નોંધણી કરો</t>
+          <t>દેશ</t>
         </is>
       </c>
     </row>
@@ -2422,12 +2422,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>register.submitLoading</t>
+          <t>register.mobileNumberPlaceholder</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>નોંધણી થઈ રહી છે...</t>
+          <t>મોબાઇલ નંબર</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>register.whatsappCta</t>
+          <t>register.checkboxAge</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>WhatsApp પર તમારી ID મેળવો</t>
+          <t>હું ઓછામાં ઓછો 18 વર્ષનો/ની છું</t>
         </is>
       </c>
     </row>
@@ -2456,12 +2456,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>register.bannerAltPrefix</t>
+          <t>register.checkboxTerms</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>નોંધણી બૅનર</t>
+          <t>હું શરતો અને ગોપનીયતા સ્વીકારું છું</t>
         </is>
       </c>
     </row>
@@ -2473,12 +2473,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>register.toastSuccess</t>
+          <t>register.submitIdle</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>સફળતાપૂર્વક નોંધણી થઈ</t>
+          <t>હવે નોંધણી કરો</t>
         </is>
       </c>
     </row>
@@ -2490,12 +2490,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>register.toastError</t>
+          <t>register.submitLoading</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>નોંધણી નિષ્ફળ</t>
+          <t>નોંધણી થઈ રહી છે...</t>
         </is>
       </c>
     </row>
@@ -2507,12 +2507,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>register.validation.usernameRequired</t>
+          <t>register.whatsappCta</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>વપરાશકર્તા નામ જરૂરી છે</t>
+          <t>WhatsApp પર તમારી ID મેળવો</t>
         </is>
       </c>
     </row>
@@ -2524,12 +2524,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>register.validation.usernameMinLength</t>
+          <t>register.bannerAltPrefix</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ઓછામાં ઓછા 3 અક્ષર</t>
+          <t>નોંધણી બૅનર</t>
         </is>
       </c>
     </row>
@@ -2541,12 +2541,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>register.validation.usernameMaxLength</t>
+          <t>register.toastSuccess</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>મહત્તમ 16 અક્ષર</t>
+          <t>સફળતાપૂર્વક નોંધણી થઈ</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>register.validation.usernameNoSpaces</t>
+          <t>register.toastError</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>વપરાશકર્તા નામમાં ખાલી જગ્યા માન્ય નથી</t>
+          <t>નોંધણી નિષ્ફળ</t>
         </is>
       </c>
     </row>
@@ -2575,12 +2575,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>register.validation.passwordRequired</t>
+          <t>register.validation.usernameRequired</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>પાસવર્ડ જરૂરી છે</t>
+          <t>વપરાશકર્તા નામ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -2592,12 +2592,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>register.validation.passwordPattern</t>
+          <t>register.validation.usernameMinLength</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>8–15 અક્ષર, અપરકેઝ, લોઅરકેઝ, સંખ્યા અને વિશેષ અક્ષર સહિત હોવા જોઈએ</t>
+          <t>ઓછામાં ઓછા 3 અક્ષર</t>
         </is>
       </c>
     </row>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>register.validation.confirmPasswordRequired</t>
+          <t>register.validation.usernameMaxLength</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>પાસવર્ડ ની પુષ્ટિ જરૂરી છે</t>
+          <t>મહત્તમ 16 અક્ષર</t>
         </is>
       </c>
     </row>
@@ -2626,12 +2626,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>register.validation.confirmPasswordMismatch</t>
+          <t>register.validation.usernameNoSpaces</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>પાસવર્ડ મેળ ખાતા નથી</t>
+          <t>વપરાશકર્તા નામમાં ખાલી જગ્યા માન્ય નથી</t>
         </is>
       </c>
     </row>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>register.validation.countryRequired</t>
+          <t>register.validation.passwordRequired</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>દેશ કોડ જરૂરી છે</t>
+          <t>પાસવર્ડ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>register.validation.mobileNumberRequired</t>
+          <t>register.validation.passwordPattern</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>મોબાઇલ નંબર જરૂરી છે</t>
+          <t>8–15 અક્ષર, અપરકેઝ, લોઅરકેઝ, સંખ્યા અને વિશેષ અક્ષર સહિત હોવા જોઈએ</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>register.validation.mobileNumberInvalid</t>
+          <t>register.validation.confirmPasswordRequired</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>અમાન્ય નંબર</t>
+          <t>પાસવર્ડ ની પુષ્ટિ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -2694,12 +2694,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>register.validation.ageRequired</t>
+          <t>register.validation.confirmPasswordMismatch</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>18+ વર્ષ હોવા જરૂરી છે</t>
+          <t>પાસવર્ડ મેળ ખાતા નથી</t>
         </is>
       </c>
     </row>
@@ -2711,12 +2711,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>register.validation.termsRequired</t>
+          <t>register.validation.countryRequired</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>શરતો સ્વીકારવી જરૂરી છે</t>
+          <t>દેશ કોડ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -2728,12 +2728,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>register.validation.showPassword</t>
+          <t>register.validation.mobileNumberRequired</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>પાસવર્ડ બતાવો</t>
+          <t>મોબાઇલ નંબર જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -2745,12 +2745,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>register.validation.hidePassword</t>
+          <t>register.validation.mobileNumberInvalid</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>પાસવર્ડ છુપાવો</t>
+          <t>અમાન્ય નંબર</t>
         </is>
       </c>
     </row>
@@ -2762,12 +2762,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>register.validation.showConfirmPassword</t>
+          <t>register.validation.ageRequired</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>પુષ્ટિ પાસવર્ડ બતાવો</t>
+          <t>18+ વર્ષ હોવા જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -2779,131 +2779,131 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>register.validation.hideConfirmPassword</t>
+          <t>register.validation.termsRequired</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>પુષ્ટિ પાસવર્ડ છુપાવો</t>
+          <t>શરતો સ્વીકારવી જરૂરી છે</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>deviceLogout</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>register.validation.showPassword</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ચેતવણી</t>
+          <t>પાસવર્ડ બતાવો</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>deviceLogout</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>noPermission</t>
+          <t>register.validation.hidePassword</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>આ એક્સેસ કરવાની તમારી પાસે પરવાનગી નથી.</t>
+          <t>પાસવર્ડ છુપાવો</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>deviceLogout</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>sessionExpired</t>
+          <t>register.validation.showConfirmPassword</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>તમારો સત્ર સમાપ્ત થઈ ગયો છે. કૃપા કરીને ફરીથી લૉગ ઇન કરો.</t>
+          <t>પુષ્ટિ પાસવર્ડ બતાવો</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>games</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>noGamesTitle</t>
+          <t>register.validation.hideConfirmPassword</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>કોઈ રમત ઉપલબ્ધ નથી</t>
+          <t>પુષ્ટિ પાસવર્ડ છુપાવો</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>games</t>
+          <t>deviceLogout</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>noGamesDescription</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>કોઈ રમત ઉપલબ્ધ નથી. કૃપા કરીને પાછળથી તપાસો.</t>
+          <t>ચેતવણી</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>games</t>
+          <t>deviceLogout</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>exploreButton</t>
+          <t>noPermission</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>રમતો એક્સ્પ્લોર કરો</t>
+          <t>આ એક્સેસ કરવાની તમારી પાસે પરવાનગી નથી.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>games</t>
+          <t>deviceLogout</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>allGameProviders</t>
+          <t>sessionExpired</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>બધા ગેમ પ્રૉવાઇડર</t>
+          <t>તમારો સત્ર સમાપ્ત થઈ ગયો છે. કૃપા કરીને ફરીથી લૉગ ઇન કરો.</t>
         </is>
       </c>
     </row>
@@ -2915,12 +2915,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>searchGames</t>
+          <t>noGamesTitle</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>રમતો શોધો...</t>
+          <t>કોઈ રમત ઉપલબ્ધ નથી</t>
         </is>
       </c>
     </row>
@@ -2932,12 +2932,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>pleaseWait</t>
+          <t>noGamesDescription</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>કૃપા રાહ જુઓ...</t>
+          <t>કોઈ રમત ઉપલબ્ધ નથી. કૃપા કરીને પાછળથી તપાસો.</t>
         </is>
       </c>
     </row>
@@ -2949,12 +2949,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>searchGamesAriaLabel</t>
+          <t>exploreButton</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>રમતો શોધો</t>
+          <t>રમતો એક્સ્પ્લોર કરો</t>
         </is>
       </c>
     </row>
@@ -2966,12 +2966,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>toasts.fetchDetailsError</t>
+          <t>allGameProviders</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ગેમ વિગત મેળવવામાં નિષ્ફળ.</t>
+          <t>બધા ગેમ પ્રૉવાઇડર</t>
         </is>
       </c>
     </row>
@@ -2983,12 +2983,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>toasts.refreshError</t>
+          <t>searchGames</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>રમતો રિફ્રેશ કરવામાં નિષ્ફળ.</t>
+          <t>રમતો શોધો...</t>
         </is>
       </c>
     </row>
@@ -3000,12 +3000,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>toasts.failedToFetchGame</t>
+          <t>pleaseWait</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ગેમ મેળવવામાં નિષ્ફળ.</t>
+          <t>કૃપા રાહ જુઓ...</t>
         </is>
       </c>
     </row>
@@ -3017,12 +3017,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>toasts.failedToChangeProvider</t>
+          <t>searchGamesAriaLabel</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>પ્રૉવાઇડર બદલવામાં નિષ્ફળ.</t>
+          <t>રમતો શોધો</t>
         </is>
       </c>
     </row>
@@ -3034,80 +3034,80 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>toasts.failedToLoadMoreGames</t>
+          <t>toasts.fetchDetailsError</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>વધુ ગેમ્સ લોડ કરવામાં નિષ્ફળ.</t>
+          <t>ગેમ વિગત મેળવવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>accountSettings</t>
+          <t>games</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>toasts.refreshError</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>એકાઉન્ટ સેટિંગ્સ</t>
+          <t>રમતો રિફ્રેશ કરવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>accountSettings</t>
+          <t>games</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>tabs.depositLimit</t>
+          <t>toasts.failedToFetchGame</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ મર્યાદા</t>
+          <t>ગેમ મેળવવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>accountSettings</t>
+          <t>games</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>tabs.contactPreference</t>
+          <t>toasts.failedToChangeProvider</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>સંપર્ક પ્રાધાન્ય</t>
+          <t>પ્રૉવાઇડર બદલવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>accountSettings</t>
+          <t>games</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>tabs.changePassword</t>
+          <t>toasts.failedToLoadMoreGames</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>પાસવર્ડ બદલો</t>
+          <t>વધુ ગેમ્સ લોડ કરવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>tabs.selfExclusion</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>સ્વ-બાકાત</t>
+          <t>એકાઉન્ટ સેટિંગ્સ</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>tabs.deactivate</t>
+          <t>tabs.depositLimit</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>નિષ્ક્રિય કરો</t>
+          <t>ડિપૉઝિટ મર્યાદા</t>
         </is>
       </c>
     </row>
@@ -3153,12 +3153,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>changePassword.newPasswordPlaceholder</t>
+          <t>tabs.contactPreference</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>નવો પાસવર્ડ દાખલ કરો</t>
+          <t>સંપર્ક પ્રાધાન્ય</t>
         </is>
       </c>
     </row>
@@ -3170,12 +3170,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>changePassword.confirmPasswordPlaceholder</t>
+          <t>tabs.changePassword</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>પુષ્ટિ પાસવર્ડ દાખલ કરો</t>
+          <t>પાસવર્ડ બદલો</t>
         </is>
       </c>
     </row>
@@ -3187,12 +3187,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>changePassword.hint1</t>
+          <t>tabs.selfExclusion</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>પાસવર્ડ 8-16 અક્ષરનો હોવો જોઈએ, જેમાં ઓછામાં ઓછો એક લોઅરકેઝ, એક અપરકેઝ, એક સંખ્યા અને એક વિશેષ અક્ષર હોવો જોઈએ, ખાલી જગ્યા વિના.</t>
+          <t>સ્વ-બાકાત</t>
         </is>
       </c>
     </row>
@@ -3204,12 +3204,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>changePassword.hint2</t>
+          <t>tabs.deactivate</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>નવો પાસવર્ડ અને પુષ્ટિ પાસવર્ડ મેળ ખાવા જોઈએ.</t>
+          <t>નિષ્ક્રિય કરો</t>
         </is>
       </c>
     </row>
@@ -3221,12 +3221,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>changePassword.toastSuccess</t>
+          <t>changePassword.newPasswordPlaceholder</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>પાસવર્ડ સફળતાપૂર્વક અપડેટ થઈ ગયો.</t>
+          <t>નવો પાસવર્ડ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>changePassword.toastError</t>
+          <t>changePassword.confirmPasswordPlaceholder</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>પાસવર્ડ અપડેટ કરવામાં નિષ્ફળ.</t>
+          <t>પુષ્ટિ પાસવર્ડ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -3255,12 +3255,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>changePassword.validation.passwordRequired</t>
+          <t>changePassword.hint1</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>પાસવર્ડ જરૂરી છે</t>
+          <t>પાસવર્ડ 8-16 અક્ષરનો હોવો જોઈએ, જેમાં ઓછામાં ઓછો એક લોઅરકેઝ, એક અપરકેઝ, એક સંખ્યા અને એક વિશેષ અક્ષર હોવો જોઈએ, ખાલી જગ્યા વિના.</t>
         </is>
       </c>
     </row>
@@ -3272,12 +3272,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>changePassword.validation.passwordMinLength</t>
+          <t>changePassword.hint2</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>પાસવર્ડ ઓછામાં ઓછા 8 અક્ષરનો હોવો જોઈએ</t>
+          <t>નવો પાસવર્ડ અને પુષ્ટિ પાસવર્ડ મેળ ખાવા જોઈએ.</t>
         </is>
       </c>
     </row>
@@ -3289,12 +3289,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>changePassword.validation.passwordPattern</t>
+          <t>changePassword.toastSuccess</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>અપરકેઝ, લોઅરકેઝ, સંખ્યા અને વિશેષ અક્ષર સામેલ હોવા જોઈએ</t>
+          <t>પાસવર્ડ સફળતાપૂર્વક અપડેટ થઈ ગયો.</t>
         </is>
       </c>
     </row>
@@ -3306,12 +3306,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>changePassword.validation.confirmRequired</t>
+          <t>changePassword.toastError</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>કૃપા કરીને તમારો પાસવર્ડ ની પુષ્ટિ કરો</t>
+          <t>પાસવર્ડ અપડેટ કરવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
@@ -3323,12 +3323,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>changePassword.validation.confirmMismatch</t>
+          <t>changePassword.validation.passwordRequired</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>પાસવર્ડ મેળ ખાતા નથી</t>
+          <t>પાસવર્ડ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -3340,12 +3340,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>contactPreference.labels.all</t>
+          <t>changePassword.validation.passwordMinLength</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>બધા</t>
+          <t>પાસવર્ડ ઓછામાં ઓછા 8 અક્ષરનો હોવો જોઈએ</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>contactPreference.labels.email</t>
+          <t>changePassword.validation.passwordPattern</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>ઇ-મેઇલ</t>
+          <t>અપરકેઝ, લોઅરકેઝ, સંખ્યા અને વિશેષ અક્ષર સામેલ હોવા જોઈએ</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>contactPreference.labels.whatsapp</t>
+          <t>changePassword.validation.confirmRequired</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>કૃપા કરીને તમારો પાસવર્ડ ની પુષ્ટિ કરો</t>
         </is>
       </c>
     </row>
@@ -3391,12 +3391,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>contactPreference.labels.telegram</t>
+          <t>changePassword.validation.confirmMismatch</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>પાસવર્ડ મેળ ખાતા નથી</t>
         </is>
       </c>
     </row>
@@ -3408,12 +3408,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>contactPreference.labels.sms</t>
+          <t>contactPreference.labels.all</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>SMS</t>
+          <t>બધા</t>
         </is>
       </c>
     </row>
@@ -3425,12 +3425,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>contactPreference.labels.call</t>
+          <t>contactPreference.labels.email</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>કૉલ</t>
+          <t>ઇ-મેઇલ</t>
         </is>
       </c>
     </row>
@@ -3442,12 +3442,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>contactPreference.labels.none</t>
+          <t>contactPreference.labels.whatsapp</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>કોઈ નહીં</t>
+          <t>WhatsApp</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>contactPreference.toastSuccess</t>
+          <t>contactPreference.labels.telegram</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>સંપર્ક સેટિંગ્સ સફળતાપૂર્વક અપડેટ થઈ.</t>
+          <t>Telegram</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>contactPreference.toastError</t>
+          <t>contactPreference.labels.sms</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>સંપર્ક સેટિંગ્સ અપડેટ કરવામાં નિષ્ફળ.</t>
+          <t>SMS</t>
         </is>
       </c>
     </row>
@@ -3493,12 +3493,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>depositLimit.dailyLabel</t>
+          <t>contactPreference.labels.call</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>દૈનિક ડિપૉઝિટ મર્યાદા</t>
+          <t>કૉલ</t>
         </is>
       </c>
     </row>
@@ -3510,12 +3510,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>depositLimit.weeklyLabel</t>
+          <t>contactPreference.labels.none</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>સાપ્તાહિક ડિપૉઝિટ મર્યાદા</t>
+          <t>કોઈ નહીં</t>
         </is>
       </c>
     </row>
@@ -3527,12 +3527,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>depositLimit.monthlyLabel</t>
+          <t>contactPreference.toastSuccess</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>માસિક ડિપૉઝિટ મર્યાદા</t>
+          <t>સંપર્ક સેટિંગ્સ સફળતાપૂર્વક અપડેટ થઈ.</t>
         </is>
       </c>
     </row>
@@ -3544,12 +3544,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>depositLimit.hint1</t>
+          <t>contactPreference.toastError</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ મર્યાદા સક્ષમ કરવાથી વપરાશકર્તા ચોક્કસ સમયગાળા માટે ડિપૉઝિટ કરવાથી પ્રતિબંધિત થઈ શકે છે. એકવાર મર્યાદા સેટ થઈ ગઈ, ત્યારે નિર્ધારિત સમય સમાપ્ત ન થાય ત્યાં સુધી વપરાશકર્તા કોઈ ડિપૉઝિટ કરી શકશે નહીં.</t>
+          <t>સંપર્ક સેટિંગ્સ અપડેટ કરવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
@@ -3561,12 +3561,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>depositLimit.hint2</t>
+          <t>depositLimit.dailyLabel</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>જો તમે આ ડિપૉઝિટ મર્યાદા લાગુ કરવા ઇચ્છો, તો સમયગાળો અને જે રકમ ઓળંગવી ન ઇચ્છો તે પસંદ કરી શકો છો.</t>
+          <t>દૈનિક ડિપૉઝિટ મર્યાદા</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>depositLimit.toastSuccess</t>
+          <t>depositLimit.weeklyLabel</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ મર્યાદા સફળતાપૂર્વક અપડેટ થઈ.</t>
+          <t>સાપ્તાહિક ડિપૉઝિટ મર્યાદા</t>
         </is>
       </c>
     </row>
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>depositLimit.toastError</t>
+          <t>depositLimit.monthlyLabel</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ મર્યાદા અપડેટ કરવામાં નિષ્ફળ.</t>
+          <t>માસિક ડિપૉઝિટ મર્યાદા</t>
         </is>
       </c>
     </row>
@@ -3612,12 +3612,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>depositLimit.validation.dailyExceedsWeeklyOrMonthly</t>
+          <t>depositLimit.hint1</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>દૈનિક મર્યાદા સાપ્તાહિક અથવા માસિક મર્યાદા કરતાં વધારે ન હોઈ શકે.</t>
+          <t>ડિપૉઝિટ મર્યાદા સક્ષમ કરવાથી વપરાશકર્તા ચોક્કસ સમયગાળા માટે ડિપૉઝિટ કરવાથી પ્રતિબંધિત થઈ શકે છે. એકવાર મર્યાદા સેટ થઈ ગઈ, ત્યારે નિર્ધારિત સમય સમાપ્ત ન થાય ત્યાં સુધી વપરાશકર્તા કોઈ ડિપૉઝિટ કરી શકશે નહીં.</t>
         </is>
       </c>
     </row>
@@ -3629,12 +3629,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>depositLimit.validation.weeklyOutOfRange</t>
+          <t>depositLimit.hint2</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>સાપ્તાહિક મર્યાદા દૈનિક અને માસિક મર્યાદાની વચ્ચે હોવી જોઈએ.</t>
+          <t>જો તમે આ ડિપૉઝિટ મર્યાદા લાગુ કરવા ઇચ્છો, તો સમયગાળો અને જે રકમ ઓળંગવી ન ઇચ્છો તે પસંદ કરી શકો છો.</t>
         </is>
       </c>
     </row>
@@ -3646,12 +3646,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>depositLimit.validation.monthlyTooSmall</t>
+          <t>depositLimit.toastSuccess</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>માસિક મર્યાદા દૈનિક અથવા સાપ્તાહિક મર્યાદા કરતાં નાની ન હોઈ શકે.</t>
+          <t>ડિપૉઝિટ મર્યાદા સફળતાપૂર્વક અપડેટ થઈ.</t>
         </is>
       </c>
     </row>
@@ -3663,12 +3663,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>selfExclusion.checkboxLabel</t>
+          <t>depositLimit.toastError</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>હું મારા ખાતાને આ સમય માટે સ્વ-બાકાત કરવા ઇચ્છું છું:</t>
+          <t>ડિપૉઝિટ મર્યાદા અપડેટ કરવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>selfExclusion.selectPlaceholder</t>
+          <t>depositLimit.validation.dailyExceedsWeeklyOrMonthly</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>સમયગાળો પસંદ કરો</t>
+          <t>દૈનિક મર્યાદા સાપ્તાહિક અથવા માસિક મર્યાદા કરતાં વધારે ન હોઈ શકે.</t>
         </is>
       </c>
     </row>
@@ -3697,12 +3697,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>selfExclusion.toastSuccess</t>
+          <t>depositLimit.validation.weeklyOutOfRange</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>તમારું ખાતું {{timePeriod}} માટે સ્વ-બાકાત કરવામાં આવ્યું છે.</t>
+          <t>સાપ્તાહિક મર્યાદા દૈનિક અને માસિક મર્યાદાની વચ્ચે હોવી જોઈએ.</t>
         </is>
       </c>
     </row>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>selfExclusion.hint</t>
+          <t>depositLimit.validation.monthlyTooSmall</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>આ સમયગાળા દરમિયાન તમે વેબસાઇટ પર રમી નહીં શકો અને કોઈ માર્કેટિંગ ઇ-મેઇલ અથવા પ્રોમોશન પ્રાપ્ત નહીં થાય.</t>
+          <t>માસિક મર્યાદા દૈનિક અથવા સાપ્તાહિક મર્યાદા કરતાં નાની ન હોઈ શકે.</t>
         </is>
       </c>
     </row>
@@ -3731,12 +3731,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>selfExclusion.confirmText</t>
+          <t>selfExclusion.checkboxLabel</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>શું તમે ખરેખર {{timePeriod}} માટે તમારા ખાતાને સ્વ-બાકાત કરવા ઇચ્છો છો?</t>
+          <t>હું મારા ખાતાને આ સમય માટે સ્વ-બાકાત કરવા ઇચ્છું છું:</t>
         </is>
       </c>
     </row>
@@ -3748,12 +3748,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>selfExclusion.periods.1 day</t>
+          <t>selfExclusion.selectPlaceholder</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>1 દિવસ</t>
+          <t>સમયગાળો પસંદ કરો</t>
         </is>
       </c>
     </row>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>selfExclusion.periods.1 week</t>
+          <t>selfExclusion.toastSuccess</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>1 અઠવાડિયું</t>
+          <t>તમારું ખાતું {{timePeriod}} માટે સ્વ-બાકાત કરવામાં આવ્યું છે.</t>
         </is>
       </c>
     </row>
@@ -3782,12 +3782,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>selfExclusion.periods.1 month</t>
+          <t>selfExclusion.hint</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>1 મહિનો</t>
+          <t>આ સમયગાળા દરમિયાન તમે વેબસાઇટ પર રમી નહીં શકો અને કોઈ માર્કેટિંગ ઇ-મેઇલ અથવા પ્રોમોશન પ્રાપ્ત નહીં થાય.</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>selfExclusion.periods.6 weeks</t>
+          <t>selfExclusion.confirmText</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>6 અઠવાડિયા</t>
+          <t>શું તમે ખરેખર {{timePeriod}} માટે તમારા ખાતાને સ્વ-બાકાત કરવા ઇચ્છો છો?</t>
         </is>
       </c>
     </row>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>selfExclusion.periods.undetermined</t>
+          <t>selfExclusion.periods.1 day</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>અનિર્ધારિત</t>
+          <t>1 દિવસ</t>
         </is>
       </c>
     </row>
@@ -3833,12 +3833,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>deactivate.checkboxLabel</t>
+          <t>selfExclusion.periods.1 week</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>હું મારા ખાતાને આ સમય માટે સ્વ-બાકાત કરવા ઇચ્છું છું:</t>
+          <t>1 અઠવાડિયું</t>
         </is>
       </c>
     </row>
@@ -3850,12 +3850,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>deactivate.selectPlaceholder</t>
+          <t>selfExclusion.periods.1 month</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>સમયગાળો પસંદ કરો</t>
+          <t>1 મહિનો</t>
         </is>
       </c>
     </row>
@@ -3867,12 +3867,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>deactivate.hint</t>
+          <t>selfExclusion.periods.6 weeks</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>આ સમય દરમિયાન તમે તમારા ખાતામાં સાઇન ઇન કરી નહીં શકો અથવા અસાધારણ સંજોગો સિવાય ખાતું ફરી સક્ષમ નહીં કરી શકો. નિષ્ક્રિય સમય સમાપ્ત થયા પછી, તમને સ્ટ્રેચ ઑપ્શન આપવામાં આવશે. બધા ફૉન્ડ્સ પ્રત્યાર્પણ કરવામાં આવશે અને બધા દાવ રદ્દ ગણાશે.</t>
+          <t>6 અઠવાડિયા</t>
         </is>
       </c>
     </row>
@@ -3884,12 +3884,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>deactivate.toastSuccess</t>
+          <t>selfExclusion.periods.undetermined</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>નિષ્ક્રિય સ્ટેટ સફળતાપૂર્વક અપડેટ થઈ.</t>
+          <t>અનિર્ધારિત</t>
         </is>
       </c>
     </row>
@@ -3901,80 +3901,80 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>deactivate.toastError</t>
+          <t>deactivate.checkboxLabel</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>ખાતું નિષ્ક્રિય કરવામાં નિષ્ફળ.</t>
+          <t>હું મારા ખાતાને આ સમય માટે સ્વ-બાકાત કરવા ઇચ્છું છું:</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>deposit</t>
+          <t>accountSettings</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>deactivate.selectPlaceholder</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ</t>
+          <t>સમયગાળો પસંદ કરો</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>deposit</t>
+          <t>accountSettings</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>selectAmount</t>
+          <t>deactivate.hint</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>રકમ પસંદ કરો</t>
+          <t>આ સમય દરમિયાન તમે તમારા ખાતામાં સાઇન ઇન કરી નહીં શકો અથવા અસાધારણ સંજોગો સિવાય ખાતું ફરી સક્ષમ નહીં કરી શકો. નિષ્ક્રિય સમય સમાપ્ત થયા પછી, તમને સ્ટ્રેચ ઑપ્શન આપવામાં આવશે. બધા ફૉન્ડ્સ પ્રત્યાર્પણ કરવામાં આવશે અને બધા દાવ રદ્દ ગણાશે.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>deposit</t>
+          <t>accountSettings</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>helpText</t>
+          <t>deactivate.toastSuccess</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>મદદ જોઈએ? ડિપૉઝિટ માર્ગદર્શિકા જુઓ અથવા અમને લાઇવ ચૅટ / ઇ-મેઇલ પર સંપર્ક કરો.</t>
+          <t>નિષ્ક્રિય સ્ટેટ સફળતાપૂર્વક અપડેટ થઈ.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>deposit</t>
+          <t>accountSettings</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>enterAmount</t>
+          <t>deactivate.toastError</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>રકમ દાખલ કરો</t>
+          <t>ખાતું નિષ્ક્રિય કરવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
@@ -3986,12 +3986,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>bonusCode</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>બોનસ કોડ</t>
+          <t>ડિપૉઝિટ</t>
         </is>
       </c>
     </row>
@@ -4003,12 +4003,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>bonusCodePlaceholder</t>
+          <t>selectAmount</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>બોનસ કોડ દાખલ કરો</t>
+          <t>રકમ પસંદ કરો</t>
         </is>
       </c>
     </row>
@@ -4020,12 +4020,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>bankLimitText</t>
+          <t>helpText</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>બૅન્ક મર્યાદા : ₹{{limit}}</t>
+          <t>મદદ જોઈએ? ડિપૉઝિટ માર્ગદર્શિકા જુઓ અથવા અમને લાઇવ ચૅટ / ઇ-મેઇલ પર સંપર્ક કરો.</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>paymentMethods.bank</t>
+          <t>enterAmount</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>બૅન્ક ટ્રાન્સફર</t>
+          <t>રકમ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>paymentMethods.qr</t>
+          <t>bonusCode</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>QR ટ્રાન્સફર</t>
+          <t>બોનસ કોડ</t>
         </is>
       </c>
     </row>
@@ -4071,12 +4071,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>paymentMethods.upi</t>
+          <t>bonusCodePlaceholder</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>UPI</t>
+          <t>બોનસ કોડ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -4088,12 +4088,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>paymentMethods.azeePay</t>
+          <t>bankLimitText</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Azee Pay</t>
+          <t>બૅન્ક મર્યાદા : ₹{{limit}}</t>
         </is>
       </c>
     </row>
@@ -4105,12 +4105,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>azeePayAlt</t>
+          <t>paymentMethods.bank</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>azee-pay</t>
+          <t>બૅન્ક ટ્રાન્સફર</t>
         </is>
       </c>
     </row>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>toastSuccess</t>
+          <t>paymentMethods.qr</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ સફળ.</t>
+          <t>QR ટ્રાન્સફર</t>
         </is>
       </c>
     </row>
@@ -4139,12 +4139,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>paymentDetailsTitle</t>
+          <t>paymentMethods.upi</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>તમારી ચુકવણી વિગત</t>
+          <t>UPI</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>enterUtr</t>
+          <t>paymentMethods.azeePay</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>UTR નંબર દાખલ કરો</t>
+          <t>Azee Pay</t>
         </is>
       </c>
     </row>
@@ -4173,12 +4173,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>whatsappCta</t>
+          <t>azeePayAlt</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ માટે WhatsApp કરો</t>
+          <t>azee-pay</t>
         </is>
       </c>
     </row>
@@ -4190,12 +4190,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>transferDetails</t>
+          <t>toastSuccess</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>ટ્રાન્સફર વિગત</t>
+          <t>ડિપૉઝિટ સફળ.</t>
         </is>
       </c>
     </row>
@@ -4207,12 +4207,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>previousPromotion</t>
+          <t>paymentDetailsTitle</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>પહેલાનું પ્રોમોશન</t>
+          <t>તમારી ચુકવણી વિગત</t>
         </is>
       </c>
     </row>
@@ -4224,12 +4224,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>nextPromotion</t>
+          <t>enterUtr</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>આગળનું પ્રોમોશન</t>
+          <t>UTR નંબર દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4241,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>qrCodeAlt</t>
+          <t>whatsappCta</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>QR કોડ</t>
+          <t>ડિપૉઝિટ માટે WhatsApp કરો</t>
         </is>
       </c>
     </row>
@@ -4258,12 +4258,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>transferLabels.qrCode</t>
+          <t>transferDetails</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>QR કોડ</t>
+          <t>ટ્રાન્સફર વિગત</t>
         </is>
       </c>
     </row>
@@ -4275,12 +4275,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>transferLabels.qrName</t>
+          <t>previousPromotion</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>QR નામ</t>
+          <t>પહેલાનું પ્રોમોશન</t>
         </is>
       </c>
     </row>
@@ -4292,12 +4292,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>transferLabels.id</t>
+          <t>nextPromotion</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>આગળનું પ્રોમોશન</t>
         </is>
       </c>
     </row>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>transferLabels.upiId</t>
+          <t>qrCodeAlt</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>UPI ID</t>
+          <t>QR કોડ</t>
         </is>
       </c>
     </row>
@@ -4326,12 +4326,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>transferLabels.upiName</t>
+          <t>transferLabels.qrCode</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>UPI નામ</t>
+          <t>QR કોડ</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>transferLabels.paymentUpiName</t>
+          <t>transferLabels.qrName</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>ચુકવણી UPI નામ</t>
+          <t>QR નામ</t>
         </is>
       </c>
     </row>
@@ -4360,12 +4360,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>transferLabels.bankName</t>
+          <t>transferLabels.id</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>બૅન્ક નામ</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
@@ -4377,12 +4377,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>transferLabels.accountHolderName</t>
+          <t>transferLabels.upiId</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>ખાતા ધારકનું નામ</t>
+          <t>UPI ID</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>transferLabels.accountNumber</t>
+          <t>transferLabels.upiName</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>ખાતા નંબર</t>
+          <t>UPI નામ</t>
         </is>
       </c>
     </row>
@@ -4411,12 +4411,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>transferLabels.accountType</t>
+          <t>transferLabels.paymentUpiName</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>ખાતા પ્રકાર</t>
+          <t>ચુકવણી UPI નામ</t>
         </is>
       </c>
     </row>
@@ -4428,12 +4428,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>transferLabels.ifscCode</t>
+          <t>transferLabels.bankName</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>IFSC કોડ</t>
+          <t>બૅન્ક નામ</t>
         </is>
       </c>
     </row>
@@ -4445,12 +4445,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>transferLabels.branch</t>
+          <t>transferLabels.accountHolderName</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>શાખા</t>
+          <t>ખાતા ધારકનું નામ</t>
         </is>
       </c>
     </row>
@@ -4462,12 +4462,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>campaign.title</t>
+          <t>transferLabels.accountNumber</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>પ્રોમોશન્સ</t>
+          <t>ખાતા નંબર</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>campaign.giftAlt</t>
+          <t>transferLabels.accountType</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>ભેટ</t>
+          <t>ખાતા પ્રકાર</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4496,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>campaign.minDepositLimitLabel</t>
+          <t>transferLabels.ifscCode</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>ન્યૂનતમ ડિપૉઝિટ મર્યાદા: ₹{{limit}}</t>
+          <t>IFSC કોડ</t>
         </is>
       </c>
     </row>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>campaign.claimUntil</t>
+          <t>transferLabels.branch</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>ક્લેઇમ ક્યાં સુધી: {{date}}</t>
+          <t>શાખા</t>
         </is>
       </c>
     </row>
@@ -4530,12 +4530,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>campaign.applyCode</t>
+          <t>campaign.title</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>કોડ લાગુ કરો</t>
+          <t>પ્રોમોશન્સ</t>
         </is>
       </c>
     </row>
@@ -4547,12 +4547,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>campaign.noContent</t>
+          <t>campaign.giftAlt</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>કોઈ સામગ્રી ઉપલબ્ધ નથી</t>
+          <t>ભેટ</t>
         </is>
       </c>
     </row>
@@ -4564,12 +4564,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>psp.paymentVerifying</t>
+          <t>campaign.minDepositLimitLabel</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>ચુકવણી ચકાસાઈ રહી છે…</t>
+          <t>ન્યૂનતમ ડિપૉઝિટ મર્યાદા: ₹{{limit}}</t>
         </is>
       </c>
     </row>
@@ -4581,12 +4581,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>psp.continueToPay</t>
+          <t>campaign.claimUntil</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>ચુકવણી ચાલુ રાખો</t>
+          <t>ક્લેઇમ ક્યાં સુધી: {{date}}</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>psp.toastSuccess</t>
+          <t>campaign.applyCode</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ સફળતાપૂર્વક પ્રક્રિયા થઈ</t>
+          <t>કોડ લાગુ કરો</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>psp.toastProcessedCheckSupport</t>
+          <t>campaign.noContent</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ પ્રક્રિયા થઈ. કૃપા કરીને સહાય ટીમ સાથે ચકાસો</t>
+          <t>કોઈ સામગ્રી ઉપલબ્ધ નથી</t>
         </is>
       </c>
     </row>
@@ -4632,12 +4632,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>psp.toastUnableToVerify</t>
+          <t>psp.paymentVerifying</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>ચુકવણી ચકાસી શકાઈ નહીં</t>
+          <t>ચુકવણી ચકાસાઈ રહી છે…</t>
         </is>
       </c>
     </row>
@@ -4649,12 +4649,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>psp.toastVerifyingPayment</t>
+          <t>psp.continueToPay</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>ચુકવણી ચકાસી રહ્યા છીએ...</t>
+          <t>ચુકવણી ચાલુ રાખો</t>
         </is>
       </c>
     </row>
@@ -4666,12 +4666,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>psp.toastSomethingWentWrong</t>
+          <t>psp.toastSuccess</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>કંઈક ખોટું થયું</t>
+          <t>ડિપૉઝિટ સફળતાપૂર્વક પ્રક્રિયા થઈ</t>
         </is>
       </c>
     </row>
@@ -4683,12 +4683,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>validation.toastAmountGreaterThanZero</t>
+          <t>psp.toastProcessedCheckSupport</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>રકમ 0 કરતાં વધારે હોવી જોઈએ</t>
+          <t>ડિપૉઝિટ પ્રક્રિયા થઈ. કૃપા કરીને સહાય ટીમ સાથે ચકાસો</t>
         </is>
       </c>
     </row>
@@ -4700,12 +4700,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>validation.amountExceedsLimit</t>
+          <t>psp.toastUnableToVerify</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>રકમ ₹{{limit}} ની મર્યાદા કરતાં વધી ગઈ</t>
+          <t>ચુકવણી ચકાસી શકાઈ નહીં</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>validation.minDepositRequired</t>
+          <t>psp.toastVerifyingPayment</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>ઓછામાં ઓછી {{min}} ની ડિપૉઝિટ જરૂરી છે</t>
+          <t>ચુકવણી ચકાસી રહ્યા છીએ...</t>
         </is>
       </c>
     </row>
@@ -4734,80 +4734,80 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>validation.toastUtrRequired</t>
+          <t>psp.toastSomethingWentWrong</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>કૃપા કરીને UTR નંબર દાખલ કરો</t>
+          <t>કંઈક ખોટું થયું</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>withdraw</t>
+          <t>deposit</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>validation.toastAmountGreaterThanZero</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>ઉપાડ</t>
+          <t>રકમ 0 કરતાં વધારે હોવી જોઈએ</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>withdraw</t>
+          <t>deposit</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>withdrawableMoney</t>
+          <t>validation.amountExceedsLimit</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>ઉપાડ બૅલૅન્સ</t>
+          <t>રકમ ₹{{limit}} ની મર્યાદા કરતાં વધી ગઈ</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>withdraw</t>
+          <t>deposit</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>selectBankPlaceholder</t>
+          <t>validation.minDepositRequired</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>બૅન્ક ખાતું પસંદ કરો</t>
+          <t>ઓછામાં ઓછી {{min}} ની ડિપૉઝિટ જરૂરી છે</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>withdraw</t>
+          <t>deposit</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>enterAmountPlaceholder</t>
+          <t>validation.toastUtrRequired</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>રકમ દાખલ કરો</t>
+          <t>કૃપા કરીને UTR નંબર દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -4819,12 +4819,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>whatsappCta</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>WhatsApp દ્વારા ઉપાડ</t>
+          <t>ઉપાડ</t>
         </is>
       </c>
     </row>
@@ -4836,12 +4836,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>withdrawableMoney</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>ઉપાડ કરો</t>
+          <t>ઉપાડ બૅલૅન્સ</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>submitting</t>
+          <t>selectBankPlaceholder</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>ઉપાડ થઈ રહ્યો છે…</t>
+          <t>બૅન્ક ખાતું પસંદ કરો</t>
         </is>
       </c>
     </row>
@@ -4870,12 +4870,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>validation.bankRequired</t>
+          <t>enterAmountPlaceholder</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>બૅન્ક ખાતું પસંદ કરો</t>
+          <t>રકમ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -4887,12 +4887,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>validation.amountRequired</t>
+          <t>whatsappCta</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>રકમ જરૂરી છે</t>
+          <t>WhatsApp દ્વારા ઉપાડ</t>
         </is>
       </c>
     </row>
@@ -4904,12 +4904,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>validation.amountNumbersOnly</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>રકમ ફક્ત સંખ્યા ધરાવવી જોઈએ</t>
+          <t>ઉપાડ કરો</t>
         </is>
       </c>
     </row>
@@ -4921,12 +4921,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>validation.amountExceedsMax</t>
+          <t>submitting</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>તમે મહત્તમ ₹{{max}} ઉપાડ કરી શકો છો</t>
+          <t>ઉપાડ થઈ રહ્યો છે…</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>validation.amountMinimum</t>
+          <t>validation.bankRequired</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>રકમ ₹500 કરતાં વધારે હોવી જોઈએ</t>
+          <t>બૅન્ક ખાતું પસંદ કરો</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>toasts.success</t>
+          <t>validation.amountRequired</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>રકમ સફળતાપૂર્વક ઉપાડવામાં આવી.</t>
+          <t>રકમ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -4972,87 +4972,87 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>toasts.error</t>
+          <t>validation.amountNumbersOnly</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>ઉપાડ પ્રક્રિયા કરવામાં નિષ્ફળ.</t>
+          <t>રકમ ફક્ત સંખ્યા ધરાવવી જોઈએ</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>wallet</t>
+          <t>withdraw</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>validation.amountExceedsMax</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>વૉલેટ</t>
+          <t>તમે મહત્તમ ₹{{max}} ઉપાડ કરી શકો છો</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>wallet</t>
+          <t>withdraw</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>realMoney</t>
+          <t>validation.amountMinimum</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>રિઅલ મની ₹ {{amount}}</t>
+          <t>રકમ ₹500 કરતાં વધારે હોવી જોઈએ</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>wallet</t>
+          <t>withdraw</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>withdrawableMoney</t>
+          <t>toasts.success</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>ઉપાડ યોગ્ય મની ₹ {{amount}}</t>
+          <t>રકમ સફળતાપૂર્વક ઉપાડવામાં આવી.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>wallet</t>
+          <t>withdraw</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>moneySuffix</t>
+          <t>toasts.error</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>{{wallet}} મની</t>
+          <t>ઉપાડ પ્રક્રિયા કરવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>bonus</t>
+          <t>wallet</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -5062,58 +5062,58 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>બોનસ</t>
+          <t>વૉલેટ</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>bonus</t>
+          <t>wallet</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>tabs.active</t>
+          <t>realMoney</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>સક્રિય બોનસ</t>
+          <t>રિઅલ મની ₹ {{amount}}</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>bonus</t>
+          <t>wallet</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>tabs.unclaimed</t>
+          <t>withdrawableMoney</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>ક્લૅઇમ ન કરેલો બોનસ</t>
+          <t>ઉપાડ યોગ્ય મની ₹ {{amount}}</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>bonus</t>
+          <t>wallet</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>tabs.redeemed</t>
+          <t>moneySuffix</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>રિડીમ કરેલો બોનસ</t>
+          <t>{{wallet}} મની</t>
         </is>
       </c>
     </row>
@@ -5125,12 +5125,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>toastExpired</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>કૅમ્પેઇન સમય સમાપ્ત</t>
+          <t>બોનસ</t>
         </is>
       </c>
     </row>
@@ -5142,12 +5142,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>toastError</t>
+          <t>tabs.active</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>કૅમ્પેઇન સમાપ્ત કરવામાં નિષ્ફળ.</t>
+          <t>સક્રિય બોનસ</t>
         </is>
       </c>
     </row>
@@ -5159,12 +5159,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>noCampaigns</t>
+          <t>tabs.unclaimed</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>કોઈ કૅમ્પેઇન ઉપલબ્ધ નથી. કૃપા કરીને પાછળથી તપાસો.</t>
+          <t>ક્લૅઇમ ન કરેલો બોનસ</t>
         </is>
       </c>
     </row>
@@ -5176,12 +5176,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>campaignName</t>
+          <t>tabs.redeemed</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>કૅમ્પેઇન નામ</t>
+          <t>રિડીમ કરેલો બોનસ</t>
         </is>
       </c>
     </row>
@@ -5193,12 +5193,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>campaignCode</t>
+          <t>toastExpired</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>કૅમ્પેઇન કોડ</t>
+          <t>કૅમ્પેઇન સમય સમાપ્ત</t>
         </is>
       </c>
     </row>
@@ -5210,12 +5210,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>minOdds</t>
+          <t>toastError</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>ન્યૂનતમ ઑડ્ઝ</t>
+          <t>કૅમ્પેઇન સમાપ્ત કરવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
@@ -5227,12 +5227,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>bonusAmount</t>
+          <t>noCampaigns</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>બોનસ રકમ</t>
+          <t>કોઈ કૅમ્પેઇન ઉપલબ્ધ નથી. કૃપા કરીને પાછળથી તપાસો.</t>
         </is>
       </c>
     </row>
@@ -5244,12 +5244,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>bonusPercentage</t>
+          <t>campaignName</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>બોનસ ટકાવારી</t>
+          <t>કૅમ્પેઇન નામ</t>
         </is>
       </c>
     </row>
@@ -5261,12 +5261,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>campaignCode</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>ચેતવણી</t>
+          <t>કૅમ્પેઇન કોડ</t>
         </is>
       </c>
     </row>
@@ -5278,80 +5278,80 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>cancelConfirm</t>
+          <t>minOdds</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>શું તમે ખરેખર બોનસ રદ કરવા ઇચ્છો છો?</t>
+          <t>ન્યૂનતમ ઑડ્ઝ</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>kyc</t>
+          <t>bonus</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>bonusAmount</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>KYC</t>
+          <t>બોનસ રકમ</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>kyc</t>
+          <t>bonus</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>subtitle</t>
+          <t>bonusPercentage</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>KYC અપડેટ કરો</t>
+          <t>બોનસ ટકાવારી</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>kyc</t>
+          <t>bonus</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>documentTypeLabel</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>દસ્તાવેજ પ્રકાર</t>
+          <t>ચેતવણી</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>kyc</t>
+          <t>bonus</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>documentNumberLabel</t>
+          <t>cancelConfirm</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>દસ્તાવેજ નંબર</t>
+          <t>શું તમે ખરેખર બોનસ રદ કરવા ઇચ્છો છો?</t>
         </is>
       </c>
     </row>
@@ -5363,12 +5363,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>documentTypePlaceholder</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>દસ્તાવેજ પ્રકાર દાખલ કરો</t>
+          <t>KYC</t>
         </is>
       </c>
     </row>
@@ -5380,12 +5380,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>documentNumberPlaceholder</t>
+          <t>subtitle</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>દસ્તાવેજ નંબર દાખલ કરો</t>
+          <t>KYC અપડેટ કરો</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>frontImageLabel</t>
+          <t>documentTypeLabel</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>આગળની છબી</t>
+          <t>દસ્તાવેજ પ્રકાર</t>
         </is>
       </c>
     </row>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>backImageLabel</t>
+          <t>documentNumberLabel</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>પાછળની છબી</t>
+          <t>દસ્તાવેજ નંબર</t>
         </is>
       </c>
     </row>
@@ -5431,12 +5431,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>save</t>
+          <t>documentTypePlaceholder</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>સાચવો</t>
+          <t>દસ્તાવેજ પ્રકાર દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -5448,12 +5448,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>saving</t>
+          <t>documentNumberPlaceholder</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>સાચવી રહ્યા છીએ…</t>
+          <t>દસ્તાવેજ નંબર દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -5465,12 +5465,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>toastSuccess</t>
+          <t>frontImageLabel</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>KYC સફળતાપૂર્વક અપડેટ થઈ.</t>
+          <t>આગળની છબી</t>
         </is>
       </c>
     </row>
@@ -5482,12 +5482,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>toastError</t>
+          <t>backImageLabel</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>KYC અપડેટ કરવામાં નિષ્ફળ.</t>
+          <t>પાછળની છબી</t>
         </is>
       </c>
     </row>
@@ -5499,12 +5499,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>toastAlreadyVerified</t>
+          <t>save</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>KYC પહેલેથી ચકાસાઈ ગઈ છે</t>
+          <t>સાચવો</t>
         </is>
       </c>
     </row>
@@ -5516,12 +5516,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>toastPending</t>
+          <t>saving</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>KYC સ્ટેટ્સ પ્રતીક્ષારત છે</t>
+          <t>સાચવી રહ્યા છીએ…</t>
         </is>
       </c>
     </row>
@@ -5533,12 +5533,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>toastRejected</t>
+          <t>toastSuccess</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>KYC નકારી કઢાઈ</t>
+          <t>KYC સફળતાપૂર્વક અપડેટ થઈ.</t>
         </is>
       </c>
     </row>
@@ -5550,12 +5550,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>validation.documentTypeRequired</t>
+          <t>toastError</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>કૃપા કરીને દસ્તાવેજ પ્રકાર પસંદ કરો</t>
+          <t>KYC અપડેટ કરવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
@@ -5567,12 +5567,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>validation.documentNumberRequired</t>
+          <t>toastAlreadyVerified</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>કૃપા કરીને તમારો દસ્તાવેજ નંબર દાખલ કરો</t>
+          <t>KYC પહેલેથી ચકાસાઈ ગઈ છે</t>
         </is>
       </c>
     </row>
@@ -5584,12 +5584,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>validation.aadharInvalid</t>
+          <t>toastPending</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>માન્ય 12-અંકનો આધાર નંબર દાખલ કરો</t>
+          <t>KYC સ્ટેટ્સ પ્રતીક્ષારત છે</t>
         </is>
       </c>
     </row>
@@ -5601,12 +5601,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>validation.panInvalid</t>
+          <t>toastRejected</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>માન્ય PAN નંબર દાખલ કરો</t>
+          <t>KYC નકારી કઢાઈ</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>validation.frontImageRequired</t>
+          <t>validation.documentTypeRequired</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>આગળની છબી જરૂરી છે</t>
+          <t>કૃપા કરીને દસ્તાવેજ પ્રકાર પસંદ કરો</t>
         </is>
       </c>
     </row>
@@ -5635,80 +5635,80 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>validation.backImageRequired</t>
+          <t>validation.documentNumberRequired</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>પાછળની છબી જરૂરી છે</t>
+          <t>કૃપા કરીને તમારો દસ્તાવેજ નંબર દાખલ કરો</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>kyc</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>validation.aadharInvalid</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>પ્રૉફાઇલ</t>
+          <t>માન્ય 12-અંકનો આધાર નંબર દાખલ કરો</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>kyc</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>yourPersonalData</t>
+          <t>validation.panInvalid</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>તમારો વ્યક્તિગત ડેટા</t>
+          <t>માન્ય PAN નંબર દાખલ કરો</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>kyc</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>updatePersonalData</t>
+          <t>validation.frontImageRequired</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>વ્યક્તિગત વિગત અપડેટ કરો</t>
+          <t>આગળની છબી જરૂરી છે</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>kyc</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>fields.firstName</t>
+          <t>validation.backImageRequired</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>પ્રથમ નામ</t>
+          <t>પાછળની છબી જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -5720,12 +5720,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>fields.lastName</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>છેલ્લું નામ</t>
+          <t>પ્રૉફાઇલ</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>fields.userName</t>
+          <t>yourPersonalData</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>વપરાશકર્તા નામ</t>
+          <t>તમારો વ્યક્તિગત ડેટા</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>fields.email</t>
+          <t>updatePersonalData</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>ઇ-મેઇલ</t>
+          <t>વ્યક્તિગત વિગત અપડેટ કરો</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>fields.dateOfBirth</t>
+          <t>fields.firstName</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>જન્મ તારીખ</t>
+          <t>પ્રથમ નામ</t>
         </is>
       </c>
     </row>
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>fields.city</t>
+          <t>fields.lastName</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>શહેર</t>
+          <t>છેલ્લું નામ</t>
         </is>
       </c>
     </row>
@@ -5805,12 +5805,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>fields.country</t>
+          <t>fields.userName</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>દેશ</t>
+          <t>વપરાશકર્તા નામ</t>
         </is>
       </c>
     </row>
@@ -5822,12 +5822,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>fields.state</t>
+          <t>fields.email</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>રાજ્ય</t>
+          <t>ઇ-મેઇલ</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>fields.countryCode</t>
+          <t>fields.dateOfBirth</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>દેશ કોડ</t>
+          <t>જન્મ તારીખ</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>fields.phone</t>
+          <t>fields.city</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>ફોન નંબર</t>
+          <t>શહેર</t>
         </is>
       </c>
     </row>
@@ -5873,12 +5873,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>fields.address</t>
+          <t>fields.country</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>સરનામું</t>
+          <t>દેશ</t>
         </is>
       </c>
     </row>
@@ -5890,12 +5890,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>fields.currency</t>
+          <t>fields.state</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>ચલણ</t>
+          <t>રાજ્ય</t>
         </is>
       </c>
     </row>
@@ -5907,12 +5907,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>fields.zipCode</t>
+          <t>fields.countryCode</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>ઝિપ કોડ</t>
+          <t>દેશ કોડ</t>
         </is>
       </c>
     </row>
@@ -5924,12 +5924,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>validation.firstNameRequired</t>
+          <t>fields.phone</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>તમારું પ્રથમ નામ દાખલ કરો</t>
+          <t>ફોન નંબર</t>
         </is>
       </c>
     </row>
@@ -5941,12 +5941,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>validation.firstNameMaxLength</t>
+          <t>fields.address</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>પ્રથમ નામ 10 અક્ષરથી વધુ ન હોઈ શકે</t>
+          <t>સરનામું</t>
         </is>
       </c>
     </row>
@@ -5958,12 +5958,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>validation.lastNameRequired</t>
+          <t>fields.currency</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>તમારું છેલ્લું નામ દાખલ કરો</t>
+          <t>ચલણ</t>
         </is>
       </c>
     </row>
@@ -5975,12 +5975,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>validation.lastNameMaxLength</t>
+          <t>fields.zipCode</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>છેલ્લું નામ 10 અક્ષરથી વધુ ન હોઈ શકે</t>
+          <t>ઝિપ કોડ</t>
         </is>
       </c>
     </row>
@@ -5992,12 +5992,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>validation.emailPattern</t>
+          <t>validation.firstNameRequired</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>માન્ય ઇ-મેઇલ દાખલ કરો</t>
+          <t>તમારું પ્રથમ નામ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -6009,12 +6009,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>validation.dobRequired</t>
+          <t>validation.firstNameMaxLength</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>તમારી જન્મ તારીખ પસંદ કરો</t>
+          <t>પ્રથમ નામ 10 અક્ષરથી વધુ ન હોઈ શકે</t>
         </is>
       </c>
     </row>
@@ -6026,12 +6026,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>validation.countryCodeRequired</t>
+          <t>validation.lastNameRequired</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>દેશ કોડ દાખલ કરો</t>
+          <t>તમારું છેલ્લું નામ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -6043,12 +6043,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>validation.zipCodeRequired</t>
+          <t>validation.lastNameMaxLength</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>કૃપા કરીને પિનકોડ દાખલ કરો</t>
+          <t>છેલ્લું નામ 10 અક્ષરથી વધુ ન હોઈ શકે</t>
         </is>
       </c>
     </row>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>toasts.success</t>
+          <t>validation.emailPattern</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>ખેલાડીની વિગત સફળતાપૂર્વક અપડેટ થઈ</t>
+          <t>માન્ય ઇ-મેઇલ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -6077,114 +6077,114 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>toasts.error</t>
+          <t>validation.dobRequired</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>ખેલાડીની પ્રૉફાઇલ અપડેટ કરવામાં નિષ્ફળ.</t>
+          <t>તમારી જન્મ તારીખ પસંદ કરો</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>promotions</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>noPromotions</t>
+          <t>validation.countryCodeRequired</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>કોઈ પ્રોમોશન ઉપલબ્ધ નથી.</t>
+          <t>દેશ કોડ દાખલ કરો</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>promotions</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>imageAlt</t>
+          <t>validation.zipCodeRequired</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>promotion_card_image</t>
+          <t>કૃપા કરીને પિનકોડ દાખલ કરો</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>bankInfo</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>toasts.success</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>બૅન્ક માહિતી</t>
+          <t>ખેલાડીની વિગત સફળતાપૂર્વક અપડેટ થઈ</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>bankInfo</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>bankDetailsTitle</t>
+          <t>toasts.error</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>તમારો બૅન્ક ડેટા</t>
+          <t>ખેલાડીની પ્રૉફાઇલ અપડેટ કરવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>bankInfo</t>
+          <t>promotions</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>labels.accountNo</t>
+          <t>noPromotions</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>ખાતા નંબર</t>
+          <t>કોઈ પ્રોમોશન ઉપલબ્ધ નથી.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>bankInfo</t>
+          <t>promotions</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>labels.bankName</t>
+          <t>imageAlt</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>બૅન્ક નામ</t>
+          <t>promotion_card_image</t>
         </is>
       </c>
     </row>
@@ -6196,12 +6196,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>labels.branchName</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>શાખા નામ</t>
+          <t>બૅન્ક માહિતી</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>labels.ifscCode</t>
+          <t>bankDetailsTitle</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>IFSC કોડ</t>
+          <t>તમારો બૅન્ક ડેટા</t>
         </is>
       </c>
     </row>
@@ -6230,12 +6230,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>labels.accountType</t>
+          <t>labels.accountNo</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>ખાતા પ્રકાર</t>
+          <t>ખાતા નંબર</t>
         </is>
       </c>
     </row>
@@ -6247,12 +6247,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>labels.accountHolderName</t>
+          <t>labels.bankName</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>ખાતા ધારકનું નામ</t>
+          <t>બૅન્ક નામ</t>
         </is>
       </c>
     </row>
@@ -6264,12 +6264,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>labels.amount</t>
+          <t>labels.branchName</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>રકમ</t>
+          <t>શાખા નામ</t>
         </is>
       </c>
     </row>
@@ -6281,12 +6281,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>labels.email</t>
+          <t>labels.ifscCode</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>ઇ-મેઇલ સરનામું</t>
+          <t>IFSC કોડ</t>
         </is>
       </c>
     </row>
@@ -6298,12 +6298,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>placeholders.selectAccount</t>
+          <t>labels.accountType</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>બૅન્ક ખાતું પસંદ કરો</t>
+          <t>ખાતા પ્રકાર</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>placeholders.enterAccountNo</t>
+          <t>labels.accountHolderName</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>ખાતા નંબર દાખલ કરો</t>
+          <t>ખાતા ધારકનું નામ</t>
         </is>
       </c>
     </row>
@@ -6332,12 +6332,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>placeholders.enterBankName</t>
+          <t>labels.amount</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>બૅન્ક નામ દાખલ કરો</t>
+          <t>રકમ</t>
         </is>
       </c>
     </row>
@@ -6349,12 +6349,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>placeholders.enterAccountHolderName</t>
+          <t>labels.email</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>ખાતા ધારકનું નામ દાખલ કરો</t>
+          <t>ઇ-મેઇલ સરનામું</t>
         </is>
       </c>
     </row>
@@ -6366,12 +6366,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>placeholders.enterBranchName</t>
+          <t>placeholders.selectAccount</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>શાખા નામ દાખલ કરો</t>
+          <t>બૅન્ક ખાતું પસંદ કરો</t>
         </is>
       </c>
     </row>
@@ -6383,12 +6383,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>placeholders.enterIfscCode</t>
+          <t>placeholders.enterAccountNo</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>IFSC કોડ દાખલ કરો</t>
+          <t>ખાતા નંબર દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -6400,12 +6400,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>placeholders.enterAccountType</t>
+          <t>placeholders.enterBankName</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>ખાતા પ્રકાર દાખલ કરો</t>
+          <t>બૅન્ક નામ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>placeholders.savings</t>
+          <t>placeholders.enterAccountHolderName</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>બચત</t>
+          <t>ખાતા ધારકનું નામ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -6434,12 +6434,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>placeholders.current</t>
+          <t>placeholders.enterBranchName</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>ચાલુ</t>
+          <t>શાખા નામ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -6451,12 +6451,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>validation.accountNoRequired</t>
+          <t>placeholders.enterIfscCode</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>ખાતા નંબર જરૂરી છે</t>
+          <t>IFSC કોડ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -6468,12 +6468,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>validation.accountNoNumbersOnly</t>
+          <t>placeholders.enterAccountType</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>ખાતા નંબર ફક્ત સંખ્યા ધરાવવો જોઈએ</t>
+          <t>ખાતા પ્રકાર દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -6485,12 +6485,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>validation.accountNoMaxLength</t>
+          <t>placeholders.savings</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>ખાતા નંબર 16 અંક કરતાં વધુ ન હોઈ શકે</t>
+          <t>બચત</t>
         </is>
       </c>
     </row>
@@ -6502,12 +6502,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>validation.accountNoDuplicate</t>
+          <t>placeholders.current</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>આ ખાતા નંબર પહેલેથી નોંધાયેલ છે.</t>
+          <t>ચાલુ</t>
         </is>
       </c>
     </row>
@@ -6519,12 +6519,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>validation.bankNameRequired</t>
+          <t>validation.accountNoRequired</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>બૅન્ક નામ જરૂરી છે</t>
+          <t>ખાતા નંબર જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -6536,12 +6536,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>validation.accountHolderNameRequired</t>
+          <t>validation.accountNoNumbersOnly</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>ખાતા ધારકનું નામ જરૂરી છે</t>
+          <t>ખાતા નંબર ફક્ત સંખ્યા ધરાવવો જોઈએ</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>validation.branchNameRequired</t>
+          <t>validation.accountNoMaxLength</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>શાખા નામ જરૂરી છે</t>
+          <t>ખાતા નંબર 16 અંક કરતાં વધુ ન હોઈ શકે</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>validation.ifscCodeRequired</t>
+          <t>validation.accountNoDuplicate</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>IFSC કોડ જરૂરી છે</t>
+          <t>આ ખાતા નંબર પહેલેથી નોંધાયેલ છે.</t>
         </is>
       </c>
     </row>
@@ -6587,12 +6587,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>validation.ifscCodeInvalid</t>
+          <t>validation.bankNameRequired</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>માન્ય IFSC કોડ દાખલ કરો (4 અક્ષર + 7 અંક)</t>
+          <t>બૅન્ક નામ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -6604,12 +6604,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>validation.accountTypeRequired</t>
+          <t>validation.accountHolderNameRequired</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>કૃપા કરીને ખાતા પ્રકાર પસંદ કરો</t>
+          <t>ખાતા ધારકનું નામ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -6621,12 +6621,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>validation.limitReached</t>
+          <t>validation.branchNameRequired</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>તમે 5 બૅન્ક ખાતાઓની મહત્તમ મર્યાદા પહોંચ્યા છો.</t>
+          <t>શાખા નામ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>toasts.createSuccess</t>
+          <t>validation.ifscCodeRequired</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>બૅન્ક ખાતું સફળતાપૂર્વક બનાવવામાં આવ્યું.</t>
+          <t>IFSC કોડ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>toasts.createError</t>
+          <t>validation.ifscCodeInvalid</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>બૅન્ક ખાતું બનાવવામાં નિષ્ફળ.</t>
+          <t>માન્ય IFSC કોડ દાખલ કરો (4 અક્ષર + 7 અંક)</t>
         </is>
       </c>
     </row>
@@ -6672,12 +6672,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>toasts.updateSuccess</t>
+          <t>validation.accountTypeRequired</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>બૅન્ક ખાતું સફળતાપૂર્વક અપડેટ થઈ.</t>
+          <t>કૃપા કરીને ખાતા પ્રકાર પસંદ કરો</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>toasts.updateError</t>
+          <t>validation.limitReached</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>બૅન્ક ખાતું અપડેટ કરવામાં નિષ્ફળ</t>
+          <t>તમે 5 બૅન્ક ખાતાઓની મહત્તમ મર્યાદા પહોંચ્યા છો.</t>
         </is>
       </c>
     </row>
@@ -6706,80 +6706,80 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>toasts.alreadyExists</t>
+          <t>toasts.createSuccess</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>બૅન્ક ખાતું પહેલેથી અસ્તિત્વ ધરાવે છે</t>
+          <t>બૅન્ક ખાતું સફળતાપૂર્વક બનાવવામાં આવ્યું.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>transactionHistory</t>
+          <t>bankInfo</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>toasts.createError</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>વ્યવહાર ઇતિહાસ</t>
+          <t>બૅન્ક ખાતું બનાવવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>transactionHistory</t>
+          <t>bankInfo</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>tabs.gameHistory</t>
+          <t>toasts.updateSuccess</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>ગેમ ઇતિહાસ</t>
+          <t>બૅન્ક ખાતું સફળતાપૂર્વક અપડેટ થઈ.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>transactionHistory</t>
+          <t>bankInfo</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>tabs.depositSummary</t>
+          <t>toasts.updateError</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ સારાંશ</t>
+          <t>બૅન્ક ખાતું અપડેટ કરવામાં નિષ્ફળ</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>transactionHistory</t>
+          <t>bankInfo</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>tabs.withdrawSummary</t>
+          <t>toasts.alreadyExists</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>ઉપાડ સારાંશ</t>
+          <t>બૅન્ક ખાતું પહેલેથી અસ્તિત્વ ધરાવે છે</t>
         </is>
       </c>
     </row>
@@ -6791,12 +6791,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>tabs.allTransactions</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>બધા વ્યવહાર</t>
+          <t>વ્યવહાર ઇતિહાસ</t>
         </is>
       </c>
     </row>
@@ -6808,12 +6808,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>transactionTable.columns.serialNo</t>
+          <t>tabs.gameHistory</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>ક્રમ નં.</t>
+          <t>ગેમ ઇતિહાસ</t>
         </is>
       </c>
     </row>
@@ -6825,12 +6825,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>transactionTable.columns.description</t>
+          <t>tabs.depositSummary</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>વર્ણન</t>
+          <t>ડિપૉઝિટ સારાંશ</t>
         </is>
       </c>
     </row>
@@ -6842,12 +6842,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>transactionTable.columns.gameName</t>
+          <t>tabs.withdrawSummary</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>ગેમ નામ</t>
+          <t>ઉપાડ સારાંશ</t>
         </is>
       </c>
     </row>
@@ -6859,12 +6859,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>transactionTable.columns.startBalance</t>
+          <t>tabs.allTransactions</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>પ્રારંભ બૅલૅન્સ</t>
+          <t>બધા વ્યવહાર</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>transactionTable.columns.amount</t>
+          <t>transactionTable.columns.serialNo</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>રકમ</t>
+          <t>ક્રમ નં.</t>
         </is>
       </c>
     </row>
@@ -6893,12 +6893,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>transactionTable.columns.endBalance</t>
+          <t>transactionTable.columns.description</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>અંત બૅલૅન્સ</t>
+          <t>વર્ણન</t>
         </is>
       </c>
     </row>
@@ -6910,12 +6910,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>transactionTable.columns.timeStamp</t>
+          <t>transactionTable.columns.gameName</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>ટાઇમ સ્ટૅમ્પ</t>
+          <t>ગેમ નામ</t>
         </is>
       </c>
     </row>
@@ -6927,12 +6927,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>transactionTable.columns.transactionStatus</t>
+          <t>transactionTable.columns.startBalance</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>વ્યવહાર સ્ટેટ્સ</t>
+          <t>પ્રારંભ બૅલૅન્સ</t>
         </is>
       </c>
     </row>
@@ -6944,12 +6944,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>transactionTable.columns.providerName</t>
+          <t>transactionTable.columns.amount</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>પ્રૉવાઇડર નામ</t>
+          <t>રકમ</t>
         </is>
       </c>
     </row>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>transactionTable.columns.transactionId</t>
+          <t>transactionTable.columns.endBalance</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>વ્યવહાર ID</t>
+          <t>અંત બૅલૅન્સ</t>
         </is>
       </c>
     </row>
@@ -6978,12 +6978,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>transactionTable.columns.gameTransactionId</t>
+          <t>transactionTable.columns.timeStamp</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>ગેમ વ્યવહાર ID</t>
+          <t>ટાઇમ સ્ટૅમ્પ</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>transactionTable.columns.referenceId</t>
+          <t>transactionTable.columns.transactionStatus</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>સંદર્ભ ID</t>
+          <t>વ્યવહાર સ્ટેટ્સ</t>
         </is>
       </c>
     </row>
@@ -7012,12 +7012,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>transactionTable.columns.transactionNo</t>
+          <t>transactionTable.columns.providerName</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>વ્યવહાર નં.</t>
+          <t>પ્રૉવાઇડર નામ</t>
         </is>
       </c>
     </row>
@@ -7029,12 +7029,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>transactionTable.columns.status</t>
+          <t>transactionTable.columns.transactionId</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>સ્ટેટ્સ</t>
+          <t>વ્યવહાર ID</t>
         </is>
       </c>
     </row>
@@ -7046,12 +7046,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>transactionTable.pagination.rowsPerPage</t>
+          <t>transactionTable.columns.gameTransactionId</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>પ્રતિ પૃષ્ઠ પ્રવૃત્તિઓ:</t>
+          <t>ગેમ વ્યવહાર ID</t>
         </is>
       </c>
     </row>
@@ -7063,12 +7063,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>transactionTable.pagination.prev</t>
+          <t>transactionTable.columns.referenceId</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>પહેલા</t>
+          <t>સંદર્ભ ID</t>
         </is>
       </c>
     </row>
@@ -7080,12 +7080,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>transactionTable.pagination.next</t>
+          <t>transactionTable.columns.transactionNo</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>આગળ</t>
+          <t>વ્યવહાર નં.</t>
         </is>
       </c>
     </row>
@@ -7097,12 +7097,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>transactionTable.dateSelector.today</t>
+          <t>transactionTable.columns.status</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>આજ</t>
+          <t>સ્ટેટ્સ</t>
         </is>
       </c>
     </row>
@@ -7114,12 +7114,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>transactionTable.dateSelector.yesterday</t>
+          <t>transactionTable.pagination.rowsPerPage</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>ગઈ કાલ</t>
+          <t>પ્રતિ પૃષ્ઠ પ્રવૃત્તિઓ:</t>
         </is>
       </c>
     </row>
@@ -7131,12 +7131,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>transactionTable.dateSelector.thisWeek</t>
+          <t>transactionTable.pagination.prev</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>આ અઠવાડિયે</t>
+          <t>પહેલા</t>
         </is>
       </c>
     </row>
@@ -7148,12 +7148,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>transactionTable.dateSelector.lastWeek</t>
+          <t>transactionTable.pagination.next</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>ગત અઠવાડિયે</t>
+          <t>આગળ</t>
         </is>
       </c>
     </row>
@@ -7165,12 +7165,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>transactionTable.dateSelector.thisMonth</t>
+          <t>transactionTable.dateSelector.today</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>આ મહિને</t>
+          <t>આજ</t>
         </is>
       </c>
     </row>
@@ -7182,114 +7182,114 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>transactionTable.dateSelector.lastMonth</t>
+          <t>transactionTable.dateSelector.yesterday</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>ગત મહિને</t>
+          <t>ગઈ કાલ</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>partners</t>
+          <t>transactionHistory</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>provider</t>
+          <t>transactionTable.dateSelector.thisWeek</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>પ્રૉવાઇડર</t>
+          <t>આ અઠવાડિયે</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>header</t>
+          <t>transactionHistory</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>loginButton</t>
+          <t>transactionTable.dateSelector.lastWeek</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>લૉગ ઇન</t>
+          <t>ગત અઠવાડિયે</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>header</t>
+          <t>transactionHistory</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>registerButton</t>
+          <t>transactionTable.dateSelector.thisMonth</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>નોંધણી</t>
+          <t>આ મહિને</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>header</t>
+          <t>transactionHistory</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>helloUser</t>
+          <t>transactionTable.dateSelector.lastMonth</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>નમસ્તે, {{userName}}</t>
+          <t>ગત મહિને</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>header</t>
+          <t>transactionHistory</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>filters.allGames</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>બૅલૅન્સ</t>
+          <t>All Games</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>header</t>
+          <t>partners</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>logout</t>
+          <t>provider</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>લૉગ આઉટ</t>
+          <t>પ્રૉવાઇડર</t>
         </is>
       </c>
     </row>
@@ -7301,308 +7301,308 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>toasts.logoutSuccess</t>
+          <t>loginButton</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>લૉગ આઉટ સફળ</t>
+          <t>લૉગ ઇન</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>footer</t>
+          <t>header</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>socialLinks</t>
+          <t>registerButton</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>સોશ્યલ લિંક્સ</t>
+          <t>નોંધણી</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>footer</t>
+          <t>header</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>logoAlt</t>
+          <t>helloUser</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>લોગો</t>
+          <t>નમસ્તે, {{userName}}</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>footer</t>
+          <t>header</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>contactAlt</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>સંપર્ક</t>
+          <t>બૅલૅન્સ</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>footer</t>
+          <t>header</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>copyright</t>
+          <t>logout</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>© કૉપીરાઇટ 2026 {{brandName}}. સર્વ અધિકાર સુરક્ષિત.</t>
+          <t>લૉગ આઉટ</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>footer</t>
+          <t>header</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>toasts.logoutSuccess</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>આવૃત્તિ</t>
+          <t>લૉગ આઉટ સફળ</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>footer</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>switchToLight</t>
+          <t>socialLinks</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>લાઇટ મોડ પર સ્વિચ કરો</t>
+          <t>સોશ્યલ લિંક્સ</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>footer</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>switchToDark</t>
+          <t>logoAlt</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>ડાર્ક મોડ પર સ્વિચ કરો</t>
+          <t>લોગો</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>multiLadder</t>
+          <t>footer</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>allMilestonesComplete</t>
+          <t>contactAlt</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>બધા માઇલસ્ટોન પૂર્ણ!</t>
+          <t>સંપર્ક</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>multiLadder</t>
+          <t>footer</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>milestoneUnlocked</t>
+          <t>copyright</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>માઇલસ્ટોન અનલૉક થઈ ગઈ</t>
+          <t>© કૉપીરાઇટ 2026 {{brandName}}. સર્વ અધિકાર સુરક્ષિત.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>multiLadder</t>
+          <t>footer</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>tierReached</t>
+          <t>version</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>{{tierName}} પ્રાપ્ત!</t>
+          <t>આવૃત્તિ</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>notAuthorized</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>switchToLight</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>આ પૃષ્ઠ ઍક્સેસ કરવા માટે તમે અધિકૃત નથી.</t>
+          <t>લાઇટ મોડ પર સ્વિચ કરો</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>notFound</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>switchToDark</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>ડાર્ક મોડ પર સ્વિચ કરો</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>notFound</t>
+          <t>multiLadder</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>allMilestonesComplete</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>અરે! પૃષ્ઠ મળ્યું નહીં</t>
+          <t>બધા માઇલસ્ટોન પૂર્ણ!</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>notFound</t>
+          <t>multiLadder</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>milestoneUnlocked</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>જે પૃષ્ઠ તમે શોધી રહ્યા છો તે અસ્તિત્વ ધરાવ્યું નથી અથવા ખસેડવામાં આવ્યું છે. ચાલો તમને પાછા જ્યાં હોવ ત્યાં મોકલીએ.</t>
+          <t>માઇલસ્ટોન અનલૉક થઈ ગઈ</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>aboutSection</t>
+          <t>multiLadder</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>defaultTitle</t>
+          <t>tierReached</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>{{brandName}} વિષે</t>
+          <t>{{tierName}} પ્રાપ્ત!</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>aboutSection</t>
+          <t>notAuthorized</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>bgAlt</t>
+          <t>message</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>about background</t>
+          <t>આ પૃષ્ઠ ઍક્સેસ કરવા માટે તમે અધિકૃત નથી.</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>exploreFeatures</t>
+          <t>notFound</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>code</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>બધી સુવિધાઓ એક્સ્પ્લોર કરો</t>
+          <t>404</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>leaderboard</t>
+          <t>notFound</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -7612,109 +7612,109 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>ટૂર્નામૅન્ટ</t>
+          <t>અરે! પૃષ્ઠ મળ્યું નહીં</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>leaderboard</t>
+          <t>notFound</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>termsAndConditions</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>નિયમો અને શરતો</t>
+          <t>જે પૃષ્ઠ તમે શોધી રહ્યા છો તે અસ્તિત્વ ધરાવ્યું નથી અથવા ખસેડવામાં આવ્યું છે. ચાલો તમને પાછા જ્યાં હોવ ત્યાં મોકલીએ.</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>leaderboard</t>
+          <t>aboutSection</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>myRank</t>
+          <t>defaultTitle</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>મારો ક્રમ</t>
+          <t>{{brandName}} વિષે</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>leaderboard</t>
+          <t>aboutSection</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>start</t>
+          <t>bgAlt</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>શરૂ</t>
+          <t>about background</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>leaderboard</t>
+          <t>exploreFeatures</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>end</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>અંત</t>
+          <t>બધી સુવિધાઓ એક્સ્પ્લોર કરો</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>leaderboard</t>
+          <t>exploreFeatures</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>rank</t>
+          <t>downloadApplication</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>ક્રમ</t>
+          <t>એપ્લિકેશન ડાઉનલોડ કરો</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>leaderboard</t>
+          <t>exploreFeatures</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>installApplication</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>ખેલાડી</t>
+          <t>એપ્લિકેશન ઇન્સ્ટોલ કરો</t>
         </is>
       </c>
     </row>
@@ -7726,12 +7726,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>પૉઇન્ટ</t>
+          <t>ટૂર્નામૅન્ટ</t>
         </is>
       </c>
     </row>
@@ -7743,12 +7743,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>prize</t>
+          <t>termsAndConditions</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>ઇનામ</t>
+          <t>નિયમો અને શરતો</t>
         </is>
       </c>
     </row>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>noPlayersFound</t>
+          <t>myRank</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>કોઈ ખેલાડી મળ્યા નહીં</t>
+          <t>મારો ક્રમ</t>
         </is>
       </c>
     </row>
@@ -7777,12 +7777,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>noActiveTournaments</t>
+          <t>start</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>હાલ કોઈ સક્રિય ટૂર્નામૅન્ટ નથી</t>
+          <t>શરૂ</t>
         </is>
       </c>
     </row>
@@ -7794,131 +7794,131 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>trophyAlt</t>
+          <t>end</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>ટ્રૉફી</t>
+          <t>અંત</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>ladder</t>
+          <t>leaderboard</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>loading</t>
+          <t>rank</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>તમારી લૅડર લોડ થઈ રહી છે…</t>
+          <t>ક્રમ</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>ladder</t>
+          <t>leaderboard</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>allMilestones</t>
+          <t>player</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>બધા માઇલસ્ટોન</t>
+          <t>ખેલાડી</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>ladder</t>
+          <t>leaderboard</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>creditedInstantly</t>
+          <t>points</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>તમારા વૉલેટમાં તરત ક્રેડિટ</t>
+          <t>પૉઇન્ટ</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>ladder</t>
+          <t>leaderboard</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>fullTermsApply</t>
+          <t>prize</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>સંપૂર્ણ T&amp;C લાગૂ.</t>
+          <t>ઇનામ</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>ladder</t>
+          <t>leaderboard</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>simulatingProgress</t>
+          <t>noPlayersFound</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>પ્રગતિ સિમ્યુલેટ થઈ રહી છે</t>
+          <t>કોઈ ખેલાડી મળ્યા નહીં</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>ladder</t>
+          <t>leaderboard</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>simulateProgress</t>
+          <t>noActiveTournaments</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>તમારી પ્રગતિ સિમ્યુલેટ કરો</t>
+          <t>હાલ કોઈ સક્રિય ટૂર્નામૅન્ટ નથી</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>ladder</t>
+          <t>leaderboard</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>simulateBetAmount</t>
+          <t>trophyAlt</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>દાવ રકમ સિમ્યુલેટ કરો</t>
+          <t>ટ્રૉફી</t>
         </is>
       </c>
     </row>
@@ -7930,12 +7930,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>toNextReward</t>
+          <t>loading</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>આગળના ઇનામ સુધી</t>
+          <t>તમારી લૅડર લોડ થઈ રહી છે…</t>
         </is>
       </c>
     </row>
@@ -7947,12 +7947,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>unlocked</t>
+          <t>allMilestones</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>અનલૉક</t>
+          <t>બધા માઇલસ્ટોન</t>
         </is>
       </c>
     </row>
@@ -7964,12 +7964,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>stillToEarn</t>
+          <t>creditedInstantly</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>હજૂ કમાવવા</t>
+          <t>તમારા વૉલેટમાં તરત ક્રેડિટ</t>
         </is>
       </c>
     </row>
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>nextReward</t>
+          <t>fullTermsApply</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>આગળનું ઇનામ</t>
+          <t>સંપૂર્ણ T&amp;C લાગૂ.</t>
         </is>
       </c>
     </row>
@@ -7998,12 +7998,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>moreToUnlock</t>
+          <t>simulatingProgress</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>અનલૉક કરવા વધુ</t>
+          <t>પ્રગતિ સિમ્યુલેટ થઈ રહી છે</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>percentThere</t>
+          <t>simulateProgress</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>ત્યાં સુધી</t>
+          <t>તમારી પ્રગતિ સિમ્યુલેટ કરો</t>
         </is>
       </c>
     </row>
@@ -8032,12 +8032,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>allMilestonesCompletePre</t>
+          <t>simulateBetAmount</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>બધા માઇલસ્ટોન પૂર્ણ</t>
+          <t>દાવ રકમ સિમ્યુલેટ કરો</t>
         </is>
       </c>
     </row>
@@ -8049,12 +8049,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>allMilestonesCompletePost</t>
+          <t>toNextReward</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>કમાયા!</t>
+          <t>આગળના ઇનામ સુધી</t>
         </is>
       </c>
     </row>
@@ -8066,12 +8066,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>bonusCredited</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>{{count}} બોનસ ક્રેડિટ</t>
+          <t>અનલૉક</t>
         </is>
       </c>
     </row>
@@ -8083,12 +8083,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>bonusesCredited</t>
+          <t>stillToEarn</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>{{count}} બોનસ ક્રેડિટ</t>
+          <t>હજૂ કમાવવા</t>
         </is>
       </c>
     </row>
@@ -8100,12 +8100,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>milestoneName</t>
+          <t>nextReward</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>{{name}} માઇલસ્ટોન</t>
+          <t>આગળનું ઇનામ</t>
         </is>
       </c>
     </row>
@@ -8117,12 +8117,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>creditedInstantlyLabel</t>
+          <t>moreToUnlock</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>તરત ક્રેડિટ</t>
+          <t>અનલૉક કરવા વધુ</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>bonusEarnedLabel</t>
+          <t>percentThere</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>બોનસ કમાયા</t>
+          <t>ત્યાં સુધી</t>
         </is>
       </c>
     </row>
@@ -8151,12 +8151,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>totalPossible</t>
+          <t>allMilestonesCompletePre</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>કુલ સંભવ</t>
+          <t>બધા માઇલસ્ટોન પૂર્ણ</t>
         </is>
       </c>
     </row>
@@ -8168,12 +8168,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>creditedRewards</t>
+          <t>allMilestonesCompletePost</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>ક્રેડિટ ઇનામ</t>
+          <t>કમાયા!</t>
         </is>
       </c>
     </row>
@@ -8185,12 +8185,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>credited</t>
+          <t>bonusCredited</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>ક્રેડિટ</t>
+          <t>{{count}} બોનસ ક્રેડિટ</t>
         </is>
       </c>
     </row>
@@ -8202,12 +8202,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>realMoney</t>
+          <t>bonusesCredited</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>રિઅલ મની</t>
+          <t>{{count}} બોનસ ક્રેડિટ</t>
         </is>
       </c>
     </row>
@@ -8219,12 +8219,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>completedAt</t>
+          <t>milestoneName</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>પૂર્ણ સ્થળ</t>
+          <t>{{name}} માઇલસ્ટોન</t>
         </is>
       </c>
     </row>
@@ -8236,12 +8236,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>tierPercentThere</t>
+          <t>creditedInstantlyLabel</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>{{pct}}% ત્યાં</t>
+          <t>તરત ક્રેડિટ</t>
         </is>
       </c>
     </row>
@@ -8253,12 +8253,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>cumulativeBets</t>
+          <t>bonusEarnedLabel</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>સંચિત દાવ</t>
+          <t>બોનસ કમાયા</t>
         </is>
       </c>
     </row>
@@ -8270,12 +8270,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>promotion</t>
+          <t>totalPossible</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>બોનસ લૅડર પ્રોમોશન</t>
+          <t>કુલ સંભવ</t>
         </is>
       </c>
     </row>
@@ -8287,12 +8287,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>termsAndConditions</t>
+          <t>creditedRewards</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>નિયમો અને શરતો</t>
+          <t>ક્રેડિટ ઇનામ</t>
         </is>
       </c>
     </row>
@@ -8304,12 +8304,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>termsDialogLabel</t>
+          <t>credited</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>બોનસ લૅડર નિયમો અને શરતો</t>
+          <t>ક્રેડિટ</t>
         </is>
       </c>
     </row>
@@ -8321,12 +8321,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>understandAndClose</t>
+          <t>realMoney</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>હું સમજ્યો — બંધ કરો</t>
+          <t>રિઅલ મની</t>
         </is>
       </c>
     </row>
@@ -8338,12 +8338,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>variants.deposit.placed</t>
+          <t>completedAt</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ</t>
+          <t>પૂર્ણ સ્થળ</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>variants.deposit.totalPlacedShort</t>
+          <t>tierPercentThere</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>કુલ ડિપૉઝિટ</t>
+          <t>{{pct}}% ત્યાં</t>
         </is>
       </c>
     </row>
@@ -8372,12 +8372,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>variants.deposit.totalPlacedLong</t>
+          <t>cumulativeBets</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>આ કૅમ્પેઇનમાં કુલ ડિપૉઝિટ</t>
+          <t>સંચિત દાવ</t>
         </is>
       </c>
     </row>
@@ -8389,12 +8389,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>variants.deposit.milestonesUnlocked</t>
+          <t>promotion</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>{{done}} of {{total}} માઇલસ્ટોન પ્રાપ્ત</t>
+          <t>બોનસ લૅડર પ્રોમોશન</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>variants.deposit.betMoreToUnlock</t>
+          <t>termsAndConditions</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ</t>
+          <t>નિયમો અને શરતો</t>
         </is>
       </c>
     </row>
@@ -8423,12 +8423,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>variants.deposit.noRewardsYet</t>
+          <t>termsDialogLabel</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>હજૂ કોઈ ઇનામ નહીં — પ્રથમ ક્વૉલિફાઇંગ ડિપૉઝિટ કરો</t>
+          <t>બોનસ લૅડર નિયમો અને શરતો</t>
         </is>
       </c>
     </row>
@@ -8440,12 +8440,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>variants.deposit.cumulativeUnit</t>
+          <t>understandAndClose</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>સંચિત ડિપૉઝિટ</t>
+          <t>હું સમજ્યો — બંધ કરો</t>
         </is>
       </c>
     </row>
@@ -8457,12 +8457,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>variants.deposit.keepGoing</t>
+          <t>variants.deposit.placed</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ ચાલૂ રાખો →</t>
+          <t>ડિપૉઝિટ</t>
         </is>
       </c>
     </row>
@@ -8474,12 +8474,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>variants.deposit.overlayNextCta</t>
+          <t>variants.deposit.totalPlacedShort</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ</t>
+          <t>કુલ ડિપૉઝિટ</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>variants.bet.placed</t>
+          <t>variants.deposit.totalPlacedLong</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>લગાવ્યો</t>
+          <t>આ કૅમ્પેઇનમાં કુલ ડિપૉઝિટ</t>
         </is>
       </c>
     </row>
@@ -8508,12 +8508,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>variants.bet.totalPlacedShort</t>
+          <t>variants.deposit.milestonesUnlocked</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>કુલ દાવ</t>
+          <t>{{done}} of {{total}} માઇલસ્ટોન પ્રાપ્ત</t>
         </is>
       </c>
     </row>
@@ -8525,12 +8525,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>variants.bet.totalPlacedLong</t>
+          <t>variants.deposit.betMoreToUnlock</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>આ કૅમ્પેઇનમાં કુલ દાવ</t>
+          <t>ડિપૉઝિટ</t>
         </is>
       </c>
     </row>
@@ -8542,12 +8542,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>variants.bet.milestonesUnlocked</t>
+          <t>variants.deposit.noRewardsYet</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>{{done}} of {{total}} માઇલસ્ટોન અનલૉક</t>
+          <t>હજૂ કોઈ ઇનામ નહીં — પ્રથમ ક્વૉલિફાઇંગ ડિપૉઝિટ કરો</t>
         </is>
       </c>
     </row>
@@ -8559,12 +8559,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>variants.bet.betMoreToUnlock</t>
+          <t>variants.deposit.cumulativeUnit</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>દાવ</t>
+          <t>સંચિત ડિપૉઝિટ</t>
         </is>
       </c>
     </row>
@@ -8576,12 +8576,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>variants.bet.noRewardsYet</t>
+          <t>variants.deposit.keepGoing</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>હજૂ કોઈ ઇનામ નહીં — પ્રથમ ક્વૉલિફાઇંગ દાવ લગાવો</t>
+          <t>ડિપૉઝિટ ચાલૂ રાખો →</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>variants.bet.cumulativeUnit</t>
+          <t>variants.deposit.overlayNextCta</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>સંચિત દાવ</t>
+          <t>ડિપૉઝિટ</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>variants.bet.keepGoing</t>
+          <t>variants.bet.placed</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>દાવ ચાલૂ રાખો →</t>
+          <t>લગાવ્યો</t>
         </is>
       </c>
     </row>
@@ -8627,12 +8627,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>variants.bet.overlayNextCta</t>
+          <t>variants.bet.totalPlacedShort</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>દાવ</t>
+          <t>કુલ દાવ</t>
         </is>
       </c>
     </row>
@@ -8644,12 +8644,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>overlay.allMilestonesComplete</t>
+          <t>variants.bet.totalPlacedLong</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>બધા માઇલસ્ટોન પૂર્ણ!</t>
+          <t>આ કૅમ્પેઇનમાં કુલ દાવ</t>
         </is>
       </c>
     </row>
@@ -8661,12 +8661,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>overlay.milestoneUnlocked</t>
+          <t>variants.bet.milestonesUnlocked</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>માઇલસ્ટોન અનલૉક</t>
+          <t>{{done}} of {{total}} માઇલસ્ટોન અનલૉક</t>
         </is>
       </c>
     </row>
@@ -8678,12 +8678,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>overlay.tierReached</t>
+          <t>variants.bet.betMoreToUnlock</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>{{name}} પ્રાપ્ત!</t>
+          <t>દાવ</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>overlay.creditedToWallet</t>
+          <t>variants.bet.noRewardsYet</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>તમારા વૉલેટમાં ક્રેડિટ</t>
+          <t>હજૂ કોઈ ઇનામ નહીં — પ્રથમ ક્વૉલિફાઇંગ દાવ લગાવો</t>
         </is>
       </c>
     </row>
@@ -8712,12 +8712,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>overlay.rolloverNote</t>
+          <t>variants.bet.cumulativeUnit</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>રિઅલ મની · રૉલઓવર: 1× · ક્યારેય સમાપ્ત નહીં</t>
+          <t>સંચિત દાવ</t>
         </is>
       </c>
     </row>
@@ -8729,12 +8729,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>overlay.nextMilestone</t>
+          <t>variants.bet.keepGoing</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>આગળ માઇલસ્ટોન — {{name}}</t>
+          <t>દાવ ચાલૂ રાખો →</t>
         </is>
       </c>
     </row>
@@ -8746,7 +8746,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>overlay.betMore</t>
+          <t>variants.bet.overlayNextCta</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>overlay.betMoreToEarn</t>
+          <t>overlay.allMilestonesComplete</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>વધુ કમાવવા</t>
+          <t>બધા માઇલસ્ટોન પૂર્ણ!</t>
         </is>
       </c>
     </row>
@@ -8780,12 +8780,12 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>overlay.allDoneTitle</t>
+          <t>overlay.milestoneUnlocked</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>તમે બધા માઇલસ્ટોન પૂર્ણ કર્યા!</t>
+          <t>માઇલસ્ટોન અનલૉક</t>
         </is>
       </c>
     </row>
@@ -8797,12 +8797,12 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>overlay.allDoneSubtitle</t>
+          <t>overlay.tierReached</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>બધા બોનસ તમારા વૉલેટમાં ક્રેડિટ થઈ ગયા.</t>
+          <t>{{name}} પ્રાપ્ત!</t>
         </is>
       </c>
     </row>
@@ -8814,12 +8814,12 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>overlay.viewLadder</t>
+          <t>overlay.rolloverNote</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>મારી લૅડર જુઓ</t>
+          <t>રિઅલ મની · રૉલઓવર: 1× · ક્યારેય સમાપ્ત નહીં</t>
         </is>
       </c>
     </row>
@@ -8831,12 +8831,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>overlay.viewLadderArrow</t>
+          <t>overlay.nextMilestone</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>મારી લૅડર જુઓ →</t>
+          <t>આગળ માઇલસ્ટોન — {{name}}</t>
         </is>
       </c>
     </row>
@@ -8848,12 +8848,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>achievement.milestoneUnlocked</t>
+          <t>overlay.betMore</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>માઇલસ્ટોન અનલૉક</t>
+          <t>દાવ</t>
         </is>
       </c>
     </row>
@@ -8865,12 +8865,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>achievement.tierAchieved</t>
+          <t>overlay.betMoreToEarn</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>ટિઅર પ્રાપ્ત!</t>
+          <t>વધુ કમાવવા</t>
         </is>
       </c>
     </row>
@@ -8882,12 +8882,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>achievement.creditedToWallet</t>
+          <t>overlay.allDoneTitle</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>વૉલેટમાં ક્રેડિટ</t>
+          <t>તમે બધા માઇલસ્ટોન પૂર્ણ કર્યા!</t>
         </is>
       </c>
     </row>
@@ -8899,61 +8899,435 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>achievement.gotIt</t>
+          <t>overlay.allDoneSubtitle</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>સમજ્યો!</t>
+          <t>બધા બોનસ તમારા વૉલેટમાં ક્રેડિટ થઈ ગયા.</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>pwa</t>
+          <t>ladder</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>overlay.viewLadder</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Setbet એપ</t>
+          <t>મારી લૅડર જુઓ</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>pwa</t>
+          <t>ladder</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>subTitle</t>
+          <t>overlay.viewLadderArrow</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Setbet</t>
+          <t>મારી લૅડર જુઓ →</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
+          <t>ladder</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>achievement.milestoneUnlocked</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>માઇલસ્ટોન અનલૉક</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>ladder</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>achievement.tierAchieved</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>ટિઅર પ્રાપ્ત!</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>jackpot</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>monthlyJackpot</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>માસિક જેકપોટ</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>jackpot</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>જેકપોટ વિજેતાઓ</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>jackpot</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>winner</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>જેકપોટ વિજેતા</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>jackpot</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>congratulationDefault</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>અભિનંદન — તમે આ મહિનાના જેકપોટ વિજેતાઓમાંના એક છો!</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>jackpot</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>youWonThisMonthPre</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>તમે જીત્યા</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>jackpot</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>youWonThisMonthPost</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>આ મહિને</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>jackpot</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>loadError</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>{{month}} માટેના વિજેતાઓ લોડ કરી શકાયા નથી.</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>jackpot</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>noWinners</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>{{month}} માટે હજી સુધી કોઈ જેકપોટ વિજેતા નથી.</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>jackpot</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>checkBack</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>આગામી ડ્રો પછી ફરી તપાસો.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>jackpot</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>loadMore</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>વધુ વિજેતાઓ લોડ કરો</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>jackpot</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>winnerCount</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>{{month}} માટે {{count}} વિજેતા</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>jackpot</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>winnersCount</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>{{month}} માટે {{count}} વિજેતાઓ</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>jackpot</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>previousMonth</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>પાછલો મહિનો</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>jackpot</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>nextMonth</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>આગલો મહિનો</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>jackpot</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>backToThisMonth</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>આ મહિને પાછા જાઓ</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>jackpot</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>you</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>તમે</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>jackpot</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>youBadge</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>તમે</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>jackpot</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>{{position}} સ્થાન</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
           <t>pwa</t>
         </is>
       </c>
-      <c r="B502" t="inlineStr">
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Setbet એપ</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>pwa</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>subTitle</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Setbet</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>pwa</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C502" t="inlineStr">
+      <c r="C524" t="inlineStr">
         <is>
           <t>બૅટિંગ માટેની તમારી અંતિમ મંઝિલ</t>
         </is>

--- a/setbet/locales-excel/gu.xlsx
+++ b/setbet/locales-excel/gu.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C524"/>
+  <dimension ref="A1:C515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -586,29 +586,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>unexpectedError</t>
+          <t>failedToLoadPageError</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>અણધારી ભૂલ આવી. કૃપા કરીને ફરી પ્રયાસ કરો.</t>
+          <t>{{page}} પૃષ્ઠ લોડ કરવામાં નિષ્ફળ. ફરી પ્રયાસ કરો.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>errors</t>
+          <t>locale</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>failedToLoadPageError</t>
+          <t>unavailable.title</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{{page}} પૃષ્ઠ લોડ કરવામાં નિષ્ફળ. ફરી પ્રયાસ કરો.</t>
+          <t>ભાષા ઉપલબ્ધ નથી</t>
         </is>
       </c>
     </row>
@@ -620,29 +620,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>unavailable.title</t>
+          <t>unavailable.message</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ભાષા ઉપલબ્ધ નથી</t>
+          <t>{{locale}} ભાષા હાલમાં ઉપલબ્ધ નથી. મૂળભૂત ભાષા દર્શાવવામાં આવી રહી છે.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>locale</t>
+          <t>context</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>unavailable.message</t>
+          <t>idleWarning</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{{locale}} ભાષા હાલમાં ઉપલબ્ધ નથી. મૂળભૂત ભાષા દર્શાવવામાં આવી રહી છે.</t>
+          <t>નિષ્ક્રિયતાને કારણે 1 મિનિટમાં તમે લૉગ આઉટ થઈ જશો</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>idleWarning</t>
+          <t>brandIdError</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>નિષ્ક્રિયતાને કારણે 1 મિનિટમાં તમે લૉગ આઉટ થઈ જશો</t>
+          <t>બ્રાન્ડ ID મેળવવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
@@ -671,29 +671,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>brandIdError</t>
+          <t>initializationError</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>બ્રાન્ડ ID મેળવવામાં નિષ્ફળ.</t>
+          <t>બ્રાન્ડ પ્રારંભ કરવામાં નિષ્ફળ. કૃપા કરીને રિફ્રેશ કરો.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>context</t>
+          <t>seo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>initializationError</t>
+          <t>accountSettings.pageName</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>બ્રાન્ડ પ્રારંભ કરવામાં નિષ્ફળ. કૃપા કરીને રિફ્રેશ કરો.</t>
+          <t>એકાઉન્ટ સેટિંગ્સ</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>accountSettings.pageName</t>
+          <t>bankInfo.pageName</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>એકાઉન્ટ સેટિંગ્સ</t>
+          <t>બેંક માહિતી</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>bankInfo.pageName</t>
+          <t>bonus.pageName</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>બેંક માહિતી</t>
+          <t>બોનસ</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>bonus.pageName</t>
+          <t>deposit.pageName</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>બોનસ</t>
+          <t>જમા કરો</t>
         </is>
       </c>
     </row>
@@ -756,12 +756,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>deposit.pageName</t>
+          <t>kyc.pageName</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>જમા કરો</t>
+          <t>KYC ચકાસણી</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>kyc.pageName</t>
+          <t>profile.pageName</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KYC ચકાસણી</t>
+          <t>પ્રોફાઇલ</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>profile.pageName</t>
+          <t>transactionHistory.pageName</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>પ્રોફાઇલ</t>
+          <t>વ્યવહાર ઇતિહાસ</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>transactionHistory.pageName</t>
+          <t>wallet.pageName</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>વ્યવહાર ઇતિહાસ</t>
+          <t>વૉલેટ</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>wallet.pageName</t>
+          <t>withdraw.pageName</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>વૉલેટ</t>
+          <t>ઉપાડ</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>withdraw.pageName</t>
+          <t>casino.pageName</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ઉપાડ</t>
+          <t>કેસિનો</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>casino.pageName</t>
+          <t>exchange.pageName</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>કેસિનો</t>
+          <t>એક્સચેન્જ</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>exchange.pageName</t>
+          <t>liveCasino.pageName</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>એક્સચેન્જ</t>
+          <t>લાઈવ કેસિનો</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>liveCasino.pageName</t>
+          <t>sports.pageName</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>લાઈવ કેસિનો</t>
+          <t>રમતગમત</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sports.pageName</t>
+          <t>leaderboard.pageName</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>રમતગમત</t>
+          <t>લીડરબોર્ડ</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>leaderboard.pageName</t>
+          <t>multiladder.pageName</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>લીડરબોર્ડ</t>
+          <t>મલ્ટી લેડર</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>multiladder.pageName</t>
+          <t>promotions.pageName</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>મલ્ટી લેડર</t>
+          <t>પ્રમોશન્સ</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>multiladder.pageDescription</t>
+          <t>jackpot.pageName</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IPL બોનસ લેડરમાં આગળ વધો અને વાસ્તવિક રોકડ ઇનામો મેળવો.</t>
+          <t>જેકપોટ</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>promotions.pageName</t>
+          <t>jackpotWinners.pageName</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>પ્રમોશન્સ</t>
+          <t>જેકપોટ વિજેતાઓ</t>
         </is>
       </c>
     </row>
@@ -994,46 +994,46 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>jackpot.pageName</t>
+          <t>cms.defaultPageName</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>જેકપોટ</t>
+          <t>પેજ</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>seo</t>
+          <t>common</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jackpotWinners.pageName</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>જેકપોટ વિજેતાઓ</t>
+          <t>સબમિટ કરો</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>seo</t>
+          <t>common</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>cms.defaultPageName</t>
+          <t>submitting</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>પેજ</t>
+          <t>સબમિટ થઈ રહ્યું છે…</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>loading</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>સબમિટ કરો</t>
+          <t>લોડ થઈ રહ્યું છે</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>submitting</t>
+          <t>edit</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>સબમિટ થઈ રહ્યું છે…</t>
+          <t>સંપાદિત કરો</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>loading</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>લોડ થઈ રહ્યું છે</t>
+          <t>રદ કરો</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>close</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>સંપાદિત કરો</t>
+          <t>બંધ કરો</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>retry</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>રદ કરો</t>
+          <t>ફરી પ્રયાસ કરો</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>close</t>
+          <t>tryAgain</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>બંધ કરો</t>
+          <t>ફરી પ્રયાસ કરો</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>retry</t>
+          <t>goBackHome</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ફરી પ્રયાસ કરો</t>
+          <t>હોમ પર પાછા જાઓ</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>tryAgain</t>
+          <t>readMore</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ફરી પ્રયાસ કરો</t>
+          <t>વધુ વાંચો</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>goBackHome</t>
+          <t>seeAll</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>હોમ પર પાછા જાઓ</t>
+          <t>બધું જુઓ</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>readMore</t>
+          <t>pick</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>વધુ વાંચો</t>
+          <t>પસંદ કરો</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>seeAll</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>બધું જુઓ</t>
+          <t>ઠીક છે</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>pick</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>પસંદ કરો</t>
+          <t>અથવા</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>of</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ઠીક છે</t>
+          <t>નો</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>or</t>
+          <t>update</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>અથવા</t>
+          <t>અપડેટ કરો</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>of</t>
+          <t>updating</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>નો</t>
+          <t>અપડેટ થઈ રહ્યું છે…</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>અપડેટ કરો</t>
+          <t>હા</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>updating</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>અપડેટ થઈ રહ્યું છે…</t>
+          <t>ના</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>copied</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>હા</t>
+          <t>કૉપી થઈ ગયું</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>copy</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ના</t>
+          <t>કૉપી કરો</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>copied</t>
+          <t>gotIt</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>કૉપી થઈ ગયું</t>
+          <t>સમજી ગયું!</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>copy</t>
+          <t>downloadImage</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>કૉપી કરો</t>
+          <t>છબી ડાઉનલોડ કરો</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>gotIt</t>
+          <t>notAvailable</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>સમજી ગયું!</t>
+          <t>ઉપલબ્ધ નથી</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>downloadImage</t>
+          <t>total</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>છબી ડાઉનલોડ કરો</t>
+          <t>કુલ</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>notAvailable</t>
+          <t>goToSlide</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ઉપલબ્ધ નથી</t>
+          <t>સ્લાઇડ {{index}} પર જાઓ</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>logoAlt</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>કુલ</t>
+          <t>લોગો</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>goToSlide</t>
+          <t>whatsappCta</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>સ્લાઇડ {{index}} પર જાઓ</t>
+          <t>WhatsApp પર તમારી ID મેળવો</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>logoAlt</t>
+          <t>noDataAvailable</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>લોગો</t>
+          <t>કોઈ ડેટા ઉપલબ્ધ નથી</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>whatsappCta</t>
+          <t>creditedToWallet</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>WhatsApp પર તમારી ID મેળવો</t>
+          <t>તમારા વૉલેટમાં જમા કરવામાં આવ્યું</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>noDataAvailable</t>
+          <t>imageUpload.preview</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>કોઈ ડેટા ઉપલબ્ધ નથી</t>
+          <t>પૂર્વાવલોકન</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>creditedToWallet</t>
+          <t>imageUpload.imagePreviewAlt</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>તમારા વૉલેટમાં જમા કરવામાં આવ્યું</t>
+          <t>અપલોડ કરેલી રસીદ પૂર્વાવલોકન</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>imageUpload.preview</t>
+          <t>imageUpload.modalImageAlt</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>પૂર્વાવલોકન</t>
+          <t>રસીદ પૂર્વાવલોકન</t>
         </is>
       </c>
     </row>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>imageUpload.imagePreviewAlt</t>
+          <t>imageUpload.removeImage</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>અપલોડ કરેલી રસીદ પૂર્વાવલોકન</t>
+          <t>છબી દૂર કરો</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>imageUpload.modalImageAlt</t>
+          <t>imageUpload.clickToUpload</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>રસીદ પૂર્વાવલોકન</t>
+          <t>અપલોડ કરવા ક્લિક કરો</t>
         </is>
       </c>
     </row>
@@ -1606,12 +1606,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>imageUpload.removeImage</t>
+          <t>imageUpload.dragAndDrop</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>છબી દૂર કરો</t>
+          <t>અથવા ખેંચો અને છોડો</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>imageUpload.clickToUpload</t>
+          <t>imageUpload.fileTypesHint</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>અપલોડ કરવા ક્લિક કરો</t>
+          <t>JPG, JPEG, PNG અથવા SVG (મહત્તમ 1MB)</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>imageUpload.dragAndDrop</t>
+          <t>imageUpload.browseFiles</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>અથવા ખેંચો અને છોડો</t>
+          <t>ફાઇલ બ્રાઉઝ કરો</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>imageUpload.fileTypesHint</t>
+          <t>imageUpload.toastInvalidFileTypeErr</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>JPG, JPEG, PNG અથવા SVG (મહત્તમ 1MB)</t>
+          <t>માત્ર JPG, JPEG, PNG અને SVG ફાઇલો માન્ય છે.</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>imageUpload.browseFiles</t>
+          <t>imageUpload.toastFileSizeExceededErr</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ફાઇલ બ્રાઉઝ કરો</t>
+          <t>ફાઇલ કદ 1MB ની મર્યાદા કરતાં વધી ગઈ છે.</t>
         </is>
       </c>
     </row>
@@ -1691,12 +1691,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>imageUpload.toastInvalidFileTypeErr</t>
+          <t>imageUpload.toastValidFileErr</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>માત્ર JPG, JPEG, PNG અને SVG ફાઇલો માન્ય છે.</t>
+          <t>કૃપા કરીને પ્રથમ માન્ય ફાઇલ પસંદ કરો.</t>
         </is>
       </c>
     </row>
@@ -1708,12 +1708,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>imageUpload.toastFileSizeExceededErr</t>
+          <t>imageUpload.toastNoFileErr</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ફાઇલ કદ 1MB ની મર્યાદા કરતાં વધી ગઈ છે.</t>
+          <t>કોઈ ફાઇલ પસંદ નથી</t>
         </is>
       </c>
     </row>
@@ -1725,12 +1725,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>imageUpload.toastValidFileErr</t>
+          <t>banner.defaultAlt</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>કૃપા કરીને પ્રથમ માન્ય ફાઇલ પસંદ કરો.</t>
+          <t>બૅનર {{index}}</t>
         </is>
       </c>
     </row>
@@ -1742,12 +1742,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>imageUpload.toastNoFileErr</t>
+          <t>timeLeft.dayLeft</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>કોઈ ફાઇલ પસંદ નથી</t>
+          <t>{{count}} દિવસ બાકી</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>banner.defaultAlt</t>
+          <t>timeLeft.daysLeft</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>બૅનર {{index}}</t>
+          <t>{{count}} દિવસ બાકી</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>timeLeft.dayLeft</t>
+          <t>timeLeft.hoursLeft</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{{count}} દિવસ બાકી</t>
+          <t>{{count}} કલાક બાકી</t>
         </is>
       </c>
     </row>
@@ -1793,12 +1793,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>timeLeft.daysLeft</t>
+          <t>timeLeft.minsLeft</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{{count}} દિવસ બાકી</t>
+          <t>{{count}} મિનિટ બાકી</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>timeLeft.hoursLeft</t>
+          <t>timeLeft.expired</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{{count}} કલાક બાકી</t>
+          <t>સમય સમાપ્ત</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>timeLeft.minsLeft</t>
+          <t>days.mo</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{{count}} મિનિટ બાકી</t>
+          <t>સો</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>timeLeft.expired</t>
+          <t>days.tu</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>સમય સમાપ્ત</t>
+          <t>મં</t>
         </is>
       </c>
     </row>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>days.mo</t>
+          <t>days.we</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>સો</t>
+          <t>બુ</t>
         </is>
       </c>
     </row>
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>days.tu</t>
+          <t>days.th</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>મં</t>
+          <t>ગુ</t>
         </is>
       </c>
     </row>
@@ -1895,12 +1895,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>days.we</t>
+          <t>days.fr</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>બુ</t>
+          <t>શુ</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>days.th</t>
+          <t>days.sa</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ગુ</t>
+          <t>શ</t>
         </is>
       </c>
     </row>
@@ -1929,46 +1929,46 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>days.fr</t>
+          <t>days.su</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>શુ</t>
+          <t>ર</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>days.sa</t>
+          <t>login.title</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>શ</t>
+          <t>લૉગ ઇન</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>days.su</t>
+          <t>login.usernamePlaceholder</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ર</t>
+          <t>વપરાશકર્તા નામ</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>login.title</t>
+          <t>login.passwordPlaceholder</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>લૉગ ઇન</t>
+          <t>પાસવર્ડ</t>
         </is>
       </c>
     </row>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>login.usernamePlaceholder</t>
+          <t>login.forgotPassword</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>વપરાશકર્તા નામ</t>
+          <t>પાસવર્ડ ભૂલ્યા?</t>
         </is>
       </c>
     </row>
@@ -2014,12 +2014,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>login.passwordPlaceholder</t>
+          <t>login.submitIdle</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>પાસવર્ડ</t>
+          <t>હવે લૉગ ઇન કરો</t>
         </is>
       </c>
     </row>
@@ -2031,12 +2031,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>login.forgotPassword</t>
+          <t>login.submitLoading</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>પાસવર્ડ ભૂલ્યા?</t>
+          <t>લૉગ ઇન થઈ રહ્યું છે…</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2048,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>login.submitIdle</t>
+          <t>login.noAccount</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>હવે લૉગ ઇન કરો</t>
+          <t>ખાતું નથી?</t>
         </is>
       </c>
     </row>
@@ -2065,12 +2065,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>login.submitLoading</t>
+          <t>login.registerNow</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>લૉગ ઇન થઈ રહ્યું છે…</t>
+          <t>હવે નોંધણી કરો</t>
         </is>
       </c>
     </row>
@@ -2082,12 +2082,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>login.noAccount</t>
+          <t>login.whatsappCta</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ખાતું નથી?</t>
+          <t>WhatsApp પર તમારી ID મેળવો</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>login.registerNow</t>
+          <t>login.bannerAltPrefix</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>હવે નોંધણી કરો</t>
+          <t>લૉગ ઇન બૅનર</t>
         </is>
       </c>
     </row>
@@ -2116,12 +2116,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>login.whatsappCta</t>
+          <t>login.toastSuccess</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>WhatsApp પર તમારી ID મેળવો</t>
+          <t>લૉગ ઇન સફળ</t>
         </is>
       </c>
     </row>
@@ -2133,12 +2133,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>login.bannerAltPrefix</t>
+          <t>login.toastError</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>લૉગ ઇન બૅનર</t>
+          <t>લૉગ ઇન નિષ્ફળ</t>
         </is>
       </c>
     </row>
@@ -2150,12 +2150,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>login.toastSuccess</t>
+          <t>login.validation.usernameRequired</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>લૉગ ઇન સફળ</t>
+          <t>વપરાશકર્તા નામ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -2167,12 +2167,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>login.toastError</t>
+          <t>login.validation.usernameMinLength</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>લૉગ ઇન નિષ્ફળ</t>
+          <t>ઓછામાં ઓછા 3 અક્ષર</t>
         </is>
       </c>
     </row>
@@ -2184,12 +2184,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>login.validation.usernameRequired</t>
+          <t>login.validation.usernameMaxLength</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>વપરાશકર્તા નામ જરૂરી છે</t>
+          <t>16 અક્ષરથી વધુ ન હોઈ શકે</t>
         </is>
       </c>
     </row>
@@ -2201,12 +2201,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>login.validation.usernameMinLength</t>
+          <t>login.validation.usernameNoSpaces</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ઓછામાં ઓછા 3 અક્ષર</t>
+          <t>વપરાશકર્તા નામમાં ખાલી જગ્યા માન્ય નથી</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>login.validation.usernameMaxLength</t>
+          <t>login.validation.passwordRequired</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>16 અક્ષરથી વધુ ન હોઈ શકે</t>
+          <t>પાસવર્ડ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -2235,12 +2235,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>login.validation.usernameNoSpaces</t>
+          <t>login.validation.passwordPattern</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>વપરાશકર્તા નામમાં ખાલી જગ્યા માન્ય નથી</t>
+          <t>પાસવર્ડ 8–15 અક્ષરનો હોવો જોઈએ, જેમાં અપરકેઝ, લોઅરકેઝ, સંખ્યા અને વિશેષ અક્ષર હોવા જોઈએ</t>
         </is>
       </c>
     </row>
@@ -2252,12 +2252,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>login.validation.passwordRequired</t>
+          <t>login.validation.showPassword</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>પાસવર્ડ જરૂરી છે</t>
+          <t>પાસવર્ડ બતાવો</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>login.validation.passwordPattern</t>
+          <t>login.validation.hidePassword</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>પાસવર્ડ 8–15 અક્ષરનો હોવો જોઈએ, જેમાં અપરકેઝ, લોઅરકેઝ, સંખ્યા અને વિશેષ અક્ષર હોવા જોઈએ</t>
+          <t>પાસવર્ડ છુપાવો</t>
         </is>
       </c>
     </row>
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>login.validation.showPassword</t>
+          <t>register.title</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>પાસવર્ડ બતાવો</t>
+          <t>નોંધણી</t>
         </is>
       </c>
     </row>
@@ -2303,12 +2303,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>login.validation.hidePassword</t>
+          <t>register.usernamePlaceholder</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>પાસવર્ડ છુપાવો</t>
+          <t>વપરાશકર્તા નામ</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>register.title</t>
+          <t>register.passwordPlaceholder</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>નોંધણી</t>
+          <t>પાસવર્ડ</t>
         </is>
       </c>
     </row>
@@ -2337,12 +2337,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>register.usernamePlaceholder</t>
+          <t>register.confirmPasswordPlaceholder</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>વપરાશકર્તા નામ</t>
+          <t>પાસવર્ડ ની પુષ્ટિ કરો</t>
         </is>
       </c>
     </row>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>register.passwordPlaceholder</t>
+          <t>register.promoCodePlaceholder</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>પાસવર્ડ</t>
+          <t>પ્રોમો કોડ (વૈકલ્પિક)</t>
         </is>
       </c>
     </row>
@@ -2371,12 +2371,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>register.confirmPasswordPlaceholder</t>
+          <t>register.countryPlaceholder</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>પાસવર્ડ ની પુષ્ટિ કરો</t>
+          <t>દેશ</t>
         </is>
       </c>
     </row>
@@ -2388,12 +2388,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>register.promoCodePlaceholder</t>
+          <t>register.mobileNumberPlaceholder</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>પ્રોમો કોડ (વૈકલ્પિક)</t>
+          <t>મોબાઇલ નંબર</t>
         </is>
       </c>
     </row>
@@ -2405,12 +2405,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>register.countryPlaceholder</t>
+          <t>register.checkboxAge</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>દેશ</t>
+          <t>હું ઓછામાં ઓછો 18 વર્ષનો/ની છું</t>
         </is>
       </c>
     </row>
@@ -2422,12 +2422,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>register.mobileNumberPlaceholder</t>
+          <t>register.checkboxTerms</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>મોબાઇલ નંબર</t>
+          <t>હું શરતો અને ગોપનીયતા સ્વીકારું છું</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>register.checkboxAge</t>
+          <t>register.submitIdle</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>હું ઓછામાં ઓછો 18 વર્ષનો/ની છું</t>
+          <t>હવે નોંધણી કરો</t>
         </is>
       </c>
     </row>
@@ -2456,12 +2456,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>register.checkboxTerms</t>
+          <t>register.submitLoading</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>હું શરતો અને ગોપનીયતા સ્વીકારું છું</t>
+          <t>નોંધણી થઈ રહી છે...</t>
         </is>
       </c>
     </row>
@@ -2473,12 +2473,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>register.submitIdle</t>
+          <t>register.whatsappCta</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>હવે નોંધણી કરો</t>
+          <t>WhatsApp પર તમારી ID મેળવો</t>
         </is>
       </c>
     </row>
@@ -2490,12 +2490,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>register.submitLoading</t>
+          <t>register.bannerAltPrefix</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>નોંધણી થઈ રહી છે...</t>
+          <t>નોંધણી બૅનર</t>
         </is>
       </c>
     </row>
@@ -2507,12 +2507,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>register.whatsappCta</t>
+          <t>register.toastSuccess</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>WhatsApp પર તમારી ID મેળવો</t>
+          <t>સફળતાપૂર્વક નોંધણી થઈ</t>
         </is>
       </c>
     </row>
@@ -2524,12 +2524,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>register.bannerAltPrefix</t>
+          <t>register.toastError</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>નોંધણી બૅનર</t>
+          <t>નોંધણી નિષ્ફળ</t>
         </is>
       </c>
     </row>
@@ -2541,12 +2541,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>register.toastSuccess</t>
+          <t>register.validation.usernameRequired</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>સફળતાપૂર્વક નોંધણી થઈ</t>
+          <t>વપરાશકર્તા નામ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>register.toastError</t>
+          <t>register.validation.usernameMinLength</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>નોંધણી નિષ્ફળ</t>
+          <t>ઓછામાં ઓછા 3 અક્ષર</t>
         </is>
       </c>
     </row>
@@ -2575,12 +2575,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>register.validation.usernameRequired</t>
+          <t>register.validation.usernameMaxLength</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>વપરાશકર્તા નામ જરૂરી છે</t>
+          <t>મહત્તમ 16 અક્ષર</t>
         </is>
       </c>
     </row>
@@ -2592,12 +2592,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>register.validation.usernameMinLength</t>
+          <t>register.validation.usernameNoSpaces</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ઓછામાં ઓછા 3 અક્ષર</t>
+          <t>વપરાશકર્તા નામમાં ખાલી જગ્યા માન્ય નથી</t>
         </is>
       </c>
     </row>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>register.validation.usernameMaxLength</t>
+          <t>register.validation.passwordRequired</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>મહત્તમ 16 અક્ષર</t>
+          <t>પાસવર્ડ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -2626,12 +2626,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>register.validation.usernameNoSpaces</t>
+          <t>register.validation.passwordPattern</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>વપરાશકર્તા નામમાં ખાલી જગ્યા માન્ય નથી</t>
+          <t>8–15 અક્ષર, અપરકેઝ, લોઅરકેઝ, સંખ્યા અને વિશેષ અક્ષર સહિત હોવા જોઈએ</t>
         </is>
       </c>
     </row>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>register.validation.passwordRequired</t>
+          <t>register.validation.confirmPasswordRequired</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>પાસવર્ડ જરૂરી છે</t>
+          <t>પાસવર્ડ ની પુષ્ટિ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>register.validation.passwordPattern</t>
+          <t>register.validation.confirmPasswordMismatch</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>8–15 અક્ષર, અપરકેઝ, લોઅરકેઝ, સંખ્યા અને વિશેષ અક્ષર સહિત હોવા જોઈએ</t>
+          <t>પાસવર્ડ મેળ ખાતા નથી</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>register.validation.confirmPasswordRequired</t>
+          <t>register.validation.countryRequired</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>પાસવર્ડ ની પુષ્ટિ જરૂરી છે</t>
+          <t>દેશ કોડ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -2694,12 +2694,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>register.validation.confirmPasswordMismatch</t>
+          <t>register.validation.mobileNumberRequired</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>પાસવર્ડ મેળ ખાતા નથી</t>
+          <t>મોબાઇલ નંબર જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -2711,12 +2711,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>register.validation.countryRequired</t>
+          <t>register.validation.mobileNumberInvalid</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>દેશ કોડ જરૂરી છે</t>
+          <t>અમાન્ય નંબર</t>
         </is>
       </c>
     </row>
@@ -2728,12 +2728,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>register.validation.mobileNumberRequired</t>
+          <t>register.validation.ageRequired</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>મોબાઇલ નંબર જરૂરી છે</t>
+          <t>18+ વર્ષ હોવા જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -2745,12 +2745,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>register.validation.mobileNumberInvalid</t>
+          <t>register.validation.termsRequired</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>અમાન્ય નંબર</t>
+          <t>શરતો સ્વીકારવી જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -2762,12 +2762,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>register.validation.ageRequired</t>
+          <t>register.validation.showPassword</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>18+ વર્ષ હોવા જરૂરી છે</t>
+          <t>પાસવર્ડ બતાવો</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>register.validation.termsRequired</t>
+          <t>register.validation.hidePassword</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>શરતો સ્વીકારવી જરૂરી છે</t>
+          <t>પાસવર્ડ છુપાવો</t>
         </is>
       </c>
     </row>
@@ -2796,12 +2796,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>register.validation.showPassword</t>
+          <t>register.validation.showConfirmPassword</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>પાસવર્ડ બતાવો</t>
+          <t>પુષ્ટિ પાસવર્ડ બતાવો</t>
         </is>
       </c>
     </row>
@@ -2813,46 +2813,46 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>register.validation.hidePassword</t>
+          <t>register.validation.hideConfirmPassword</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>પાસવર્ડ છુપાવો</t>
+          <t>પુષ્ટિ પાસવર્ડ છુપાવો</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>auth</t>
+          <t>deviceLogout</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>register.validation.showConfirmPassword</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>પુષ્ટિ પાસવર્ડ બતાવો</t>
+          <t>ચેતવણી</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>auth</t>
+          <t>deviceLogout</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>register.validation.hideConfirmPassword</t>
+          <t>noPermission</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>પુષ્ટિ પાસવર્ડ છુપાવો</t>
+          <t>આ એક્સેસ કરવાની તમારી પાસે પરવાનગી નથી.</t>
         </is>
       </c>
     </row>
@@ -2864,46 +2864,46 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>sessionExpired</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ચેતવણી</t>
+          <t>તમારો સત્ર સમાપ્ત થઈ ગયો છે. કૃપા કરીને ફરીથી લૉગ ઇન કરો.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>deviceLogout</t>
+          <t>games</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>noPermission</t>
+          <t>noGamesTitle</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>આ એક્સેસ કરવાની તમારી પાસે પરવાનગી નથી.</t>
+          <t>કોઈ રમત ઉપલબ્ધ નથી</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>deviceLogout</t>
+          <t>games</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>sessionExpired</t>
+          <t>noGamesDescription</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>તમારો સત્ર સમાપ્ત થઈ ગયો છે. કૃપા કરીને ફરીથી લૉગ ઇન કરો.</t>
+          <t>કોઈ રમત ઉપલબ્ધ નથી. કૃપા કરીને પાછળથી તપાસો.</t>
         </is>
       </c>
     </row>
@@ -2915,12 +2915,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>noGamesTitle</t>
+          <t>exploreButton</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>કોઈ રમત ઉપલબ્ધ નથી</t>
+          <t>રમતો એક્સ્પ્લોર કરો</t>
         </is>
       </c>
     </row>
@@ -2932,12 +2932,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>noGamesDescription</t>
+          <t>allGameProviders</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>કોઈ રમત ઉપલબ્ધ નથી. કૃપા કરીને પાછળથી તપાસો.</t>
+          <t>બધા ગેમ પ્રૉવાઇડર</t>
         </is>
       </c>
     </row>
@@ -2949,12 +2949,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>exploreButton</t>
+          <t>searchGames</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>રમતો એક્સ્પ્લોર કરો</t>
+          <t>રમતો શોધો...</t>
         </is>
       </c>
     </row>
@@ -2966,12 +2966,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>allGameProviders</t>
+          <t>pleaseWait</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>બધા ગેમ પ્રૉવાઇડર</t>
+          <t>કૃપા રાહ જુઓ...</t>
         </is>
       </c>
     </row>
@@ -2983,12 +2983,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>searchGames</t>
+          <t>searchGamesAriaLabel</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>રમતો શોધો...</t>
+          <t>રમતો શોધો</t>
         </is>
       </c>
     </row>
@@ -3000,12 +3000,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>pleaseWait</t>
+          <t>toasts.fetchDetailsError</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>કૃપા રાહ જુઓ...</t>
+          <t>ગેમ વિગત મેળવવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
@@ -3017,12 +3017,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>searchGamesAriaLabel</t>
+          <t>toasts.refreshError</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>રમતો શોધો</t>
+          <t>રમતો રિફ્રેશ કરવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
@@ -3034,12 +3034,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>toasts.fetchDetailsError</t>
+          <t>toasts.failedToFetchGame</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ગેમ વિગત મેળવવામાં નિષ્ફળ.</t>
+          <t>ગેમ મેળવવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
@@ -3051,12 +3051,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>toasts.refreshError</t>
+          <t>toasts.failedToChangeProvider</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>રમતો રિફ્રેશ કરવામાં નિષ્ફળ.</t>
+          <t>પ્રૉવાઇડર બદલવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
@@ -3068,46 +3068,46 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>toasts.failedToFetchGame</t>
+          <t>toasts.failedToLoadMoreGames</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>ગેમ મેળવવામાં નિષ્ફળ.</t>
+          <t>વધુ ગેમ્સ લોડ કરવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>games</t>
+          <t>accountSettings</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>toasts.failedToChangeProvider</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>પ્રૉવાઇડર બદલવામાં નિષ્ફળ.</t>
+          <t>એકાઉન્ટ સેટિંગ્સ</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>games</t>
+          <t>accountSettings</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>toasts.failedToLoadMoreGames</t>
+          <t>tabs.depositLimit</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>વધુ ગેમ્સ લોડ કરવામાં નિષ્ફળ.</t>
+          <t>ડિપૉઝિટ મર્યાદા</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>tabs.contactPreference</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>એકાઉન્ટ સેટિંગ્સ</t>
+          <t>સંપર્ક પ્રાધાન્ય</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>tabs.depositLimit</t>
+          <t>tabs.changePassword</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ મર્યાદા</t>
+          <t>પાસવર્ડ બદલો</t>
         </is>
       </c>
     </row>
@@ -3153,12 +3153,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>tabs.contactPreference</t>
+          <t>tabs.selfExclusion</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>સંપર્ક પ્રાધાન્ય</t>
+          <t>સ્વ-બાકાત</t>
         </is>
       </c>
     </row>
@@ -3170,12 +3170,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>tabs.changePassword</t>
+          <t>tabs.deactivate</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>પાસવર્ડ બદલો</t>
+          <t>નિષ્ક્રિય કરો</t>
         </is>
       </c>
     </row>
@@ -3187,12 +3187,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>tabs.selfExclusion</t>
+          <t>changePassword.newPasswordPlaceholder</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>સ્વ-બાકાત</t>
+          <t>નવો પાસવર્ડ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -3204,12 +3204,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>tabs.deactivate</t>
+          <t>changePassword.confirmPasswordPlaceholder</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>નિષ્ક્રિય કરો</t>
+          <t>પુષ્ટિ પાસવર્ડ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -3221,12 +3221,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>changePassword.newPasswordPlaceholder</t>
+          <t>changePassword.hint1</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>નવો પાસવર્ડ દાખલ કરો</t>
+          <t>પાસવર્ડ 8-16 અક્ષરનો હોવો જોઈએ, જેમાં ઓછામાં ઓછો એક લોઅરકેઝ, એક અપરકેઝ, એક સંખ્યા અને એક વિશેષ અક્ષર હોવો જોઈએ, ખાલી જગ્યા વિના.</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>changePassword.confirmPasswordPlaceholder</t>
+          <t>changePassword.hint2</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>પુષ્ટિ પાસવર્ડ દાખલ કરો</t>
+          <t>નવો પાસવર્ડ અને પુષ્ટિ પાસવર્ડ મેળ ખાવા જોઈએ.</t>
         </is>
       </c>
     </row>
@@ -3255,12 +3255,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>changePassword.hint1</t>
+          <t>changePassword.toastSuccess</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>પાસવર્ડ 8-16 અક્ષરનો હોવો જોઈએ, જેમાં ઓછામાં ઓછો એક લોઅરકેઝ, એક અપરકેઝ, એક સંખ્યા અને એક વિશેષ અક્ષર હોવો જોઈએ, ખાલી જગ્યા વિના.</t>
+          <t>પાસવર્ડ સફળતાપૂર્વક અપડેટ થઈ ગયો.</t>
         </is>
       </c>
     </row>
@@ -3272,12 +3272,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>changePassword.hint2</t>
+          <t>changePassword.toastError</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>નવો પાસવર્ડ અને પુષ્ટિ પાસવર્ડ મેળ ખાવા જોઈએ.</t>
+          <t>પાસવર્ડ અપડેટ કરવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
@@ -3289,12 +3289,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>changePassword.toastSuccess</t>
+          <t>changePassword.validation.passwordRequired</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>પાસવર્ડ સફળતાપૂર્વક અપડેટ થઈ ગયો.</t>
+          <t>પાસવર્ડ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -3306,12 +3306,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>changePassword.toastError</t>
+          <t>changePassword.validation.passwordMinLength</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>પાસવર્ડ અપડેટ કરવામાં નિષ્ફળ.</t>
+          <t>પાસવર્ડ ઓછામાં ઓછા 8 અક્ષરનો હોવો જોઈએ</t>
         </is>
       </c>
     </row>
@@ -3323,12 +3323,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>changePassword.validation.passwordRequired</t>
+          <t>changePassword.validation.passwordPattern</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>પાસવર્ડ જરૂરી છે</t>
+          <t>અપરકેઝ, લોઅરકેઝ, સંખ્યા અને વિશેષ અક્ષર સામેલ હોવા જોઈએ</t>
         </is>
       </c>
     </row>
@@ -3340,12 +3340,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>changePassword.validation.passwordMinLength</t>
+          <t>changePassword.validation.confirmRequired</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>પાસવર્ડ ઓછામાં ઓછા 8 અક્ષરનો હોવો જોઈએ</t>
+          <t>કૃપા કરીને તમારો પાસવર્ડ ની પુષ્ટિ કરો</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>changePassword.validation.passwordPattern</t>
+          <t>changePassword.validation.confirmMismatch</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>અપરકેઝ, લોઅરકેઝ, સંખ્યા અને વિશેષ અક્ષર સામેલ હોવા જોઈએ</t>
+          <t>પાસવર્ડ મેળ ખાતા નથી</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>changePassword.validation.confirmRequired</t>
+          <t>contactPreference.labels.all</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>કૃપા કરીને તમારો પાસવર્ડ ની પુષ્ટિ કરો</t>
+          <t>બધા</t>
         </is>
       </c>
     </row>
@@ -3391,12 +3391,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>changePassword.validation.confirmMismatch</t>
+          <t>contactPreference.labels.email</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>પાસવર્ડ મેળ ખાતા નથી</t>
+          <t>ઇ-મેઇલ</t>
         </is>
       </c>
     </row>
@@ -3408,12 +3408,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>contactPreference.labels.all</t>
+          <t>contactPreference.labels.whatsapp</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>બધા</t>
+          <t>WhatsApp</t>
         </is>
       </c>
     </row>
@@ -3425,12 +3425,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>contactPreference.labels.email</t>
+          <t>contactPreference.labels.telegram</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>ઇ-મેઇલ</t>
+          <t>Telegram</t>
         </is>
       </c>
     </row>
@@ -3442,12 +3442,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>contactPreference.labels.whatsapp</t>
+          <t>contactPreference.labels.sms</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>SMS</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>contactPreference.labels.telegram</t>
+          <t>contactPreference.labels.call</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>કૉલ</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>contactPreference.labels.sms</t>
+          <t>contactPreference.labels.none</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>SMS</t>
+          <t>કોઈ નહીં</t>
         </is>
       </c>
     </row>
@@ -3493,12 +3493,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>contactPreference.labels.call</t>
+          <t>contactPreference.toastSuccess</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>કૉલ</t>
+          <t>સંપર્ક સેટિંગ્સ સફળતાપૂર્વક અપડેટ થઈ.</t>
         </is>
       </c>
     </row>
@@ -3510,12 +3510,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>contactPreference.labels.none</t>
+          <t>contactPreference.toastError</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>કોઈ નહીં</t>
+          <t>સંપર્ક સેટિંગ્સ અપડેટ કરવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
@@ -3527,12 +3527,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>contactPreference.toastSuccess</t>
+          <t>depositLimit.dailyLabel</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>સંપર્ક સેટિંગ્સ સફળતાપૂર્વક અપડેટ થઈ.</t>
+          <t>દૈનિક ડિપૉઝિટ મર્યાદા</t>
         </is>
       </c>
     </row>
@@ -3544,12 +3544,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>contactPreference.toastError</t>
+          <t>depositLimit.weeklyLabel</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>સંપર્ક સેટિંગ્સ અપડેટ કરવામાં નિષ્ફળ.</t>
+          <t>સાપ્તાહિક ડિપૉઝિટ મર્યાદા</t>
         </is>
       </c>
     </row>
@@ -3561,12 +3561,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>depositLimit.dailyLabel</t>
+          <t>depositLimit.monthlyLabel</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>દૈનિક ડિપૉઝિટ મર્યાદા</t>
+          <t>માસિક ડિપૉઝિટ મર્યાદા</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>depositLimit.weeklyLabel</t>
+          <t>depositLimit.hint1</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>સાપ્તાહિક ડિપૉઝિટ મર્યાદા</t>
+          <t>ડિપૉઝિટ મર્યાદા સક્ષમ કરવાથી વપરાશકર્તા ચોક્કસ સમયગાળા માટે ડિપૉઝિટ કરવાથી પ્રતિબંધિત થઈ શકે છે. એકવાર મર્યાદા સેટ થઈ ગઈ, ત્યારે નિર્ધારિત સમય સમાપ્ત ન થાય ત્યાં સુધી વપરાશકર્તા કોઈ ડિપૉઝિટ કરી શકશે નહીં.</t>
         </is>
       </c>
     </row>
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>depositLimit.monthlyLabel</t>
+          <t>depositLimit.hint2</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>માસિક ડિપૉઝિટ મર્યાદા</t>
+          <t>જો તમે આ ડિપૉઝિટ મર્યાદા લાગુ કરવા ઇચ્છો, તો સમયગાળો અને જે રકમ ઓળંગવી ન ઇચ્છો તે પસંદ કરી શકો છો.</t>
         </is>
       </c>
     </row>
@@ -3612,12 +3612,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>depositLimit.hint1</t>
+          <t>depositLimit.toastSuccess</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ મર્યાદા સક્ષમ કરવાથી વપરાશકર્તા ચોક્કસ સમયગાળા માટે ડિપૉઝિટ કરવાથી પ્રતિબંધિત થઈ શકે છે. એકવાર મર્યાદા સેટ થઈ ગઈ, ત્યારે નિર્ધારિત સમય સમાપ્ત ન થાય ત્યાં સુધી વપરાશકર્તા કોઈ ડિપૉઝિટ કરી શકશે નહીં.</t>
+          <t>ડિપૉઝિટ મર્યાદા સફળતાપૂર્વક અપડેટ થઈ.</t>
         </is>
       </c>
     </row>
@@ -3629,12 +3629,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>depositLimit.hint2</t>
+          <t>depositLimit.toastError</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>જો તમે આ ડિપૉઝિટ મર્યાદા લાગુ કરવા ઇચ્છો, તો સમયગાળો અને જે રકમ ઓળંગવી ન ઇચ્છો તે પસંદ કરી શકો છો.</t>
+          <t>ડિપૉઝિટ મર્યાદા અપડેટ કરવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
@@ -3646,12 +3646,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>depositLimit.toastSuccess</t>
+          <t>depositLimit.validation.dailyExceedsWeeklyOrMonthly</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ મર્યાદા સફળતાપૂર્વક અપડેટ થઈ.</t>
+          <t>દૈનિક મર્યાદા સાપ્તાહિક અથવા માસિક મર્યાદા કરતાં વધારે ન હોઈ શકે.</t>
         </is>
       </c>
     </row>
@@ -3663,12 +3663,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>depositLimit.toastError</t>
+          <t>depositLimit.validation.weeklyOutOfRange</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ મર્યાદા અપડેટ કરવામાં નિષ્ફળ.</t>
+          <t>સાપ્તાહિક મર્યાદા દૈનિક અને માસિક મર્યાદાની વચ્ચે હોવી જોઈએ.</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>depositLimit.validation.dailyExceedsWeeklyOrMonthly</t>
+          <t>depositLimit.validation.monthlyTooSmall</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>દૈનિક મર્યાદા સાપ્તાહિક અથવા માસિક મર્યાદા કરતાં વધારે ન હોઈ શકે.</t>
+          <t>માસિક મર્યાદા દૈનિક અથવા સાપ્તાહિક મર્યાદા કરતાં નાની ન હોઈ શકે.</t>
         </is>
       </c>
     </row>
@@ -3697,12 +3697,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>depositLimit.validation.weeklyOutOfRange</t>
+          <t>selfExclusion.checkboxLabel</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>સાપ્તાહિક મર્યાદા દૈનિક અને માસિક મર્યાદાની વચ્ચે હોવી જોઈએ.</t>
+          <t>હું મારા ખાતાને આ સમય માટે સ્વ-બાકાત કરવા ઇચ્છું છું:</t>
         </is>
       </c>
     </row>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>depositLimit.validation.monthlyTooSmall</t>
+          <t>selfExclusion.selectPlaceholder</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>માસિક મર્યાદા દૈનિક અથવા સાપ્તાહિક મર્યાદા કરતાં નાની ન હોઈ શકે.</t>
+          <t>સમયગાળો પસંદ કરો</t>
         </is>
       </c>
     </row>
@@ -3731,12 +3731,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>selfExclusion.checkboxLabel</t>
+          <t>selfExclusion.toastSuccess</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>હું મારા ખાતાને આ સમય માટે સ્વ-બાકાત કરવા ઇચ્છું છું:</t>
+          <t>તમારું ખાતું {{timePeriod}} માટે સ્વ-બાકાત કરવામાં આવ્યું છે.</t>
         </is>
       </c>
     </row>
@@ -3748,12 +3748,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>selfExclusion.selectPlaceholder</t>
+          <t>selfExclusion.hint</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>સમયગાળો પસંદ કરો</t>
+          <t>આ સમયગાળા દરમિયાન તમે વેબસાઇટ પર રમી નહીં શકો અને કોઈ માર્કેટિંગ ઇ-મેઇલ અથવા પ્રોમોશન પ્રાપ્ત નહીં થાય.</t>
         </is>
       </c>
     </row>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>selfExclusion.toastSuccess</t>
+          <t>selfExclusion.confirmText</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>તમારું ખાતું {{timePeriod}} માટે સ્વ-બાકાત કરવામાં આવ્યું છે.</t>
+          <t>શું તમે ખરેખર {{timePeriod}} માટે તમારા ખાતાને સ્વ-બાકાત કરવા ઇચ્છો છો?</t>
         </is>
       </c>
     </row>
@@ -3782,12 +3782,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>selfExclusion.hint</t>
+          <t>selfExclusion.periods.1 day</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>આ સમયગાળા દરમિયાન તમે વેબસાઇટ પર રમી નહીં શકો અને કોઈ માર્કેટિંગ ઇ-મેઇલ અથવા પ્રોમોશન પ્રાપ્ત નહીં થાય.</t>
+          <t>1 દિવસ</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>selfExclusion.confirmText</t>
+          <t>selfExclusion.periods.1 week</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>શું તમે ખરેખર {{timePeriod}} માટે તમારા ખાતાને સ્વ-બાકાત કરવા ઇચ્છો છો?</t>
+          <t>1 અઠવાડિયું</t>
         </is>
       </c>
     </row>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>selfExclusion.periods.1 day</t>
+          <t>selfExclusion.periods.1 month</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>1 દિવસ</t>
+          <t>1 મહિનો</t>
         </is>
       </c>
     </row>
@@ -3833,12 +3833,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>selfExclusion.periods.1 week</t>
+          <t>selfExclusion.periods.6 weeks</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>1 અઠવાડિયું</t>
+          <t>6 અઠવાડિયા</t>
         </is>
       </c>
     </row>
@@ -3850,12 +3850,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>selfExclusion.periods.1 month</t>
+          <t>selfExclusion.periods.undetermined</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>1 મહિનો</t>
+          <t>અનિર્ધારિત</t>
         </is>
       </c>
     </row>
@@ -3867,12 +3867,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>selfExclusion.periods.6 weeks</t>
+          <t>deactivate.checkboxLabel</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>6 અઠવાડિયા</t>
+          <t>હું મારા ખાતાને આ સમય માટે સ્વ-બાકાત કરવા ઇચ્છું છું:</t>
         </is>
       </c>
     </row>
@@ -3884,12 +3884,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>selfExclusion.periods.undetermined</t>
+          <t>deactivate.selectPlaceholder</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>અનિર્ધારિત</t>
+          <t>સમયગાળો પસંદ કરો</t>
         </is>
       </c>
     </row>
@@ -3901,12 +3901,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>deactivate.checkboxLabel</t>
+          <t>deactivate.hint</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>હું મારા ખાતાને આ સમય માટે સ્વ-બાકાત કરવા ઇચ્છું છું:</t>
+          <t>આ સમય દરમિયાન તમે તમારા ખાતામાં સાઇન ઇન કરી નહીં શકો અથવા અસાધારણ સંજોગો સિવાય ખાતું ફરી સક્ષમ નહીં કરી શકો. નિષ્ક્રિય સમય સમાપ્ત થયા પછી, તમને સ્ટ્રેચ ઑપ્શન આપવામાં આવશે. બધા ફૉન્ડ્સ પ્રત્યાર્પણ કરવામાં આવશે અને બધા દાવ રદ્દ ગણાશે.</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>deactivate.selectPlaceholder</t>
+          <t>deactivate.toastSuccess</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>સમયગાળો પસંદ કરો</t>
+          <t>નિષ્ક્રિય સ્ટેટ સફળતાપૂર્વક અપડેટ થઈ.</t>
         </is>
       </c>
     </row>
@@ -3935,46 +3935,46 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>deactivate.hint</t>
+          <t>deactivate.toastError</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>આ સમય દરમિયાન તમે તમારા ખાતામાં સાઇન ઇન કરી નહીં શકો અથવા અસાધારણ સંજોગો સિવાય ખાતું ફરી સક્ષમ નહીં કરી શકો. નિષ્ક્રિય સમય સમાપ્ત થયા પછી, તમને સ્ટ્રેચ ઑપ્શન આપવામાં આવશે. બધા ફૉન્ડ્સ પ્રત્યાર્પણ કરવામાં આવશે અને બધા દાવ રદ્દ ગણાશે.</t>
+          <t>ખાતું નિષ્ક્રિય કરવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>accountSettings</t>
+          <t>deposit</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>deactivate.toastSuccess</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>નિષ્ક્રિય સ્ટેટ સફળતાપૂર્વક અપડેટ થઈ.</t>
+          <t>ડિપૉઝિટ</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>accountSettings</t>
+          <t>deposit</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>deactivate.toastError</t>
+          <t>selectAmount</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>ખાતું નિષ્ક્રિય કરવામાં નિષ્ફળ.</t>
+          <t>રકમ પસંદ કરો</t>
         </is>
       </c>
     </row>
@@ -3986,12 +3986,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>helpText</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ</t>
+          <t>મદદ જોઈએ? ડિપૉઝિટ માર્ગદર્શિકા જુઓ અથવા અમને લાઇવ ચૅટ / ઇ-મેઇલ પર સંપર્ક કરો.</t>
         </is>
       </c>
     </row>
@@ -4003,12 +4003,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>selectAmount</t>
+          <t>enterAmount</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>રકમ પસંદ કરો</t>
+          <t>રકમ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -4020,12 +4020,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>helpText</t>
+          <t>bonusCode</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>મદદ જોઈએ? ડિપૉઝિટ માર્ગદર્શિકા જુઓ અથવા અમને લાઇવ ચૅટ / ઇ-મેઇલ પર સંપર્ક કરો.</t>
+          <t>બોનસ કોડ</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>enterAmount</t>
+          <t>bonusCodePlaceholder</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>રકમ દાખલ કરો</t>
+          <t>બોનસ કોડ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>bonusCode</t>
+          <t>bankLimitText</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>બોનસ કોડ</t>
+          <t>બૅન્ક મર્યાદા : ₹{{limit}}</t>
         </is>
       </c>
     </row>
@@ -4071,12 +4071,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>bonusCodePlaceholder</t>
+          <t>paymentMethods.bank</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>બોનસ કોડ દાખલ કરો</t>
+          <t>બૅન્ક ટ્રાન્સફર</t>
         </is>
       </c>
     </row>
@@ -4088,12 +4088,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>bankLimitText</t>
+          <t>paymentMethods.qr</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>બૅન્ક મર્યાદા : ₹{{limit}}</t>
+          <t>QR ટ્રાન્સફર</t>
         </is>
       </c>
     </row>
@@ -4105,12 +4105,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>paymentMethods.bank</t>
+          <t>paymentMethods.upi</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>બૅન્ક ટ્રાન્સફર</t>
+          <t>UPI</t>
         </is>
       </c>
     </row>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>paymentMethods.qr</t>
+          <t>paymentMethods.azeePay</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>QR ટ્રાન્સફર</t>
+          <t>Azee Pay</t>
         </is>
       </c>
     </row>
@@ -4139,12 +4139,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>paymentMethods.upi</t>
+          <t>azeePayAlt</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>UPI</t>
+          <t>azee-pay</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>paymentMethods.azeePay</t>
+          <t>toastSuccess</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Azee Pay</t>
+          <t>ડિપૉઝિટ સફળ.</t>
         </is>
       </c>
     </row>
@@ -4173,12 +4173,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>azeePayAlt</t>
+          <t>paymentDetailsTitle</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>azee-pay</t>
+          <t>તમારી ચુકવણી વિગત</t>
         </is>
       </c>
     </row>
@@ -4190,12 +4190,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>toastSuccess</t>
+          <t>enterUtr</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ સફળ.</t>
+          <t>UTR નંબર દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -4207,12 +4207,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>paymentDetailsTitle</t>
+          <t>whatsappCta</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>તમારી ચુકવણી વિગત</t>
+          <t>ડિપૉઝિટ માટે WhatsApp કરો</t>
         </is>
       </c>
     </row>
@@ -4224,12 +4224,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>enterUtr</t>
+          <t>transferDetails</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>UTR નંબર દાખલ કરો</t>
+          <t>ટ્રાન્સફર વિગત</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4241,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>whatsappCta</t>
+          <t>previousPromotion</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ માટે WhatsApp કરો</t>
+          <t>પહેલાનું પ્રોમોશન</t>
         </is>
       </c>
     </row>
@@ -4258,12 +4258,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>transferDetails</t>
+          <t>nextPromotion</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>ટ્રાન્સફર વિગત</t>
+          <t>આગળનું પ્રોમોશન</t>
         </is>
       </c>
     </row>
@@ -4275,12 +4275,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>previousPromotion</t>
+          <t>qrCodeAlt</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>પહેલાનું પ્રોમોશન</t>
+          <t>QR કોડ</t>
         </is>
       </c>
     </row>
@@ -4292,12 +4292,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>nextPromotion</t>
+          <t>transferLabels.qrCode</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>આગળનું પ્રોમોશન</t>
+          <t>QR કોડ</t>
         </is>
       </c>
     </row>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>qrCodeAlt</t>
+          <t>transferLabels.qrName</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>QR કોડ</t>
+          <t>QR નામ</t>
         </is>
       </c>
     </row>
@@ -4326,12 +4326,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>transferLabels.qrCode</t>
+          <t>transferLabels.id</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>QR કોડ</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>transferLabels.qrName</t>
+          <t>transferLabels.upiId</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>QR નામ</t>
+          <t>UPI ID</t>
         </is>
       </c>
     </row>
@@ -4360,12 +4360,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>transferLabels.id</t>
+          <t>transferLabels.upiName</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>UPI નામ</t>
         </is>
       </c>
     </row>
@@ -4377,12 +4377,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>transferLabels.upiId</t>
+          <t>transferLabels.paymentUpiName</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>UPI ID</t>
+          <t>ચુકવણી UPI નામ</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>transferLabels.upiName</t>
+          <t>transferLabels.bankName</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>UPI નામ</t>
+          <t>બૅન્ક નામ</t>
         </is>
       </c>
     </row>
@@ -4411,12 +4411,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>transferLabels.paymentUpiName</t>
+          <t>transferLabels.accountHolderName</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>ચુકવણી UPI નામ</t>
+          <t>ખાતા ધારકનું નામ</t>
         </is>
       </c>
     </row>
@@ -4428,12 +4428,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>transferLabels.bankName</t>
+          <t>transferLabels.accountNumber</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>બૅન્ક નામ</t>
+          <t>ખાતા નંબર</t>
         </is>
       </c>
     </row>
@@ -4445,12 +4445,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>transferLabels.accountHolderName</t>
+          <t>transferLabels.accountType</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>ખાતા ધારકનું નામ</t>
+          <t>ખાતા પ્રકાર</t>
         </is>
       </c>
     </row>
@@ -4462,12 +4462,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>transferLabels.accountNumber</t>
+          <t>transferLabels.ifscCode</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>ખાતા નંબર</t>
+          <t>IFSC કોડ</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>transferLabels.accountType</t>
+          <t>transferLabels.branch</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>ખાતા પ્રકાર</t>
+          <t>શાખા</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4496,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>transferLabels.ifscCode</t>
+          <t>campaign.title</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>IFSC કોડ</t>
+          <t>પ્રોમોશન્સ</t>
         </is>
       </c>
     </row>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>transferLabels.branch</t>
+          <t>campaign.giftAlt</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>શાખા</t>
+          <t>ભેટ</t>
         </is>
       </c>
     </row>
@@ -4530,12 +4530,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>campaign.title</t>
+          <t>campaign.minDepositLimitLabel</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>પ્રોમોશન્સ</t>
+          <t>ન્યૂનતમ ડિપૉઝિટ મર્યાદા: ₹{{limit}}</t>
         </is>
       </c>
     </row>
@@ -4547,12 +4547,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>campaign.giftAlt</t>
+          <t>campaign.claimUntil</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>ભેટ</t>
+          <t>ક્લેઇમ ક્યાં સુધી: {{date}}</t>
         </is>
       </c>
     </row>
@@ -4564,12 +4564,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>campaign.minDepositLimitLabel</t>
+          <t>campaign.applyCode</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>ન્યૂનતમ ડિપૉઝિટ મર્યાદા: ₹{{limit}}</t>
+          <t>કોડ લાગુ કરો</t>
         </is>
       </c>
     </row>
@@ -4581,12 +4581,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>campaign.claimUntil</t>
+          <t>campaign.noContent</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>ક્લેઇમ ક્યાં સુધી: {{date}}</t>
+          <t>કોઈ સામગ્રી ઉપલબ્ધ નથી</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>campaign.applyCode</t>
+          <t>psp.paymentVerifying</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>કોડ લાગુ કરો</t>
+          <t>ચુકવણી ચકાસાઈ રહી છે…</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>campaign.noContent</t>
+          <t>psp.continueToPay</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>કોઈ સામગ્રી ઉપલબ્ધ નથી</t>
+          <t>ચુકવણી ચાલુ રાખો</t>
         </is>
       </c>
     </row>
@@ -4632,12 +4632,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>psp.paymentVerifying</t>
+          <t>psp.toastSuccess</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>ચુકવણી ચકાસાઈ રહી છે…</t>
+          <t>ડિપૉઝિટ સફળતાપૂર્વક પ્રક્રિયા થઈ</t>
         </is>
       </c>
     </row>
@@ -4649,12 +4649,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>psp.continueToPay</t>
+          <t>psp.toastProcessedCheckSupport</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>ચુકવણી ચાલુ રાખો</t>
+          <t>ડિપૉઝિટ પ્રક્રિયા થઈ. કૃપા કરીને સહાય ટીમ સાથે ચકાસો</t>
         </is>
       </c>
     </row>
@@ -4666,12 +4666,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>psp.toastSuccess</t>
+          <t>psp.toastUnableToVerify</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ સફળતાપૂર્વક પ્રક્રિયા થઈ</t>
+          <t>ચુકવણી ચકાસી શકાઈ નહીં</t>
         </is>
       </c>
     </row>
@@ -4683,12 +4683,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>psp.toastProcessedCheckSupport</t>
+          <t>psp.toastVerifyingPayment</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ પ્રક્રિયા થઈ. કૃપા કરીને સહાય ટીમ સાથે ચકાસો</t>
+          <t>ચુકવણી ચકાસી રહ્યા છીએ...</t>
         </is>
       </c>
     </row>
@@ -4700,12 +4700,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>psp.toastUnableToVerify</t>
+          <t>psp.toastSomethingWentWrong</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>ચુકવણી ચકાસી શકાઈ નહીં</t>
+          <t>કંઈક ખોટું થયું</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>psp.toastVerifyingPayment</t>
+          <t>validation.toastAmountGreaterThanZero</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>ચુકવણી ચકાસી રહ્યા છીએ...</t>
+          <t>રકમ 0 કરતાં વધારે હોવી જોઈએ</t>
         </is>
       </c>
     </row>
@@ -4734,12 +4734,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>psp.toastSomethingWentWrong</t>
+          <t>validation.amountExceedsLimit</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>કંઈક ખોટું થયું</t>
+          <t>રકમ ₹{{limit}} ની મર્યાદા કરતાં વધી ગઈ</t>
         </is>
       </c>
     </row>
@@ -4751,12 +4751,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>validation.toastAmountGreaterThanZero</t>
+          <t>validation.minDepositRequired</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>રકમ 0 કરતાં વધારે હોવી જોઈએ</t>
+          <t>ઓછામાં ઓછી {{min}} ની ડિપૉઝિટ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -4768,46 +4768,46 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>validation.amountExceedsLimit</t>
+          <t>validation.toastUtrRequired</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>રકમ ₹{{limit}} ની મર્યાદા કરતાં વધી ગઈ</t>
+          <t>કૃપા કરીને UTR નંબર દાખલ કરો</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>deposit</t>
+          <t>withdraw</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>validation.minDepositRequired</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>ઓછામાં ઓછી {{min}} ની ડિપૉઝિટ જરૂરી છે</t>
+          <t>ઉપાડ</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>deposit</t>
+          <t>withdraw</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>validation.toastUtrRequired</t>
+          <t>withdrawableMoney</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>કૃપા કરીને UTR નંબર દાખલ કરો</t>
+          <t>ઉપાડ બૅલૅન્સ</t>
         </is>
       </c>
     </row>
@@ -4819,12 +4819,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>selectBankPlaceholder</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>ઉપાડ</t>
+          <t>બૅન્ક ખાતું પસંદ કરો</t>
         </is>
       </c>
     </row>
@@ -4836,12 +4836,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>withdrawableMoney</t>
+          <t>enterAmountPlaceholder</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>ઉપાડ બૅલૅન્સ</t>
+          <t>રકમ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>selectBankPlaceholder</t>
+          <t>whatsappCta</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>બૅન્ક ખાતું પસંદ કરો</t>
+          <t>WhatsApp દ્વારા ઉપાડ</t>
         </is>
       </c>
     </row>
@@ -4870,12 +4870,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>enterAmountPlaceholder</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>રકમ દાખલ કરો</t>
+          <t>ઉપાડ કરો</t>
         </is>
       </c>
     </row>
@@ -4887,12 +4887,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>whatsappCta</t>
+          <t>submitting</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>WhatsApp દ્વારા ઉપાડ</t>
+          <t>ઉપાડ થઈ રહ્યો છે…</t>
         </is>
       </c>
     </row>
@@ -4904,12 +4904,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>validation.bankRequired</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>ઉપાડ કરો</t>
+          <t>બૅન્ક ખાતું પસંદ કરો</t>
         </is>
       </c>
     </row>
@@ -4921,12 +4921,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>submitting</t>
+          <t>validation.amountRequired</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>ઉપાડ થઈ રહ્યો છે…</t>
+          <t>રકમ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>validation.bankRequired</t>
+          <t>validation.amountNumbersOnly</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>બૅન્ક ખાતું પસંદ કરો</t>
+          <t>રકમ ફક્ત સંખ્યા ધરાવવી જોઈએ</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>validation.amountRequired</t>
+          <t>validation.amountExceedsMax</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>રકમ જરૂરી છે</t>
+          <t>તમે મહત્તમ ₹{{max}} ઉપાડ કરી શકો છો</t>
         </is>
       </c>
     </row>
@@ -4972,12 +4972,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>validation.amountNumbersOnly</t>
+          <t>validation.amountMinimum</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>રકમ ફક્ત સંખ્યા ધરાવવી જોઈએ</t>
+          <t>રકમ ₹500 કરતાં વધારે હોવી જોઈએ</t>
         </is>
       </c>
     </row>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>validation.amountExceedsMax</t>
+          <t>toasts.success</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>તમે મહત્તમ ₹{{max}} ઉપાડ કરી શકો છો</t>
+          <t>રકમ સફળતાપૂર્વક ઉપાડવામાં આવી.</t>
         </is>
       </c>
     </row>
@@ -5006,46 +5006,46 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>validation.amountMinimum</t>
+          <t>toasts.error</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>રકમ ₹500 કરતાં વધારે હોવી જોઈએ</t>
+          <t>ઉપાડ પ્રક્રિયા કરવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>withdraw</t>
+          <t>wallet</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>toasts.success</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>રકમ સફળતાપૂર્વક ઉપાડવામાં આવી.</t>
+          <t>વૉલેટ</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>withdraw</t>
+          <t>wallet</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>toasts.error</t>
+          <t>realMoney</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>ઉપાડ પ્રક્રિયા કરવામાં નિષ્ફળ.</t>
+          <t>રિઅલ મની ₹ {{amount}}</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>withdrawableMoney</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>વૉલેટ</t>
+          <t>ઉપાડ યોગ્ય મની ₹ {{amount}}</t>
         </is>
       </c>
     </row>
@@ -5074,46 +5074,46 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>realMoney</t>
+          <t>moneySuffix</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>રિઅલ મની ₹ {{amount}}</t>
+          <t>{{wallet}} મની</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>wallet</t>
+          <t>bonus</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>withdrawableMoney</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>ઉપાડ યોગ્ય મની ₹ {{amount}}</t>
+          <t>બોનસ</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>wallet</t>
+          <t>bonus</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>moneySuffix</t>
+          <t>tabs.active</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>{{wallet}} મની</t>
+          <t>સક્રિય બોનસ</t>
         </is>
       </c>
     </row>
@@ -5125,12 +5125,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>tabs.unclaimed</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>બોનસ</t>
+          <t>ક્લૅઇમ ન કરેલો બોનસ</t>
         </is>
       </c>
     </row>
@@ -5142,12 +5142,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>tabs.active</t>
+          <t>tabs.redeemed</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>સક્રિય બોનસ</t>
+          <t>રિડીમ કરેલો બોનસ</t>
         </is>
       </c>
     </row>
@@ -5159,12 +5159,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>tabs.unclaimed</t>
+          <t>toastExpired</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>ક્લૅઇમ ન કરેલો બોનસ</t>
+          <t>કૅમ્પેઇન સમય સમાપ્ત</t>
         </is>
       </c>
     </row>
@@ -5176,12 +5176,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>tabs.redeemed</t>
+          <t>toastError</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>રિડીમ કરેલો બોનસ</t>
+          <t>કૅમ્પેઇન સમાપ્ત કરવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
@@ -5193,12 +5193,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>toastExpired</t>
+          <t>noCampaigns</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>કૅમ્પેઇન સમય સમાપ્ત</t>
+          <t>કોઈ કૅમ્પેઇન ઉપલબ્ધ નથી. કૃપા કરીને પાછળથી તપાસો.</t>
         </is>
       </c>
     </row>
@@ -5210,12 +5210,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>toastError</t>
+          <t>campaignName</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>કૅમ્પેઇન સમાપ્ત કરવામાં નિષ્ફળ.</t>
+          <t>કૅમ્પેઇન નામ</t>
         </is>
       </c>
     </row>
@@ -5227,12 +5227,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>noCampaigns</t>
+          <t>campaignCode</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>કોઈ કૅમ્પેઇન ઉપલબ્ધ નથી. કૃપા કરીને પાછળથી તપાસો.</t>
+          <t>કૅમ્પેઇન કોડ</t>
         </is>
       </c>
     </row>
@@ -5244,12 +5244,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>campaignName</t>
+          <t>minOdds</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>કૅમ્પેઇન નામ</t>
+          <t>ન્યૂનતમ ઑડ્ઝ</t>
         </is>
       </c>
     </row>
@@ -5261,12 +5261,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>campaignCode</t>
+          <t>bonusAmount</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>કૅમ્પેઇન કોડ</t>
+          <t>બોનસ રકમ</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>minOdds</t>
+          <t>bonusPercentage</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>ન્યૂનતમ ઑડ્ઝ</t>
+          <t>બોનસ ટકાવારી</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>bonusAmount</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>બોનસ રકમ</t>
+          <t>ચેતવણી</t>
         </is>
       </c>
     </row>
@@ -5312,46 +5312,46 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>bonusPercentage</t>
+          <t>cancelConfirm</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>બોનસ ટકાવારી</t>
+          <t>શું તમે ખરેખર બોનસ રદ કરવા ઇચ્છો છો?</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>bonus</t>
+          <t>kyc</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>ચેતવણી</t>
+          <t>KYC</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>bonus</t>
+          <t>kyc</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>cancelConfirm</t>
+          <t>subtitle</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>શું તમે ખરેખર બોનસ રદ કરવા ઇચ્છો છો?</t>
+          <t>KYC અપડેટ કરો</t>
         </is>
       </c>
     </row>
@@ -5363,12 +5363,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>documentTypeLabel</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>KYC</t>
+          <t>દસ્તાવેજ પ્રકાર</t>
         </is>
       </c>
     </row>
@@ -5380,12 +5380,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>subtitle</t>
+          <t>documentNumberLabel</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>KYC અપડેટ કરો</t>
+          <t>દસ્તાવેજ નંબર</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>documentTypeLabel</t>
+          <t>documentTypePlaceholder</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>દસ્તાવેજ પ્રકાર</t>
+          <t>દસ્તાવેજ પ્રકાર દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>documentNumberLabel</t>
+          <t>documentNumberPlaceholder</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>દસ્તાવેજ નંબર</t>
+          <t>દસ્તાવેજ નંબર દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -5431,12 +5431,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>documentTypePlaceholder</t>
+          <t>frontImageLabel</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>દસ્તાવેજ પ્રકાર દાખલ કરો</t>
+          <t>આગળની છબી</t>
         </is>
       </c>
     </row>
@@ -5448,12 +5448,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>documentNumberPlaceholder</t>
+          <t>backImageLabel</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>દસ્તાવેજ નંબર દાખલ કરો</t>
+          <t>પાછળની છબી</t>
         </is>
       </c>
     </row>
@@ -5465,12 +5465,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>frontImageLabel</t>
+          <t>save</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>આગળની છબી</t>
+          <t>સાચવો</t>
         </is>
       </c>
     </row>
@@ -5482,12 +5482,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>backImageLabel</t>
+          <t>saving</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>પાછળની છબી</t>
+          <t>સાચવી રહ્યા છીએ…</t>
         </is>
       </c>
     </row>
@@ -5499,12 +5499,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>save</t>
+          <t>toastSuccess</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>સાચવો</t>
+          <t>KYC સફળતાપૂર્વક અપડેટ થઈ.</t>
         </is>
       </c>
     </row>
@@ -5516,12 +5516,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>saving</t>
+          <t>toastError</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>સાચવી રહ્યા છીએ…</t>
+          <t>KYC અપડેટ કરવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
@@ -5533,12 +5533,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>toastSuccess</t>
+          <t>toastAlreadyVerified</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>KYC સફળતાપૂર્વક અપડેટ થઈ.</t>
+          <t>KYC પહેલેથી ચકાસાઈ ગઈ છે</t>
         </is>
       </c>
     </row>
@@ -5550,12 +5550,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>toastError</t>
+          <t>toastPending</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>KYC અપડેટ કરવામાં નિષ્ફળ.</t>
+          <t>KYC સ્ટેટ્સ પ્રતીક્ષારત છે</t>
         </is>
       </c>
     </row>
@@ -5567,12 +5567,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>toastAlreadyVerified</t>
+          <t>toastRejected</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>KYC પહેલેથી ચકાસાઈ ગઈ છે</t>
+          <t>KYC નકારી કઢાઈ</t>
         </is>
       </c>
     </row>
@@ -5584,12 +5584,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>toastPending</t>
+          <t>validation.documentTypeRequired</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>KYC સ્ટેટ્સ પ્રતીક્ષારત છે</t>
+          <t>કૃપા કરીને દસ્તાવેજ પ્રકાર પસંદ કરો</t>
         </is>
       </c>
     </row>
@@ -5601,12 +5601,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>toastRejected</t>
+          <t>validation.documentNumberRequired</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>KYC નકારી કઢાઈ</t>
+          <t>કૃપા કરીને તમારો દસ્તાવેજ નંબર દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>validation.documentTypeRequired</t>
+          <t>validation.aadharInvalid</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>કૃપા કરીને દસ્તાવેજ પ્રકાર પસંદ કરો</t>
+          <t>માન્ય 12-અંકનો આધાર નંબર દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -5635,12 +5635,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>validation.documentNumberRequired</t>
+          <t>validation.panInvalid</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>કૃપા કરીને તમારો દસ્તાવેજ નંબર દાખલ કરો</t>
+          <t>માન્ય PAN નંબર દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -5652,12 +5652,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>validation.aadharInvalid</t>
+          <t>validation.frontImageRequired</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>માન્ય 12-અંકનો આધાર નંબર દાખલ કરો</t>
+          <t>આગળની છબી જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -5669,46 +5669,46 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>validation.panInvalid</t>
+          <t>validation.backImageRequired</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>માન્ય PAN નંબર દાખલ કરો</t>
+          <t>પાછળની છબી જરૂરી છે</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>kyc</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>validation.frontImageRequired</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>આગળની છબી જરૂરી છે</t>
+          <t>પ્રૉફાઇલ</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>kyc</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>validation.backImageRequired</t>
+          <t>yourPersonalData</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>પાછળની છબી જરૂરી છે</t>
+          <t>તમારો વ્યક્તિગત ડેટા</t>
         </is>
       </c>
     </row>
@@ -5720,12 +5720,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>updatePersonalData</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>પ્રૉફાઇલ</t>
+          <t>વ્યક્તિગત વિગત અપડેટ કરો</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>yourPersonalData</t>
+          <t>fields.firstName</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>તમારો વ્યક્તિગત ડેટા</t>
+          <t>પ્રથમ નામ</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>updatePersonalData</t>
+          <t>fields.lastName</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>વ્યક્તિગત વિગત અપડેટ કરો</t>
+          <t>છેલ્લું નામ</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>fields.firstName</t>
+          <t>fields.userName</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>પ્રથમ નામ</t>
+          <t>વપરાશકર્તા નામ</t>
         </is>
       </c>
     </row>
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>fields.lastName</t>
+          <t>fields.email</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>છેલ્લું નામ</t>
+          <t>ઇ-મેઇલ</t>
         </is>
       </c>
     </row>
@@ -5805,12 +5805,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>fields.userName</t>
+          <t>fields.dateOfBirth</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>વપરાશકર્તા નામ</t>
+          <t>જન્મ તારીખ</t>
         </is>
       </c>
     </row>
@@ -5822,12 +5822,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>fields.email</t>
+          <t>fields.city</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>ઇ-મેઇલ</t>
+          <t>શહેર</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>fields.dateOfBirth</t>
+          <t>fields.country</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>જન્મ તારીખ</t>
+          <t>દેશ</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>fields.city</t>
+          <t>fields.state</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>શહેર</t>
+          <t>રાજ્ય</t>
         </is>
       </c>
     </row>
@@ -5873,12 +5873,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>fields.country</t>
+          <t>fields.countryCode</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>દેશ</t>
+          <t>દેશ કોડ</t>
         </is>
       </c>
     </row>
@@ -5890,12 +5890,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>fields.state</t>
+          <t>fields.phone</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>રાજ્ય</t>
+          <t>ફોન નંબર</t>
         </is>
       </c>
     </row>
@@ -5907,12 +5907,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>fields.countryCode</t>
+          <t>fields.address</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>દેશ કોડ</t>
+          <t>સરનામું</t>
         </is>
       </c>
     </row>
@@ -5924,12 +5924,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>fields.phone</t>
+          <t>fields.currency</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>ફોન નંબર</t>
+          <t>ચલણ</t>
         </is>
       </c>
     </row>
@@ -5941,12 +5941,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>fields.address</t>
+          <t>fields.zipCode</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>સરનામું</t>
+          <t>ઝિપ કોડ</t>
         </is>
       </c>
     </row>
@@ -5958,12 +5958,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>fields.currency</t>
+          <t>validation.firstNameRequired</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>ચલણ</t>
+          <t>તમારું પ્રથમ નામ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -5975,12 +5975,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>fields.zipCode</t>
+          <t>validation.firstNameMaxLength</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>ઝિપ કોડ</t>
+          <t>પ્રથમ નામ 10 અક્ષરથી વધુ ન હોઈ શકે</t>
         </is>
       </c>
     </row>
@@ -5992,12 +5992,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>validation.firstNameRequired</t>
+          <t>validation.lastNameRequired</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>તમારું પ્રથમ નામ દાખલ કરો</t>
+          <t>તમારું છેલ્લું નામ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -6009,12 +6009,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>validation.firstNameMaxLength</t>
+          <t>validation.lastNameMaxLength</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>પ્રથમ નામ 10 અક્ષરથી વધુ ન હોઈ શકે</t>
+          <t>છેલ્લું નામ 10 અક્ષરથી વધુ ન હોઈ શકે</t>
         </is>
       </c>
     </row>
@@ -6026,12 +6026,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>validation.lastNameRequired</t>
+          <t>validation.emailPattern</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>તમારું છેલ્લું નામ દાખલ કરો</t>
+          <t>માન્ય ઇ-મેઇલ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -6043,12 +6043,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>validation.lastNameMaxLength</t>
+          <t>validation.dobRequired</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>છેલ્લું નામ 10 અક્ષરથી વધુ ન હોઈ શકે</t>
+          <t>તમારી જન્મ તારીખ પસંદ કરો</t>
         </is>
       </c>
     </row>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>validation.emailPattern</t>
+          <t>validation.countryCodeRequired</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>માન્ય ઇ-મેઇલ દાખલ કરો</t>
+          <t>દેશ કોડ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>validation.dobRequired</t>
+          <t>validation.zipCodeRequired</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>તમારી જન્મ તારીખ પસંદ કરો</t>
+          <t>કૃપા કરીને પિનકોડ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -6094,12 +6094,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>validation.countryCodeRequired</t>
+          <t>toasts.success</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>દેશ કોડ દાખલ કરો</t>
+          <t>ખેલાડીની વિગત સફળતાપૂર્વક અપડેટ થઈ</t>
         </is>
       </c>
     </row>
@@ -6111,80 +6111,80 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>validation.zipCodeRequired</t>
+          <t>toasts.error</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>કૃપા કરીને પિનકોડ દાખલ કરો</t>
+          <t>ખેલાડીની પ્રૉફાઇલ અપડેટ કરવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>promotions</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>toasts.success</t>
+          <t>noPromotions</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>ખેલાડીની વિગત સફળતાપૂર્વક અપડેટ થઈ</t>
+          <t>કોઈ પ્રોમોશન ઉપલબ્ધ નથી.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>promotions</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>toasts.error</t>
+          <t>imageAlt</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>ખેલાડીની પ્રૉફાઇલ અપડેટ કરવામાં નિષ્ફળ.</t>
+          <t>promotion_card_image</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>promotions</t>
+          <t>bankInfo</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>noPromotions</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>કોઈ પ્રોમોશન ઉપલબ્ધ નથી.</t>
+          <t>બૅન્ક માહિતી</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>promotions</t>
+          <t>bankInfo</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>imageAlt</t>
+          <t>bankDetailsTitle</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>promotion_card_image</t>
+          <t>તમારો બૅન્ક ડેટા</t>
         </is>
       </c>
     </row>
@@ -6196,12 +6196,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>labels.accountNo</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>બૅન્ક માહિતી</t>
+          <t>ખાતા નંબર</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>bankDetailsTitle</t>
+          <t>labels.bankName</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>તમારો બૅન્ક ડેટા</t>
+          <t>બૅન્ક નામ</t>
         </is>
       </c>
     </row>
@@ -6230,12 +6230,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>labels.accountNo</t>
+          <t>labels.branchName</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>ખાતા નંબર</t>
+          <t>શાખા નામ</t>
         </is>
       </c>
     </row>
@@ -6247,12 +6247,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>labels.bankName</t>
+          <t>labels.ifscCode</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>બૅન્ક નામ</t>
+          <t>IFSC કોડ</t>
         </is>
       </c>
     </row>
@@ -6264,12 +6264,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>labels.branchName</t>
+          <t>labels.accountType</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>શાખા નામ</t>
+          <t>ખાતા પ્રકાર</t>
         </is>
       </c>
     </row>
@@ -6281,12 +6281,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>labels.ifscCode</t>
+          <t>labels.accountHolderName</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>IFSC કોડ</t>
+          <t>ખાતા ધારકનું નામ</t>
         </is>
       </c>
     </row>
@@ -6298,12 +6298,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>labels.accountType</t>
+          <t>labels.amount</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>ખાતા પ્રકાર</t>
+          <t>રકમ</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>labels.accountHolderName</t>
+          <t>labels.email</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>ખાતા ધારકનું નામ</t>
+          <t>ઇ-મેઇલ સરનામું</t>
         </is>
       </c>
     </row>
@@ -6332,12 +6332,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>labels.amount</t>
+          <t>placeholders.selectAccount</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>રકમ</t>
+          <t>બૅન્ક ખાતું પસંદ કરો</t>
         </is>
       </c>
     </row>
@@ -6349,12 +6349,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>labels.email</t>
+          <t>placeholders.enterAccountNo</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>ઇ-મેઇલ સરનામું</t>
+          <t>ખાતા નંબર દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -6366,12 +6366,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>placeholders.selectAccount</t>
+          <t>placeholders.enterBankName</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>બૅન્ક ખાતું પસંદ કરો</t>
+          <t>બૅન્ક નામ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -6383,12 +6383,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>placeholders.enterAccountNo</t>
+          <t>placeholders.enterAccountHolderName</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>ખાતા નંબર દાખલ કરો</t>
+          <t>ખાતા ધારકનું નામ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -6400,12 +6400,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>placeholders.enterBankName</t>
+          <t>placeholders.enterBranchName</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>બૅન્ક નામ દાખલ કરો</t>
+          <t>શાખા નામ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>placeholders.enterAccountHolderName</t>
+          <t>placeholders.enterIfscCode</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>ખાતા ધારકનું નામ દાખલ કરો</t>
+          <t>IFSC કોડ દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -6434,12 +6434,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>placeholders.enterBranchName</t>
+          <t>placeholders.enterAccountType</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>શાખા નામ દાખલ કરો</t>
+          <t>ખાતા પ્રકાર દાખલ કરો</t>
         </is>
       </c>
     </row>
@@ -6451,12 +6451,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>placeholders.enterIfscCode</t>
+          <t>placeholders.savings</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>IFSC કોડ દાખલ કરો</t>
+          <t>બચત</t>
         </is>
       </c>
     </row>
@@ -6468,12 +6468,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>placeholders.enterAccountType</t>
+          <t>placeholders.current</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>ખાતા પ્રકાર દાખલ કરો</t>
+          <t>ચાલુ</t>
         </is>
       </c>
     </row>
@@ -6485,12 +6485,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>placeholders.savings</t>
+          <t>validation.accountNoRequired</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>બચત</t>
+          <t>ખાતા નંબર જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -6502,12 +6502,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>placeholders.current</t>
+          <t>validation.accountNoNumbersOnly</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>ચાલુ</t>
+          <t>ખાતા નંબર ફક્ત સંખ્યા ધરાવવો જોઈએ</t>
         </is>
       </c>
     </row>
@@ -6519,12 +6519,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>validation.accountNoRequired</t>
+          <t>validation.accountNoMaxLength</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>ખાતા નંબર જરૂરી છે</t>
+          <t>ખાતા નંબર 16 અંક કરતાં વધુ ન હોઈ શકે</t>
         </is>
       </c>
     </row>
@@ -6536,12 +6536,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>validation.accountNoNumbersOnly</t>
+          <t>validation.accountNoDuplicate</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>ખાતા નંબર ફક્ત સંખ્યા ધરાવવો જોઈએ</t>
+          <t>આ ખાતા નંબર પહેલેથી નોંધાયેલ છે.</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>validation.accountNoMaxLength</t>
+          <t>validation.bankNameRequired</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>ખાતા નંબર 16 અંક કરતાં વધુ ન હોઈ શકે</t>
+          <t>બૅન્ક નામ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>validation.accountNoDuplicate</t>
+          <t>validation.accountHolderNameRequired</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>આ ખાતા નંબર પહેલેથી નોંધાયેલ છે.</t>
+          <t>ખાતા ધારકનું નામ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -6587,12 +6587,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>validation.bankNameRequired</t>
+          <t>validation.branchNameRequired</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>બૅન્ક નામ જરૂરી છે</t>
+          <t>શાખા નામ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -6604,12 +6604,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>validation.accountHolderNameRequired</t>
+          <t>validation.ifscCodeRequired</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>ખાતા ધારકનું નામ જરૂરી છે</t>
+          <t>IFSC કોડ જરૂરી છે</t>
         </is>
       </c>
     </row>
@@ -6621,12 +6621,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>validation.branchNameRequired</t>
+          <t>validation.ifscCodeInvalid</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>શાખા નામ જરૂરી છે</t>
+          <t>માન્ય IFSC કોડ દાખલ કરો (4 અક્ષર + 7 અંક)</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>validation.ifscCodeRequired</t>
+          <t>validation.accountTypeRequired</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>IFSC કોડ જરૂરી છે</t>
+          <t>કૃપા કરીને ખાતા પ્રકાર પસંદ કરો</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>validation.ifscCodeInvalid</t>
+          <t>validation.limitReached</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>માન્ય IFSC કોડ દાખલ કરો (4 અક્ષર + 7 અંક)</t>
+          <t>તમે 5 બૅન્ક ખાતાઓની મહત્તમ મર્યાદા પહોંચ્યા છો.</t>
         </is>
       </c>
     </row>
@@ -6672,12 +6672,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>validation.accountTypeRequired</t>
+          <t>toasts.createSuccess</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>કૃપા કરીને ખાતા પ્રકાર પસંદ કરો</t>
+          <t>બૅન્ક ખાતું સફળતાપૂર્વક બનાવવામાં આવ્યું.</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>validation.limitReached</t>
+          <t>toasts.createError</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>તમે 5 બૅન્ક ખાતાઓની મહત્તમ મર્યાદા પહોંચ્યા છો.</t>
+          <t>બૅન્ક ખાતું બનાવવામાં નિષ્ફળ.</t>
         </is>
       </c>
     </row>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>toasts.createSuccess</t>
+          <t>toasts.updateSuccess</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>બૅન્ક ખાતું સફળતાપૂર્વક બનાવવામાં આવ્યું.</t>
+          <t>બૅન્ક ખાતું સફળતાપૂર્વક અપડેટ થઈ.</t>
         </is>
       </c>
     </row>
@@ -6723,12 +6723,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>toasts.createError</t>
+          <t>toasts.updateError</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>બૅન્ક ખાતું બનાવવામાં નિષ્ફળ.</t>
+          <t>બૅન્ક ખાતું અપડેટ કરવામાં નિષ્ફળ</t>
         </is>
       </c>
     </row>
@@ -6740,46 +6740,46 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>toasts.updateSuccess</t>
+          <t>toasts.alreadyExists</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>બૅન્ક ખાતું સફળતાપૂર્વક અપડેટ થઈ.</t>
+          <t>બૅન્ક ખાતું પહેલેથી અસ્તિત્વ ધરાવે છે</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>bankInfo</t>
+          <t>transactionHistory</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>toasts.updateError</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>બૅન્ક ખાતું અપડેટ કરવામાં નિષ્ફળ</t>
+          <t>વ્યવહાર ઇતિહાસ</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>bankInfo</t>
+          <t>transactionHistory</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>toasts.alreadyExists</t>
+          <t>tabs.gameHistory</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>બૅન્ક ખાતું પહેલેથી અસ્તિત્વ ધરાવે છે</t>
+          <t>ગેમ ઇતિહાસ</t>
         </is>
       </c>
     </row>
@@ -6791,12 +6791,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>tabs.depositSummary</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>વ્યવહાર ઇતિહાસ</t>
+          <t>ડિપૉઝિટ સારાંશ</t>
         </is>
       </c>
     </row>
@@ -6808,12 +6808,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>tabs.gameHistory</t>
+          <t>tabs.withdrawSummary</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>ગેમ ઇતિહાસ</t>
+          <t>ઉપાડ સારાંશ</t>
         </is>
       </c>
     </row>
@@ -6825,12 +6825,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>tabs.depositSummary</t>
+          <t>tabs.allTransactions</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ સારાંશ</t>
+          <t>બધા વ્યવહાર</t>
         </is>
       </c>
     </row>
@@ -6842,12 +6842,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>tabs.withdrawSummary</t>
+          <t>transactionTable.columns.serialNo</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>ઉપાડ સારાંશ</t>
+          <t>ક્રમ નં.</t>
         </is>
       </c>
     </row>
@@ -6859,12 +6859,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>tabs.allTransactions</t>
+          <t>transactionTable.columns.description</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>બધા વ્યવહાર</t>
+          <t>વર્ણન</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>transactionTable.columns.serialNo</t>
+          <t>transactionTable.columns.gameName</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>ક્રમ નં.</t>
+          <t>ગેમ નામ</t>
         </is>
       </c>
     </row>
@@ -6893,12 +6893,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>transactionTable.columns.description</t>
+          <t>transactionTable.columns.startBalance</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>વર્ણન</t>
+          <t>પ્રારંભ બૅલૅન્સ</t>
         </is>
       </c>
     </row>
@@ -6910,12 +6910,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>transactionTable.columns.gameName</t>
+          <t>transactionTable.columns.amount</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>ગેમ નામ</t>
+          <t>રકમ</t>
         </is>
       </c>
     </row>
@@ -6927,12 +6927,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>transactionTable.columns.startBalance</t>
+          <t>transactionTable.columns.endBalance</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>પ્રારંભ બૅલૅન્સ</t>
+          <t>અંત બૅલૅન્સ</t>
         </is>
       </c>
     </row>
@@ -6944,12 +6944,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>transactionTable.columns.amount</t>
+          <t>transactionTable.columns.timeStamp</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>રકમ</t>
+          <t>ટાઇમ સ્ટૅમ્પ</t>
         </is>
       </c>
     </row>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>transactionTable.columns.endBalance</t>
+          <t>transactionTable.columns.transactionStatus</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>અંત બૅલૅન્સ</t>
+          <t>વ્યવહાર સ્ટેટ્સ</t>
         </is>
       </c>
     </row>
@@ -6978,12 +6978,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>transactionTable.columns.timeStamp</t>
+          <t>transactionTable.columns.providerName</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>ટાઇમ સ્ટૅમ્પ</t>
+          <t>પ્રૉવાઇડર નામ</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>transactionTable.columns.transactionStatus</t>
+          <t>transactionTable.columns.transactionId</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>વ્યવહાર સ્ટેટ્સ</t>
+          <t>વ્યવહાર ID</t>
         </is>
       </c>
     </row>
@@ -7012,12 +7012,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>transactionTable.columns.providerName</t>
+          <t>transactionTable.columns.gameTransactionId</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>પ્રૉવાઇડર નામ</t>
+          <t>ગેમ વ્યવહાર ID</t>
         </is>
       </c>
     </row>
@@ -7029,12 +7029,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>transactionTable.columns.transactionId</t>
+          <t>transactionTable.columns.referenceId</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>વ્યવહાર ID</t>
+          <t>સંદર્ભ ID</t>
         </is>
       </c>
     </row>
@@ -7046,12 +7046,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>transactionTable.columns.gameTransactionId</t>
+          <t>transactionTable.columns.transactionNo</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>ગેમ વ્યવહાર ID</t>
+          <t>વ્યવહાર નં.</t>
         </is>
       </c>
     </row>
@@ -7063,12 +7063,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>transactionTable.columns.referenceId</t>
+          <t>transactionTable.columns.status</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>સંદર્ભ ID</t>
+          <t>સ્ટેટ્સ</t>
         </is>
       </c>
     </row>
@@ -7080,12 +7080,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>transactionTable.columns.transactionNo</t>
+          <t>transactionTable.pagination.rowsPerPage</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>વ્યવહાર નં.</t>
+          <t>પ્રતિ પૃષ્ઠ પ્રવૃત્તિઓ:</t>
         </is>
       </c>
     </row>
@@ -7097,12 +7097,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>transactionTable.columns.status</t>
+          <t>transactionTable.pagination.prev</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>સ્ટેટ્સ</t>
+          <t>પહેલા</t>
         </is>
       </c>
     </row>
@@ -7114,12 +7114,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>transactionTable.pagination.rowsPerPage</t>
+          <t>transactionTable.pagination.next</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>પ્રતિ પૃષ્ઠ પ્રવૃત્તિઓ:</t>
+          <t>આગળ</t>
         </is>
       </c>
     </row>
@@ -7131,12 +7131,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>transactionTable.pagination.prev</t>
+          <t>transactionTable.dateSelector.today</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>પહેલા</t>
+          <t>આજ</t>
         </is>
       </c>
     </row>
@@ -7148,12 +7148,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>transactionTable.pagination.next</t>
+          <t>transactionTable.dateSelector.yesterday</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>આગળ</t>
+          <t>ગઈ કાલ</t>
         </is>
       </c>
     </row>
@@ -7165,12 +7165,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>transactionTable.dateSelector.today</t>
+          <t>transactionTable.dateSelector.thisWeek</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>આજ</t>
+          <t>આ અઠવાડિયે</t>
         </is>
       </c>
     </row>
@@ -7182,12 +7182,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>transactionTable.dateSelector.yesterday</t>
+          <t>transactionTable.dateSelector.lastWeek</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>ગઈ કાલ</t>
+          <t>ગત અઠવાડિયે</t>
         </is>
       </c>
     </row>
@@ -7199,12 +7199,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>transactionTable.dateSelector.thisWeek</t>
+          <t>transactionTable.dateSelector.thisMonth</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>આ અઠવાડિયે</t>
+          <t>આ મહિને</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>transactionTable.dateSelector.lastWeek</t>
+          <t>transactionTable.dateSelector.lastMonth</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>ગત અઠવાડિયે</t>
+          <t>ગત મહિને</t>
         </is>
       </c>
     </row>
@@ -7233,63 +7233,63 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>transactionTable.dateSelector.thisMonth</t>
+          <t>filters.allGames</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>આ મહિને</t>
+          <t>All Games</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>transactionHistory</t>
+          <t>partners</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>transactionTable.dateSelector.lastMonth</t>
+          <t>provider</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>ગત મહિને</t>
+          <t>પ્રૉવાઇડર</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>transactionHistory</t>
+          <t>header</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>filters.allGames</t>
+          <t>loginButton</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>All Games</t>
+          <t>લૉગ ઇન</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>partners</t>
+          <t>header</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>provider</t>
+          <t>registerButton</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>પ્રૉવાઇડર</t>
+          <t>નોંધણી</t>
         </is>
       </c>
     </row>
@@ -7301,12 +7301,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>loginButton</t>
+          <t>helloUser</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>લૉગ ઇન</t>
+          <t>નમસ્તે, {{userName}}</t>
         </is>
       </c>
     </row>
@@ -7318,12 +7318,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>registerButton</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>નોંધણી</t>
+          <t>બૅલૅન્સ</t>
         </is>
       </c>
     </row>
@@ -7335,12 +7335,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>helloUser</t>
+          <t>logout</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>નમસ્તે, {{userName}}</t>
+          <t>લૉગ આઉટ</t>
         </is>
       </c>
     </row>
@@ -7352,46 +7352,46 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>toasts.logoutSuccess</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>બૅલૅન્સ</t>
+          <t>લૉગ આઉટ સફળ</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>header</t>
+          <t>footer</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>logout</t>
+          <t>socialLinks</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>લૉગ આઉટ</t>
+          <t>સોશ્યલ લિંક્સ</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>header</t>
+          <t>footer</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>toasts.logoutSuccess</t>
+          <t>contactAlt</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>લૉગ આઉટ સફળ</t>
+          <t>સંપર્ક</t>
         </is>
       </c>
     </row>
@@ -7403,12 +7403,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>socialLinks</t>
+          <t>copyright</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>સોશ્યલ લિંક્સ</t>
+          <t>© કૉપીરાઇટ 2026 {{brandName}}. સર્વ અધિકાર સુરક્ષિત.</t>
         </is>
       </c>
     </row>
@@ -7420,301 +7420,301 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>logoAlt</t>
+          <t>version</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>લોગો</t>
+          <t>આવૃત્તિ</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>footer</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>contactAlt</t>
+          <t>switchToLight</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>સંપર્ક</t>
+          <t>લાઇટ મોડ પર સ્વિચ કરો</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>footer</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>copyright</t>
+          <t>switchToDark</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>© કૉપીરાઇટ 2026 {{brandName}}. સર્વ અધિકાર સુરક્ષિત.</t>
+          <t>ડાર્ક મોડ પર સ્વિચ કરો</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>footer</t>
+          <t>notAuthorized</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>message</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>આવૃત્તિ</t>
+          <t>આ પૃષ્ઠ ઍક્સેસ કરવા માટે તમે અધિકૃત નથી.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>notFound</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>switchToLight</t>
+          <t>code</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>લાઇટ મોડ પર સ્વિચ કરો</t>
+          <t>404</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>notFound</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>switchToDark</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>ડાર્ક મોડ પર સ્વિચ કરો</t>
+          <t>અરે! પૃષ્ઠ મળ્યું નહીં</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>multiLadder</t>
+          <t>notFound</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>allMilestonesComplete</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>બધા માઇલસ્ટોન પૂર્ણ!</t>
+          <t>જે પૃષ્ઠ તમે શોધી રહ્યા છો તે અસ્તિત્વ ધરાવ્યું નથી અથવા ખસેડવામાં આવ્યું છે. ચાલો તમને પાછા જ્યાં હોવ ત્યાં મોકલીએ.</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>multiLadder</t>
+          <t>aboutSection</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>milestoneUnlocked</t>
+          <t>defaultTitle</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>માઇલસ્ટોન અનલૉક થઈ ગઈ</t>
+          <t>{{brandName}} વિષે</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>multiLadder</t>
+          <t>aboutSection</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>tierReached</t>
+          <t>bgAlt</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>{{tierName}} પ્રાપ્ત!</t>
+          <t>about background</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>notAuthorized</t>
+          <t>exploreFeatures</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>આ પૃષ્ઠ ઍક્સેસ કરવા માટે તમે અધિકૃત નથી.</t>
+          <t>બધી સુવિધાઓ એક્સ્પ્લોર કરો</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>notFound</t>
+          <t>exploreFeatures</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>downloadApplication</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>એપ્લિકેશન ડાઉનલોડ કરો</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>notFound</t>
+          <t>exploreFeatures</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>installApplication</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>અરે! પૃષ્ઠ મળ્યું નહીં</t>
+          <t>એપ્લિકેશન ઇન્સ્ટોલ કરો</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>notFound</t>
+          <t>leaderboard</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>જે પૃષ્ઠ તમે શોધી રહ્યા છો તે અસ્તિત્વ ધરાવ્યું નથી અથવા ખસેડવામાં આવ્યું છે. ચાલો તમને પાછા જ્યાં હોવ ત્યાં મોકલીએ.</t>
+          <t>ટૂર્નામૅન્ટ</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>aboutSection</t>
+          <t>leaderboard</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>defaultTitle</t>
+          <t>termsAndConditions</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>{{brandName}} વિષે</t>
+          <t>નિયમો અને શરતો</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>aboutSection</t>
+          <t>leaderboard</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>bgAlt</t>
+          <t>myRank</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>about background</t>
+          <t>મારો ક્રમ</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>exploreFeatures</t>
+          <t>leaderboard</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>start</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>બધી સુવિધાઓ એક્સ્પ્લોર કરો</t>
+          <t>શરૂ</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>exploreFeatures</t>
+          <t>leaderboard</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>downloadApplication</t>
+          <t>end</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>એપ્લિકેશન ડાઉનલોડ કરો</t>
+          <t>અંત</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>exploreFeatures</t>
+          <t>leaderboard</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>installApplication</t>
+          <t>rank</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>એપ્લિકેશન ઇન્સ્ટોલ કરો</t>
+          <t>ક્રમ</t>
         </is>
       </c>
     </row>
@@ -7726,12 +7726,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>player</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>ટૂર્નામૅન્ટ</t>
+          <t>ખેલાડી</t>
         </is>
       </c>
     </row>
@@ -7743,12 +7743,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>termsAndConditions</t>
+          <t>points</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>નિયમો અને શરતો</t>
+          <t>પૉઇન્ટ</t>
         </is>
       </c>
     </row>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>myRank</t>
+          <t>prize</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>મારો ક્રમ</t>
+          <t>ઇનામ</t>
         </is>
       </c>
     </row>
@@ -7777,12 +7777,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>start</t>
+          <t>noPlayersFound</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>શરૂ</t>
+          <t>કોઈ ખેલાડી મળ્યા નહીં</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>end</t>
+          <t>noActiveTournaments</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>અંત</t>
+          <t>હાલ કોઈ સક્રિય ટૂર્નામૅન્ટ નથી</t>
         </is>
       </c>
     </row>
@@ -7811,114 +7811,114 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>rank</t>
+          <t>trophyAlt</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>ક્રમ</t>
+          <t>ટ્રૉફી</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>leaderboard</t>
+          <t>ladder</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>loading</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>ખેલાડી</t>
+          <t>તમારી લૅડર લોડ થઈ રહી છે…</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>leaderboard</t>
+          <t>ladder</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>allMilestones</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>પૉઇન્ટ</t>
+          <t>બધા માઇલસ્ટોન</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>leaderboard</t>
+          <t>ladder</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>prize</t>
+          <t>creditedInstantly</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>ઇનામ</t>
+          <t>તમારા વૉલેટમાં તરત ક્રેડિટ</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>leaderboard</t>
+          <t>ladder</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>noPlayersFound</t>
+          <t>fullTermsApply</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>કોઈ ખેલાડી મળ્યા નહીં</t>
+          <t>સંપૂર્ણ T&amp;C લાગૂ.</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>leaderboard</t>
+          <t>ladder</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>noActiveTournaments</t>
+          <t>simulatingProgress</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>હાલ કોઈ સક્રિય ટૂર્નામૅન્ટ નથી</t>
+          <t>પ્રગતિ સિમ્યુલેટ થઈ રહી છે</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>leaderboard</t>
+          <t>ladder</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>trophyAlt</t>
+          <t>simulateProgress</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>ટ્રૉફી</t>
+          <t>તમારી પ્રગતિ સિમ્યુલેટ કરો</t>
         </is>
       </c>
     </row>
@@ -7930,12 +7930,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>loading</t>
+          <t>simulateBetAmount</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>તમારી લૅડર લોડ થઈ રહી છે…</t>
+          <t>દાવ રકમ સિમ્યુલેટ કરો</t>
         </is>
       </c>
     </row>
@@ -7947,12 +7947,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>allMilestones</t>
+          <t>toNextReward</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>બધા માઇલસ્ટોન</t>
+          <t>આગળના ઇનામ સુધી</t>
         </is>
       </c>
     </row>
@@ -7964,12 +7964,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>creditedInstantly</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>તમારા વૉલેટમાં તરત ક્રેડિટ</t>
+          <t>અનલૉક</t>
         </is>
       </c>
     </row>
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>fullTermsApply</t>
+          <t>stillToEarn</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>સંપૂર્ણ T&amp;C લાગૂ.</t>
+          <t>હજૂ કમાવવા</t>
         </is>
       </c>
     </row>
@@ -7998,12 +7998,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>simulatingProgress</t>
+          <t>nextReward</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>પ્રગતિ સિમ્યુલેટ થઈ રહી છે</t>
+          <t>આગળનું ઇનામ</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>simulateProgress</t>
+          <t>moreToUnlock</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>તમારી પ્રગતિ સિમ્યુલેટ કરો</t>
+          <t>અનલૉક કરવા વધુ</t>
         </is>
       </c>
     </row>
@@ -8032,12 +8032,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>simulateBetAmount</t>
+          <t>percentThere</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>દાવ રકમ સિમ્યુલેટ કરો</t>
+          <t>ત્યાં સુધી</t>
         </is>
       </c>
     </row>
@@ -8049,12 +8049,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>toNextReward</t>
+          <t>allMilestonesCompletePre</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>આગળના ઇનામ સુધી</t>
+          <t>બધા માઇલસ્ટોન પૂર્ણ</t>
         </is>
       </c>
     </row>
@@ -8066,12 +8066,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>unlocked</t>
+          <t>allMilestonesCompletePost</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>અનલૉક</t>
+          <t>કમાયા!</t>
         </is>
       </c>
     </row>
@@ -8083,12 +8083,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>stillToEarn</t>
+          <t>bonusCredited</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>હજૂ કમાવવા</t>
+          <t>{{count}} બોનસ ક્રેડિટ</t>
         </is>
       </c>
     </row>
@@ -8100,12 +8100,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>nextReward</t>
+          <t>bonusesCredited</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>આગળનું ઇનામ</t>
+          <t>{{count}} બોનસ ક્રેડિટ</t>
         </is>
       </c>
     </row>
@@ -8117,12 +8117,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>moreToUnlock</t>
+          <t>milestoneName</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>અનલૉક કરવા વધુ</t>
+          <t>{{name}} માઇલસ્ટોન</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>percentThere</t>
+          <t>creditedInstantlyLabel</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>ત્યાં સુધી</t>
+          <t>તરત ક્રેડિટ</t>
         </is>
       </c>
     </row>
@@ -8151,12 +8151,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>allMilestonesCompletePre</t>
+          <t>bonusEarnedLabel</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>બધા માઇલસ્ટોન પૂર્ણ</t>
+          <t>બોનસ કમાયા</t>
         </is>
       </c>
     </row>
@@ -8168,12 +8168,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>allMilestonesCompletePost</t>
+          <t>totalPossible</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>કમાયા!</t>
+          <t>કુલ સંભવ</t>
         </is>
       </c>
     </row>
@@ -8185,12 +8185,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>bonusCredited</t>
+          <t>creditedRewards</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>{{count}} બોનસ ક્રેડિટ</t>
+          <t>ક્રેડિટ ઇનામ</t>
         </is>
       </c>
     </row>
@@ -8202,12 +8202,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>bonusesCredited</t>
+          <t>credited</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>{{count}} બોનસ ક્રેડિટ</t>
+          <t>ક્રેડિટ</t>
         </is>
       </c>
     </row>
@@ -8219,12 +8219,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>milestoneName</t>
+          <t>realMoney</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>{{name}} માઇલસ્ટોન</t>
+          <t>રિઅલ મની</t>
         </is>
       </c>
     </row>
@@ -8236,12 +8236,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>creditedInstantlyLabel</t>
+          <t>completedAt</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>તરત ક્રેડિટ</t>
+          <t>પૂર્ણ સ્થળ</t>
         </is>
       </c>
     </row>
@@ -8253,12 +8253,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>bonusEarnedLabel</t>
+          <t>tierPercentThere</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>બોનસ કમાયા</t>
+          <t>{{pct}}% ત્યાં</t>
         </is>
       </c>
     </row>
@@ -8270,12 +8270,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>totalPossible</t>
+          <t>cumulativeBets</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>કુલ સંભવ</t>
+          <t>સંચિત દાવ</t>
         </is>
       </c>
     </row>
@@ -8287,12 +8287,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>creditedRewards</t>
+          <t>promotion</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>ક્રેડિટ ઇનામ</t>
+          <t>બોનસ લૅડર પ્રોમોશન</t>
         </is>
       </c>
     </row>
@@ -8304,12 +8304,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>credited</t>
+          <t>termsAndConditions</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>ક્રેડિટ</t>
+          <t>નિયમો અને શરતો</t>
         </is>
       </c>
     </row>
@@ -8321,12 +8321,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>realMoney</t>
+          <t>termsDialogLabel</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>રિઅલ મની</t>
+          <t>બોનસ લૅડર નિયમો અને શરતો</t>
         </is>
       </c>
     </row>
@@ -8338,12 +8338,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>completedAt</t>
+          <t>understandAndClose</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>પૂર્ણ સ્થળ</t>
+          <t>હું સમજ્યો — બંધ કરો</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>tierPercentThere</t>
+          <t>variants.deposit.placed</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>{{pct}}% ત્યાં</t>
+          <t>ડિપૉઝિટ</t>
         </is>
       </c>
     </row>
@@ -8372,12 +8372,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>cumulativeBets</t>
+          <t>variants.deposit.totalPlacedShort</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>સંચિત દાવ</t>
+          <t>કુલ ડિપૉઝિટ</t>
         </is>
       </c>
     </row>
@@ -8389,12 +8389,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>promotion</t>
+          <t>variants.deposit.totalPlacedLong</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>બોનસ લૅડર પ્રોમોશન</t>
+          <t>આ કૅમ્પેઇનમાં કુલ ડિપૉઝિટ</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>termsAndConditions</t>
+          <t>variants.deposit.milestonesUnlocked</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>નિયમો અને શરતો</t>
+          <t>{{done}} of {{total}} માઇલસ્ટોન પ્રાપ્ત</t>
         </is>
       </c>
     </row>
@@ -8423,12 +8423,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>termsDialogLabel</t>
+          <t>variants.deposit.betMoreToUnlock</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>બોનસ લૅડર નિયમો અને શરતો</t>
+          <t>ડિપૉઝિટ</t>
         </is>
       </c>
     </row>
@@ -8440,12 +8440,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>understandAndClose</t>
+          <t>variants.deposit.noRewardsYet</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>હું સમજ્યો — બંધ કરો</t>
+          <t>હજૂ કોઈ ઇનામ નહીં — પ્રથમ ક્વૉલિફાઇંગ ડિપૉઝિટ કરો</t>
         </is>
       </c>
     </row>
@@ -8457,12 +8457,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>variants.deposit.placed</t>
+          <t>variants.deposit.cumulativeUnit</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ</t>
+          <t>સંચિત ડિપૉઝિટ</t>
         </is>
       </c>
     </row>
@@ -8474,12 +8474,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>variants.deposit.totalPlacedShort</t>
+          <t>variants.deposit.keepGoing</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>કુલ ડિપૉઝિટ</t>
+          <t>ડિપૉઝિટ ચાલૂ રાખો →</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>variants.deposit.totalPlacedLong</t>
+          <t>variants.deposit.overlayNextCta</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>આ કૅમ્પેઇનમાં કુલ ડિપૉઝિટ</t>
+          <t>ડિપૉઝિટ</t>
         </is>
       </c>
     </row>
@@ -8508,12 +8508,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>variants.deposit.milestonesUnlocked</t>
+          <t>variants.bet.placed</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>{{done}} of {{total}} માઇલસ્ટોન પ્રાપ્ત</t>
+          <t>લગાવ્યો</t>
         </is>
       </c>
     </row>
@@ -8525,12 +8525,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>variants.deposit.betMoreToUnlock</t>
+          <t>variants.bet.totalPlacedShort</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ</t>
+          <t>કુલ દાવ</t>
         </is>
       </c>
     </row>
@@ -8542,12 +8542,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>variants.deposit.noRewardsYet</t>
+          <t>variants.bet.totalPlacedLong</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>હજૂ કોઈ ઇનામ નહીં — પ્રથમ ક્વૉલિફાઇંગ ડિપૉઝિટ કરો</t>
+          <t>આ કૅમ્પેઇનમાં કુલ દાવ</t>
         </is>
       </c>
     </row>
@@ -8559,12 +8559,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>variants.deposit.cumulativeUnit</t>
+          <t>variants.bet.milestonesUnlocked</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>સંચિત ડિપૉઝિટ</t>
+          <t>{{done}} of {{total}} માઇલસ્ટોન અનલૉક</t>
         </is>
       </c>
     </row>
@@ -8576,12 +8576,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>variants.deposit.keepGoing</t>
+          <t>variants.bet.betMoreToUnlock</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ ચાલૂ રાખો →</t>
+          <t>દાવ</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>variants.deposit.overlayNextCta</t>
+          <t>variants.bet.noRewardsYet</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>ડિપૉઝિટ</t>
+          <t>હજૂ કોઈ ઇનામ નહીં — પ્રથમ ક્વૉલિફાઇંગ દાવ લગાવો</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>variants.bet.placed</t>
+          <t>variants.bet.cumulativeUnit</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>લગાવ્યો</t>
+          <t>સંચિત દાવ</t>
         </is>
       </c>
     </row>
@@ -8627,12 +8627,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>variants.bet.totalPlacedShort</t>
+          <t>variants.bet.keepGoing</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>કુલ દાવ</t>
+          <t>દાવ ચાલૂ રાખો →</t>
         </is>
       </c>
     </row>
@@ -8644,12 +8644,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>variants.bet.totalPlacedLong</t>
+          <t>variants.bet.overlayNextCta</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>આ કૅમ્પેઇનમાં કુલ દાવ</t>
+          <t>દાવ</t>
         </is>
       </c>
     </row>
@@ -8661,12 +8661,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>variants.bet.milestonesUnlocked</t>
+          <t>overlay.allMilestonesComplete</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>{{done}} of {{total}} માઇલસ્ટોન અનલૉક</t>
+          <t>બધા માઇલસ્ટોન પૂર્ણ!</t>
         </is>
       </c>
     </row>
@@ -8678,12 +8678,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>variants.bet.betMoreToUnlock</t>
+          <t>overlay.milestoneUnlocked</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>દાવ</t>
+          <t>માઇલસ્ટોન અનલૉક</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>variants.bet.noRewardsYet</t>
+          <t>overlay.tierReached</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>હજૂ કોઈ ઇનામ નહીં — પ્રથમ ક્વૉલિફાઇંગ દાવ લગાવો</t>
+          <t>{{name}} પ્રાપ્ત!</t>
         </is>
       </c>
     </row>
@@ -8712,12 +8712,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>variants.bet.cumulativeUnit</t>
+          <t>overlay.rolloverNote</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>સંચિત દાવ</t>
+          <t>રિઅલ મની · રૉલઓવર: 1× · ક્યારેય સમાપ્ત નહીં</t>
         </is>
       </c>
     </row>
@@ -8729,12 +8729,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>variants.bet.keepGoing</t>
+          <t>overlay.nextMilestone</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>દાવ ચાલૂ રાખો →</t>
+          <t>આગળ માઇલસ્ટોન — {{name}}</t>
         </is>
       </c>
     </row>
@@ -8746,7 +8746,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>variants.bet.overlayNextCta</t>
+          <t>overlay.betMore</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>overlay.allMilestonesComplete</t>
+          <t>overlay.betMoreToEarn</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>બધા માઇલસ્ટોન પૂર્ણ!</t>
+          <t>વધુ કમાવવા</t>
         </is>
       </c>
     </row>
@@ -8780,12 +8780,12 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>overlay.milestoneUnlocked</t>
+          <t>overlay.allDoneTitle</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>માઇલસ્ટોન અનલૉક</t>
+          <t>તમે બધા માઇલસ્ટોન પૂર્ણ કર્યા!</t>
         </is>
       </c>
     </row>
@@ -8797,12 +8797,12 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>overlay.tierReached</t>
+          <t>overlay.allDoneSubtitle</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>{{name}} પ્રાપ્ત!</t>
+          <t>બધા બોનસ તમારા વૉલેટમાં ક્રેડિટ થઈ ગયા.</t>
         </is>
       </c>
     </row>
@@ -8814,12 +8814,12 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>overlay.rolloverNote</t>
+          <t>overlay.viewLadder</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>રિઅલ મની · રૉલઓવર: 1× · ક્યારેય સમાપ્ત નહીં</t>
+          <t>મારી લૅડર જુઓ</t>
         </is>
       </c>
     </row>
@@ -8831,12 +8831,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>overlay.nextMilestone</t>
+          <t>overlay.viewLadderArrow</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>આગળ માઇલસ્ટોન — {{name}}</t>
+          <t>મારી લૅડર જુઓ →</t>
         </is>
       </c>
     </row>
@@ -8848,12 +8848,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>overlay.betMore</t>
+          <t>achievement.milestoneUnlocked</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>દાવ</t>
+          <t>માઇલસ્ટોન અનલૉક</t>
         </is>
       </c>
     </row>
@@ -8865,114 +8865,114 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>overlay.betMoreToEarn</t>
+          <t>achievement.tierAchieved</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>વધુ કમાવવા</t>
+          <t>ટિઅર પ્રાપ્ત!</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>ladder</t>
+          <t>jackpot</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>overlay.allDoneTitle</t>
+          <t>monthlyJackpot</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>તમે બધા માઇલસ્ટોન પૂર્ણ કર્યા!</t>
+          <t>માસિક જેકપોટ</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>ladder</t>
+          <t>jackpot</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>overlay.allDoneSubtitle</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>બધા બોનસ તમારા વૉલેટમાં ક્રેડિટ થઈ ગયા.</t>
+          <t>જેકપોટ વિજેતાઓ</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>ladder</t>
+          <t>jackpot</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>overlay.viewLadder</t>
+          <t>winner</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>મારી લૅડર જુઓ</t>
+          <t>જેકપોટ વિજેતા</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>ladder</t>
+          <t>jackpot</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>overlay.viewLadderArrow</t>
+          <t>congratulationDefault</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>મારી લૅડર જુઓ →</t>
+          <t>અભિનંદન — તમે આ મહિનાના જેકપોટ વિજેતાઓમાંના એક છો!</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>ladder</t>
+          <t>jackpot</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>achievement.milestoneUnlocked</t>
+          <t>youWonThisMonthPre</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>માઇલસ્ટોન અનલૉક</t>
+          <t>તમે જીત્યા</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>ladder</t>
+          <t>jackpot</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>achievement.tierAchieved</t>
+          <t>youWonThisMonthPost</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>ટિઅર પ્રાપ્ત!</t>
+          <t>આ મહિને</t>
         </is>
       </c>
     </row>
@@ -8984,12 +8984,12 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>monthlyJackpot</t>
+          <t>loadError</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>માસિક જેકપોટ</t>
+          <t>{{month}} માટેના વિજેતાઓ લોડ કરી શકાયા નથી.</t>
         </is>
       </c>
     </row>
@@ -9001,12 +9001,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>noWinners</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>જેકપોટ વિજેતાઓ</t>
+          <t>{{month}} માટે હજી સુધી કોઈ જેકપોટ વિજેતા નથી.</t>
         </is>
       </c>
     </row>
@@ -9018,12 +9018,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>winner</t>
+          <t>checkBack</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>જેકપોટ વિજેતા</t>
+          <t>આગામી ડ્રો પછી ફરી તપાસો.</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>congratulationDefault</t>
+          <t>loadMore</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>અભિનંદન — તમે આ મહિનાના જેકપોટ વિજેતાઓમાંના એક છો!</t>
+          <t>વધુ વિજેતાઓ લોડ કરો</t>
         </is>
       </c>
     </row>
@@ -9052,12 +9052,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>youWonThisMonthPre</t>
+          <t>winnerCount</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>તમે જીત્યા</t>
+          <t>{{month}} માટે {{count}} વિજેતા</t>
         </is>
       </c>
     </row>
@@ -9069,12 +9069,12 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>youWonThisMonthPost</t>
+          <t>winnersCount</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>આ મહિને</t>
+          <t>{{month}} માટે {{count}} વિજેતાઓ</t>
         </is>
       </c>
     </row>
@@ -9086,12 +9086,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>loadError</t>
+          <t>previousMonth</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>{{month}} માટેના વિજેતાઓ લોડ કરી શકાયા નથી.</t>
+          <t>પાછલો મહિનો</t>
         </is>
       </c>
     </row>
@@ -9103,12 +9103,12 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>noWinners</t>
+          <t>nextMonth</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>{{month}} માટે હજી સુધી કોઈ જેકપોટ વિજેતા નથી.</t>
+          <t>આગલો મહિનો</t>
         </is>
       </c>
     </row>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>checkBack</t>
+          <t>backToThisMonth</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>આગામી ડ્રો પછી ફરી તપાસો.</t>
+          <t>આ મહિને પાછા જાઓ</t>
         </is>
       </c>
     </row>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>loadMore</t>
+          <t>you</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>વધુ વિજેતાઓ લોડ કરો</t>
+          <t>તમે</t>
         </is>
       </c>
     </row>
@@ -9154,12 +9154,12 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>winnerCount</t>
+          <t>youBadge</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>{{month}} માટે {{count}} વિજેતા</t>
+          <t>તમે</t>
         </is>
       </c>
     </row>
@@ -9171,165 +9171,12 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>winnersCount</t>
+          <t>place</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>{{month}} માટે {{count}} વિજેતાઓ</t>
-        </is>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>jackpot</t>
-        </is>
-      </c>
-      <c r="B516" t="inlineStr">
-        <is>
-          <t>previousMonth</t>
-        </is>
-      </c>
-      <c r="C516" t="inlineStr">
-        <is>
-          <t>પાછલો મહિનો</t>
-        </is>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>jackpot</t>
-        </is>
-      </c>
-      <c r="B517" t="inlineStr">
-        <is>
-          <t>nextMonth</t>
-        </is>
-      </c>
-      <c r="C517" t="inlineStr">
-        <is>
-          <t>આગલો મહિનો</t>
-        </is>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>jackpot</t>
-        </is>
-      </c>
-      <c r="B518" t="inlineStr">
-        <is>
-          <t>backToThisMonth</t>
-        </is>
-      </c>
-      <c r="C518" t="inlineStr">
-        <is>
-          <t>આ મહિને પાછા જાઓ</t>
-        </is>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>jackpot</t>
-        </is>
-      </c>
-      <c r="B519" t="inlineStr">
-        <is>
-          <t>you</t>
-        </is>
-      </c>
-      <c r="C519" t="inlineStr">
-        <is>
-          <t>તમે</t>
-        </is>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>jackpot</t>
-        </is>
-      </c>
-      <c r="B520" t="inlineStr">
-        <is>
-          <t>youBadge</t>
-        </is>
-      </c>
-      <c r="C520" t="inlineStr">
-        <is>
-          <t>તમે</t>
-        </is>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>jackpot</t>
-        </is>
-      </c>
-      <c r="B521" t="inlineStr">
-        <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="C521" t="inlineStr">
-        <is>
           <t>{{position}} સ્થાન</t>
-        </is>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>pwa</t>
-        </is>
-      </c>
-      <c r="B522" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="C522" t="inlineStr">
-        <is>
-          <t>Setbet એપ</t>
-        </is>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>pwa</t>
-        </is>
-      </c>
-      <c r="B523" t="inlineStr">
-        <is>
-          <t>subTitle</t>
-        </is>
-      </c>
-      <c r="C523" t="inlineStr">
-        <is>
-          <t>Setbet</t>
-        </is>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>pwa</t>
-        </is>
-      </c>
-      <c r="B524" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C524" t="inlineStr">
-        <is>
-          <t>બૅટિંગ માટેની તમારી અંતિમ મંઝિલ</t>
         </is>
       </c>
     </row>
